--- a/research/traditional_assets/database/data/netherlands/netherlands_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_healthcare_products.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -596,22 +596,22 @@
         <v>0.16</v>
       </c>
       <c r="G2">
-        <v>0.1646926085897621</v>
+        <v>0.1634152281640018</v>
       </c>
       <c r="H2">
-        <v>0.06191567301049242</v>
+        <v>0.05998220614037268</v>
       </c>
       <c r="I2">
-        <v>0.04911701699363298</v>
+        <v>0.04722828329017412</v>
       </c>
       <c r="J2">
-        <v>0.04911701699363298</v>
+        <v>0.04722828329017412</v>
       </c>
       <c r="K2">
-        <v>-365.8</v>
+        <v>-403.5</v>
       </c>
       <c r="L2">
-        <v>-0.01818154707171721</v>
+        <v>-0.02005536971962245</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -635,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.001103433229702912</v>
       </c>
       <c r="W2">
-        <v>-0.02850130507616191</v>
+        <v>-0.5182613477252468</v>
       </c>
       <c r="X2">
-        <v>0.1039336665380234</v>
+        <v>0.0986662928291079</v>
       </c>
       <c r="Y2">
-        <v>-0.1324349716141853</v>
+        <v>-0.6169276405543547</v>
       </c>
       <c r="Z2">
-        <v>0.9344557720443092</v>
+        <v>0.9330620619162941</v>
       </c>
       <c r="AA2">
-        <v>0.04589768003529877</v>
+        <v>-0.4770511599823506</v>
       </c>
       <c r="AB2">
-        <v>0.08649090429811267</v>
+        <v>0.08829591969861661</v>
       </c>
       <c r="AC2">
-        <v>-0.0405932242628139</v>
+        <v>-0.5653470796809673</v>
       </c>
       <c r="AD2">
-        <v>9219.299999999999</v>
+        <v>9237.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9219.299999999999</v>
+        <v>9237.9</v>
       </c>
       <c r="AG2">
-        <v>9219.299999999999</v>
+        <v>9211.6</v>
       </c>
       <c r="AH2">
-        <v>0.2809503058080677</v>
+        <v>0.2793218555541445</v>
       </c>
       <c r="AI2">
-        <v>0.4095118798555494</v>
+        <v>0.4096411720884032</v>
       </c>
       <c r="AJ2">
-        <v>0.2809503058080677</v>
+        <v>0.2787483016252954</v>
       </c>
       <c r="AK2">
-        <v>0.4095118798555494</v>
+        <v>0.408951871040493</v>
       </c>
       <c r="AL2">
-        <v>331.3</v>
+        <v>332.285</v>
       </c>
       <c r="AM2">
-        <v>246.5</v>
+        <v>246.255</v>
       </c>
       <c r="AN2">
-        <v>5.288418516606436</v>
+        <v>5.415899630650173</v>
       </c>
       <c r="AO2">
-        <v>2.982795049803803</v>
+        <v>2.85959342131002</v>
       </c>
       <c r="AP2">
-        <v>5.288418516606436</v>
+        <v>5.400480741044732</v>
       </c>
       <c r="AQ2">
-        <v>4.008924949290061</v>
+        <v>3.858601855799882</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +775,10 @@
         <v>-0.02850130507616191</v>
       </c>
       <c r="X3">
-        <v>0.1039336665380234</v>
+        <v>0.1038962917591346</v>
       </c>
       <c r="Y3">
-        <v>-0.1324349716141853</v>
+        <v>-0.1323975968352965</v>
       </c>
       <c r="Z3">
         <v>0.9344557720443092</v>
@@ -787,10 +787,10 @@
         <v>0.04589768003529877</v>
       </c>
       <c r="AB3">
-        <v>0.08649090429811267</v>
+        <v>0.08646402997478218</v>
       </c>
       <c r="AC3">
-        <v>-0.0405932242628139</v>
+        <v>-0.04056634993948342</v>
       </c>
       <c r="AD3">
         <v>9219.299999999999</v>
@@ -833,6 +833,116 @@
       </c>
       <c r="AQ3">
         <v>4.008924949290061</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Onward Medical N.V. (ENXTBR:ONWD)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-37.7</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>26.3</v>
+      </c>
+      <c r="V4">
+        <v>0.1099038863351442</v>
+      </c>
+      <c r="W4">
+        <v>-1.008021390374332</v>
+      </c>
+      <c r="X4">
+        <v>0.09343629389908117</v>
+      </c>
+      <c r="Y4">
+        <v>-1.101457684273413</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-1</v>
+      </c>
+      <c r="AB4">
+        <v>0.09012780942245105</v>
+      </c>
+      <c r="AC4">
+        <v>-1.090127809422451</v>
+      </c>
+      <c r="AD4">
+        <v>18.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>18.6</v>
+      </c>
+      <c r="AG4">
+        <v>-7.699999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.07212097712291586</v>
+      </c>
+      <c r="AI4">
+        <v>0.4856396866840732</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.03324697754749568</v>
+      </c>
+      <c r="AK4">
+        <v>-0.6416666666666666</v>
+      </c>
+      <c r="AL4">
+        <v>0.985</v>
+      </c>
+      <c r="AM4">
+        <v>-0.245</v>
+      </c>
+      <c r="AN4">
+        <v>-0.4946808510638298</v>
+      </c>
+      <c r="AO4">
+        <v>-38.57868020304569</v>
+      </c>
+      <c r="AP4">
+        <v>0.2047872340425532</v>
+      </c>
+      <c r="AQ4">
+        <v>155.1020408163265</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1237,49 @@
         <v>2.9827950498038</v>
       </c>
       <c r="F2">
-        <v>3.11031041824304</v>
+        <v>2.59640964844683</v>
       </c>
       <c r="G2">
         <v>5.28841851660644</v>
       </c>
       <c r="H2">
-        <v>3.76466471634257</v>
+        <v>4.51759765961108</v>
       </c>
       <c r="I2">
         <v>0.280950305808068</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="K2">
         <v>23595.4</v>
       </c>
       <c r="L2">
-        <v>25097.3418941719</v>
+        <v>24238.701463942</v>
       </c>
       <c r="M2">
         <v>32814.7</v>
       </c>
       <c r="N2">
-        <v>31660.2818941719</v>
+        <v>32114.229463942</v>
       </c>
       <c r="O2">
         <v>9219.299999999999</v>
       </c>
       <c r="P2">
-        <v>6562.94</v>
+        <v>7875.528</v>
       </c>
       <c r="Q2">
-        <v>0.08649090429811269</v>
+        <v>0.0864640299747822</v>
       </c>
       <c r="R2">
-        <v>0.08797460292155759</v>
+        <v>0.0873509874185749</v>
       </c>
       <c r="S2">
         <v>0.0418488</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0428876</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1178,20 +1288,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.103933666538023</v>
+        <v>0.103896291759135</v>
       </c>
       <c r="X2">
-        <v>0.099227803651947</v>
+        <v>0.101392057129704</v>
       </c>
       <c r="Y2">
         <v>1.34171574501466</v>
       </c>
       <c r="Z2">
-        <v>1.23310518070423</v>
+        <v>1.28388122701395</v>
       </c>
       <c r="AA2">
         <v>9219.299999999999</v>
@@ -1224,7 +1334,7 @@
         <v>23595.4</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1522,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09086773821336736</v>
+        <v>0.09083876366469271</v>
       </c>
       <c r="C2">
-        <v>29627.84178228922</v>
+        <v>29627.32179656933</v>
       </c>
       <c r="D2">
-        <v>29627.84178228922</v>
+        <v>29627.32179656933</v>
       </c>
       <c r="E2">
         <v>-9219.299999999999</v>
@@ -1463,19 +1573,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09086773821336736</v>
+        <v>0.09083876366469271</v>
       </c>
       <c r="T2">
         <v>1.040156204727314</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1604,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09067707744877689</v>
+        <v>0.09063778965443781</v>
       </c>
       <c r="C3">
-        <v>29425.56899889399</v>
+        <v>29431.97174576014</v>
       </c>
       <c r="D3">
-        <v>29753.71599889399</v>
+        <v>29760.11874576014</v>
       </c>
       <c r="E3">
         <v>-8891.152999999998</v>
@@ -1527,37 +1637,37 @@
         <v>1181.9</v>
       </c>
       <c r="M3">
-        <v>16.9651999</v>
+        <v>16.5057941</v>
       </c>
       <c r="N3">
-        <v>1164.9348001</v>
+        <v>1165.3942059</v>
       </c>
       <c r="O3">
-        <v>300.5531784258</v>
+        <v>300.6717051222</v>
       </c>
       <c r="P3">
-        <v>864.3816216742</v>
+        <v>864.7225007778001</v>
       </c>
       <c r="Q3">
-        <v>1619.4816216742</v>
+        <v>1619.8225007778</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09120551863512816</v>
+        <v>0.09117632692367454</v>
       </c>
       <c r="T3">
         <v>1.047952122948604</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>69.66614050919613</v>
+        <v>71.60515833648986</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1686,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09048641668418639</v>
+        <v>0.09043681564418288</v>
       </c>
       <c r="C4">
-        <v>29224.37033493646</v>
+        <v>29237.8175121276</v>
       </c>
       <c r="D4">
-        <v>29880.66433493646</v>
+        <v>29894.1115121276</v>
       </c>
       <c r="E4">
         <v>-8563.005999999999</v>
@@ -1609,37 +1719,37 @@
         <v>1181.9</v>
       </c>
       <c r="M4">
-        <v>33.9303998</v>
+        <v>33.0115882</v>
       </c>
       <c r="N4">
-        <v>1147.9696002</v>
+        <v>1148.8884118</v>
       </c>
       <c r="O4">
-        <v>296.1761568516</v>
+        <v>296.4132102444</v>
       </c>
       <c r="P4">
-        <v>851.7934433484</v>
+        <v>852.4752015556001</v>
       </c>
       <c r="Q4">
-        <v>1606.8934433484</v>
+        <v>1607.5752015556</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09155019253488407</v>
+        <v>0.09152077922875805</v>
       </c>
       <c r="T4">
         <v>1.055907141541756</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>34.83307025459806</v>
+        <v>35.80257916824493</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1768,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09029575591959589</v>
+        <v>0.09023584163392798</v>
       </c>
       <c r="C5">
-        <v>29024.2595979649</v>
+        <v>29044.875320964</v>
       </c>
       <c r="D5">
-        <v>30008.7005979649</v>
+        <v>30029.316320964</v>
       </c>
       <c r="E5">
         <v>-8234.858999999999</v>
@@ -1691,37 +1801,37 @@
         <v>1181.9</v>
       </c>
       <c r="M5">
-        <v>50.8955997</v>
+        <v>49.51738229999999</v>
       </c>
       <c r="N5">
-        <v>1131.0044003</v>
+        <v>1132.3826177</v>
       </c>
       <c r="O5">
-        <v>291.7991352774</v>
+        <v>292.1547153666</v>
       </c>
       <c r="P5">
-        <v>839.2052650226001</v>
+        <v>840.2279023334</v>
       </c>
       <c r="Q5">
-        <v>1594.3052650226</v>
+        <v>1595.3279023334</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09190197311298545</v>
+        <v>0.09187233364322472</v>
       </c>
       <c r="T5">
         <v>1.06402618113683</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.22204683639871</v>
+        <v>23.86838611216329</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1850,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09010509515500541</v>
+        <v>0.09003486762367308</v>
       </c>
       <c r="C6">
-        <v>28825.25083320303</v>
+        <v>28853.1616924297</v>
       </c>
       <c r="D6">
-        <v>30137.83883320303</v>
+        <v>30165.7496924297</v>
       </c>
       <c r="E6">
         <v>-7906.712</v>
@@ -1773,37 +1883,37 @@
         <v>1181.9</v>
       </c>
       <c r="M6">
-        <v>67.86079960000001</v>
+        <v>66.0231764</v>
       </c>
       <c r="N6">
-        <v>1114.0392004</v>
+        <v>1115.8768236</v>
       </c>
       <c r="O6">
-        <v>287.4221137032</v>
+        <v>287.8962204888001</v>
       </c>
       <c r="P6">
-        <v>826.6170866968</v>
+        <v>827.9806031112</v>
       </c>
       <c r="Q6">
-        <v>1581.7170866968</v>
+        <v>1583.0806031112</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09226108245313064</v>
+        <v>0.09223121210799279</v>
       </c>
       <c r="T6">
         <v>1.072314367390134</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.41653512729903</v>
+        <v>17.90128958412247</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1932,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08991443439041492</v>
+        <v>0.08983389361341818</v>
       </c>
       <c r="C7">
-        <v>28627.35832868608</v>
+        <v>28662.69344828212</v>
       </c>
       <c r="D7">
-        <v>30268.09332868608</v>
+        <v>30303.42844828212</v>
       </c>
       <c r="E7">
         <v>-7578.565</v>
@@ -1855,37 +1965,37 @@
         <v>1181.9</v>
       </c>
       <c r="M7">
-        <v>84.82599949999999</v>
+        <v>82.52897049999999</v>
       </c>
       <c r="N7">
-        <v>1097.0740005</v>
+        <v>1099.3710295</v>
       </c>
       <c r="O7">
-        <v>283.045092129</v>
+        <v>283.637725611</v>
       </c>
       <c r="P7">
-        <v>814.0289083709999</v>
+        <v>815.7333038890001</v>
       </c>
       <c r="Q7">
-        <v>1569.128908371</v>
+        <v>1570.833303889</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09262775198991045</v>
+        <v>0.09259764590886124</v>
       </c>
       <c r="T7">
         <v>1.080777041775086</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.93322810183922</v>
+        <v>14.32103166729797</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2014,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08972377362582443</v>
+        <v>0.08963291960316326</v>
       </c>
       <c r="C8">
-        <v>28430.59662053065</v>
+        <v>28473.48771878979</v>
       </c>
       <c r="D8">
-        <v>30399.47862053065</v>
+        <v>30442.36971878979</v>
       </c>
       <c r="E8">
         <v>-7250.418</v>
@@ -1937,37 +2047,37 @@
         <v>1181.9</v>
       </c>
       <c r="M8">
-        <v>101.7911994</v>
+        <v>99.03476459999999</v>
       </c>
       <c r="N8">
-        <v>1080.1088006</v>
+        <v>1082.8652354</v>
       </c>
       <c r="O8">
-        <v>278.6680705548</v>
+        <v>279.3792307332</v>
       </c>
       <c r="P8">
-        <v>801.4407300452</v>
+        <v>803.4860046668</v>
       </c>
       <c r="Q8">
-        <v>1556.5407300452</v>
+        <v>1558.5860046668</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09300222300619621</v>
+        <v>0.09297187617357794</v>
       </c>
       <c r="T8">
         <v>1.089419773061846</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.61102341819935</v>
+        <v>11.93419305608164</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2096,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08953311286123396</v>
+        <v>0.08943194559290836</v>
       </c>
       <c r="C9">
-        <v>28234.98049834245</v>
+        <v>28285.56194983758</v>
       </c>
       <c r="D9">
-        <v>30532.00949834245</v>
+        <v>30582.59094983758</v>
       </c>
       <c r="E9">
         <v>-6922.270999999999</v>
@@ -2019,37 +2129,37 @@
         <v>1181.9</v>
       </c>
       <c r="M9">
-        <v>118.7563993</v>
+        <v>115.5405587</v>
       </c>
       <c r="N9">
-        <v>1063.1436007</v>
+        <v>1066.3594413</v>
       </c>
       <c r="O9">
-        <v>274.2910489806</v>
+        <v>275.1207358554</v>
       </c>
       <c r="P9">
-        <v>788.8525517194</v>
+        <v>791.2387054446001</v>
       </c>
       <c r="Q9">
-        <v>1543.9525517194</v>
+        <v>1546.3387054446</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09338474716261716</v>
+        <v>0.09335415440097673</v>
       </c>
       <c r="T9">
         <v>1.098248369537569</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.952305787028017</v>
+        <v>10.22930833378427</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2178,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08934245209664346</v>
+        <v>0.08923097158265346</v>
       </c>
       <c r="C10">
-        <v>28040.52501076619</v>
+        <v>28098.93391022917</v>
       </c>
       <c r="D10">
-        <v>30665.70101076618</v>
+        <v>30724.10991022917</v>
       </c>
       <c r="E10">
         <v>-6594.124</v>
@@ -2101,37 +2211,37 @@
         <v>1181.9</v>
       </c>
       <c r="M10">
-        <v>135.7215992</v>
+        <v>132.0463528</v>
       </c>
       <c r="N10">
-        <v>1046.1784008</v>
+        <v>1049.8536472</v>
       </c>
       <c r="O10">
-        <v>269.9140274064</v>
+        <v>270.8622409776</v>
       </c>
       <c r="P10">
-        <v>776.2643733936</v>
+        <v>778.9914062224</v>
       </c>
       <c r="Q10">
-        <v>1531.3643733936</v>
+        <v>1534.0914062224</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09377558706156897</v>
+        <v>0.09374474302462331</v>
       </c>
       <c r="T10">
         <v>1.107268892023633</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2249,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.708267563649514</v>
+        <v>8.950644792061233</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2260,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08922524933205297</v>
+        <v>0.08913016757239853</v>
       </c>
       <c r="C11">
-        <v>27795.14333720299</v>
+        <v>27842.26398183961</v>
       </c>
       <c r="D11">
-        <v>30748.46633720299</v>
+        <v>30795.58698183961</v>
       </c>
       <c r="E11">
         <v>-6265.977</v>
@@ -2183,37 +2293,37 @@
         <v>1181.9</v>
       </c>
       <c r="M11">
-        <v>155.9354544</v>
+        <v>152.9821314</v>
       </c>
       <c r="N11">
-        <v>1025.9645456</v>
+        <v>1028.9178686</v>
       </c>
       <c r="O11">
-        <v>264.6988527648001</v>
+        <v>265.4608100988</v>
       </c>
       <c r="P11">
-        <v>761.2656928352001</v>
+        <v>763.4570585012</v>
       </c>
       <c r="Q11">
-        <v>1516.3656928352</v>
+        <v>1518.5570585012</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09417501684840987</v>
+        <v>0.09414391601362476</v>
       </c>
       <c r="T11">
         <v>1.116487667751149</v>
       </c>
       <c r="U11">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2331,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.579418064657913</v>
+        <v>7.725738876716947</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2342,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0890427505674625</v>
+        <v>0.08894032356214364</v>
       </c>
       <c r="C12">
-        <v>27596.7650740653</v>
+        <v>27649.63654330891</v>
       </c>
       <c r="D12">
-        <v>30878.2350740653</v>
+        <v>30931.10654330891</v>
       </c>
       <c r="E12">
         <v>-5937.83</v>
@@ -2265,37 +2375,37 @@
         <v>1181.9</v>
       </c>
       <c r="M12">
-        <v>173.261616</v>
+        <v>169.980146</v>
       </c>
       <c r="N12">
-        <v>1008.638384</v>
+        <v>1011.919854</v>
       </c>
       <c r="O12">
-        <v>260.228703072</v>
+        <v>261.075322332</v>
       </c>
       <c r="P12">
-        <v>748.4096809280001</v>
+        <v>750.8445316680001</v>
       </c>
       <c r="Q12">
-        <v>1503.509680928</v>
+        <v>1505.944531668</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0945833228527361</v>
+        <v>0.09455195951349293</v>
       </c>
       <c r="T12">
         <v>1.1259113051615</v>
       </c>
       <c r="U12">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2413,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.821476258192122</v>
+        <v>6.953164989045251</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2424,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08903981580287199</v>
+        <v>0.08888923355188874</v>
       </c>
       <c r="C13">
-        <v>27270.71383578931</v>
+        <v>27358.16391461306</v>
       </c>
       <c r="D13">
-        <v>30880.33083578931</v>
+        <v>30967.78091461306</v>
       </c>
       <c r="E13">
         <v>-5609.682999999999</v>
@@ -2347,37 +2457,37 @@
         <v>1181.9</v>
       </c>
       <c r="M13">
-        <v>198.528935</v>
+        <v>193.1145095</v>
       </c>
       <c r="N13">
-        <v>983.371065</v>
+        <v>988.7854905000002</v>
       </c>
       <c r="O13">
-        <v>253.70973477</v>
+        <v>255.106656549</v>
       </c>
       <c r="P13">
-        <v>729.66133023</v>
+        <v>733.6788339510001</v>
       </c>
       <c r="Q13">
-        <v>1484.76133023</v>
+        <v>1488.778833951</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09500080427288987</v>
+        <v>0.09496917253021206</v>
       </c>
       <c r="T13">
         <v>1.135546709704666</v>
       </c>
       <c r="U13">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.953288370785851</v>
+        <v>6.120202998004147</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2506,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08900720103828151</v>
+        <v>0.08871200354163382</v>
       </c>
       <c r="C14">
-        <v>26965.87671693141</v>
+        <v>27157.91632913804</v>
       </c>
       <c r="D14">
-        <v>30903.64071693141</v>
+        <v>31095.68032913804</v>
       </c>
       <c r="E14">
         <v>-5281.536</v>
@@ -2429,45 +2539,45 @@
         <v>1181.9</v>
       </c>
       <c r="M14">
-        <v>222.483666</v>
+        <v>210.670374</v>
       </c>
       <c r="N14">
-        <v>959.4163340000001</v>
+        <v>971.2296260000001</v>
       </c>
       <c r="O14">
-        <v>247.529414172</v>
+        <v>250.577243508</v>
       </c>
       <c r="P14">
-        <v>711.8869198280001</v>
+        <v>720.652382492</v>
       </c>
       <c r="Q14">
-        <v>1466.986919828</v>
+        <v>1475.752382492</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09542777390713808</v>
+        <v>0.09539586766094753</v>
       </c>
       <c r="T14">
         <v>1.145401100714724</v>
       </c>
       <c r="U14">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.041923</v>
+        <v>0.039697</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>5.31230009487528</v>
+        <v>5.610186081503801</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2588,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08885215627369103</v>
+        <v>0.08861194153137891</v>
       </c>
       <c r="C15">
-        <v>26749.02374061481</v>
+        <v>26902.44756265606</v>
       </c>
       <c r="D15">
-        <v>31014.93474061481</v>
+        <v>31168.35856265606</v>
       </c>
       <c r="E15">
         <v>-4953.388999999999</v>
@@ -2511,37 +2621,37 @@
         <v>1181.9</v>
       </c>
       <c r="M15">
-        <v>241.0239715</v>
+        <v>231.6389673</v>
       </c>
       <c r="N15">
-        <v>940.8760285000001</v>
+        <v>950.2610327000001</v>
       </c>
       <c r="O15">
-        <v>242.746015353</v>
+        <v>245.1673464366</v>
       </c>
       <c r="P15">
-        <v>698.130013147</v>
+        <v>705.0936862634001</v>
       </c>
       <c r="Q15">
-        <v>1453.230013147</v>
+        <v>1460.1936862634</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09586455893527704</v>
+        <v>0.09583237187514818</v>
       </c>
       <c r="T15">
         <v>1.15548202944915</v>
       </c>
       <c r="U15">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.903661626038719</v>
+        <v>5.102336682710638</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2670,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08869711150910053</v>
+        <v>0.08844064752112402</v>
       </c>
       <c r="C16">
-        <v>26532.97527327773</v>
+        <v>26699.50863152076</v>
       </c>
       <c r="D16">
-        <v>31127.03327327774</v>
+        <v>31293.56663152076</v>
       </c>
       <c r="E16">
         <v>-4625.241999999999</v>
@@ -2593,37 +2703,37 @@
         <v>1181.9</v>
       </c>
       <c r="M16">
-        <v>259.564277</v>
+        <v>249.4573494</v>
       </c>
       <c r="N16">
-        <v>922.3357230000001</v>
+        <v>932.4426506000001</v>
       </c>
       <c r="O16">
-        <v>237.962616534</v>
+        <v>240.5702038548</v>
       </c>
       <c r="P16">
-        <v>684.3731064660001</v>
+        <v>691.8724467452</v>
       </c>
       <c r="Q16">
-        <v>1439.473106466</v>
+        <v>1446.9724467452</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09631150175476808</v>
+        <v>0.09627902735014419</v>
       </c>
       <c r="T16">
         <v>1.165797398386702</v>
       </c>
       <c r="U16">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.553400081321669</v>
+        <v>4.737884062517022</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2752,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08869788674451005</v>
+        <v>0.08826935351086911</v>
       </c>
       <c r="C17">
-        <v>26204.26575656146</v>
+        <v>26497.579717749</v>
       </c>
       <c r="D17">
-        <v>31126.47075656146</v>
+        <v>31419.784717749</v>
       </c>
       <c r="E17">
         <v>-4297.095</v>
@@ -2675,45 +2785,45 @@
         <v>1181.9</v>
       </c>
       <c r="M17">
-        <v>284.9956695</v>
+        <v>267.2757314999999</v>
       </c>
       <c r="N17">
-        <v>896.9043305000001</v>
+        <v>914.6242685000002</v>
       </c>
       <c r="O17">
-        <v>231.401317269</v>
+        <v>235.9730612730001</v>
       </c>
       <c r="P17">
-        <v>665.5030132310001</v>
+        <v>678.6512072270001</v>
       </c>
       <c r="Q17">
-        <v>1420.603013231</v>
+        <v>1433.751207227</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09676896087589418</v>
+        <v>0.09673619236572836</v>
       </c>
       <c r="T17">
         <v>1.176355481887491</v>
       </c>
       <c r="U17">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.147080557657387</v>
+        <v>4.422025125015888</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2834,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08855322997991955</v>
+        <v>0.08821677950061418</v>
       </c>
       <c r="C18">
-        <v>25981.43605200043</v>
+        <v>26208.37636465963</v>
       </c>
       <c r="D18">
-        <v>31231.78805200043</v>
+        <v>31458.72836465963</v>
       </c>
       <c r="E18">
         <v>-3968.947999999999</v>
@@ -2757,37 +2867,37 @@
         <v>1181.9</v>
       </c>
       <c r="M18">
-        <v>303.9953808</v>
+        <v>290.3444656</v>
       </c>
       <c r="N18">
-        <v>877.9046192000001</v>
+        <v>891.5555344000002</v>
       </c>
       <c r="O18">
-        <v>226.4993917536</v>
+        <v>230.0213278752001</v>
       </c>
       <c r="P18">
-        <v>651.4052274464</v>
+        <v>661.5342065248001</v>
       </c>
       <c r="Q18">
-        <v>1406.5052274464</v>
+        <v>1416.6342065248</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09723731188085662</v>
+        <v>0.09720424226263594</v>
       </c>
       <c r="T18">
         <v>1.187164948328775</v>
       </c>
       <c r="U18">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.8878880228038</v>
+        <v>4.070682034725859</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2916,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08840857321532906</v>
+        <v>0.08805290549035928</v>
       </c>
       <c r="C19">
-        <v>25759.3214551308</v>
+        <v>26002.23915108279</v>
       </c>
       <c r="D19">
-        <v>31337.8204551308</v>
+        <v>31580.73815108279</v>
       </c>
       <c r="E19">
         <v>-3640.800999999999</v>
@@ -2839,37 +2949,37 @@
         <v>1181.9</v>
       </c>
       <c r="M19">
-        <v>322.9950921</v>
+        <v>308.4909947</v>
       </c>
       <c r="N19">
-        <v>858.9049079000001</v>
+        <v>873.4090053000001</v>
       </c>
       <c r="O19">
-        <v>221.5974662382</v>
+        <v>225.3395233674</v>
       </c>
       <c r="P19">
-        <v>637.3074416618001</v>
+        <v>648.0694819326001</v>
       </c>
       <c r="Q19">
-        <v>1392.4074416618</v>
+        <v>1403.1694819326</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.0977169484522037</v>
+        <v>0.0976835704703124</v>
       </c>
       <c r="T19">
         <v>1.198234883840933</v>
       </c>
       <c r="U19">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2987,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.659188727344753</v>
+        <v>3.83123015033022</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2998,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08826391645073858</v>
+        <v>0.08788903148010439</v>
       </c>
       <c r="C20">
-        <v>25537.92927416912</v>
+        <v>25797.05202983585</v>
       </c>
       <c r="D20">
-        <v>31444.57527416911</v>
+        <v>31703.69802983585</v>
       </c>
       <c r="E20">
         <v>-3312.654</v>
@@ -2921,37 +3031,37 @@
         <v>1181.9</v>
       </c>
       <c r="M20">
-        <v>341.9948033999999</v>
+        <v>326.6375237999999</v>
       </c>
       <c r="N20">
-        <v>839.9051966000002</v>
+        <v>855.2624762000002</v>
       </c>
       <c r="O20">
-        <v>216.6955407228</v>
+        <v>220.6577188596</v>
       </c>
       <c r="P20">
-        <v>623.2096558772001</v>
+        <v>634.6047573404001</v>
       </c>
       <c r="Q20">
-        <v>1378.3096558772</v>
+        <v>1389.7047573404</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09820828347651046</v>
+        <v>0.09817458960988339</v>
       </c>
       <c r="T20">
         <v>1.209574817780217</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.455900464714489</v>
+        <v>3.618384030867431</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3080,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0881192596861481</v>
+        <v>0.08772515746984949</v>
       </c>
       <c r="C21">
-        <v>25317.26691725639</v>
+        <v>25592.82614187451</v>
       </c>
       <c r="D21">
-        <v>31552.05991725639</v>
+        <v>31827.61914187451</v>
       </c>
       <c r="E21">
         <v>-2984.507</v>
@@ -3003,37 +3113,37 @@
         <v>1181.9</v>
       </c>
       <c r="M21">
-        <v>360.9945147</v>
+        <v>344.7840529</v>
       </c>
       <c r="N21">
-        <v>820.9054853000001</v>
+        <v>837.1159471000001</v>
       </c>
       <c r="O21">
-        <v>211.7936152074001</v>
+        <v>215.9759143518</v>
       </c>
       <c r="P21">
-        <v>609.1118700926</v>
+        <v>621.1400327482</v>
       </c>
       <c r="Q21">
-        <v>1364.2118700926</v>
+        <v>1376.2400327482</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09871175022981246</v>
+        <v>0.09867773267882651</v>
       </c>
       <c r="T21">
         <v>1.221194750088372</v>
       </c>
       <c r="U21">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3151,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.274010966571621</v>
+        <v>3.427942766084934</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3162,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08797460292155759</v>
+        <v>0.08756128345959456</v>
       </c>
       <c r="C22">
-        <v>25097.34189417187</v>
+        <v>25389.5728030258</v>
       </c>
       <c r="D22">
-        <v>31660.28189417187</v>
+        <v>31952.5128030258</v>
       </c>
       <c r="E22">
         <v>-2656.36</v>
@@ -3085,37 +3195,37 @@
         <v>1181.9</v>
       </c>
       <c r="M22">
-        <v>379.994226</v>
+        <v>362.930582</v>
       </c>
       <c r="N22">
-        <v>801.9057740000001</v>
+        <v>818.9694180000001</v>
       </c>
       <c r="O22">
-        <v>206.891689692</v>
+        <v>211.294109844</v>
       </c>
       <c r="P22">
-        <v>595.0140843080001</v>
+        <v>607.675308156</v>
       </c>
       <c r="Q22">
-        <v>1350.114084308</v>
+        <v>1362.775308156</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.099227803651947</v>
+        <v>0.0991934543244932</v>
       </c>
       <c r="T22">
         <v>1.233105180704231</v>
       </c>
       <c r="U22">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.110310418243039</v>
+        <v>3.256545627780687</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3244,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08823507815696711</v>
+        <v>0.08739740944933964</v>
       </c>
       <c r="C23">
-        <v>24574.85757378302</v>
+        <v>25187.30350743262</v>
       </c>
       <c r="D23">
-        <v>31465.94457378302</v>
+        <v>32078.39050743262</v>
       </c>
       <c r="E23">
         <v>-2328.213</v>
@@ -3167,45 +3277,45 @@
         <v>1181.9</v>
       </c>
       <c r="M23">
-        <v>416.9107635</v>
+        <v>381.0771111</v>
       </c>
       <c r="N23">
-        <v>764.9892365000001</v>
+        <v>800.8228889000002</v>
       </c>
       <c r="O23">
-        <v>197.367223017</v>
+        <v>206.6123053362001</v>
       </c>
       <c r="P23">
-        <v>567.622013483</v>
+        <v>594.2105835638001</v>
       </c>
       <c r="Q23">
-        <v>1322.722013483</v>
+        <v>1349.3105835638</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09975692171767989</v>
+        <v>0.09972223221435399</v>
       </c>
       <c r="T23">
         <v>1.245317141209099</v>
       </c>
       <c r="U23">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.834899224183738</v>
+        <v>3.101472026457798</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3326,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08810971339237664</v>
+        <v>0.08764163543908476</v>
       </c>
       <c r="C24">
-        <v>24339.94497358919</v>
+        <v>24671.91772986347</v>
       </c>
       <c r="D24">
-        <v>31559.17897358919</v>
+        <v>31891.15172986347</v>
       </c>
       <c r="E24">
         <v>-2000.066</v>
@@ -3249,37 +3359,37 @@
         <v>1181.9</v>
       </c>
       <c r="M24">
-        <v>436.763657</v>
+        <v>417.2717252</v>
       </c>
       <c r="N24">
-        <v>745.1363430000001</v>
+        <v>764.6282748000001</v>
       </c>
       <c r="O24">
-        <v>192.245176494</v>
+        <v>197.2740948984</v>
       </c>
       <c r="P24">
-        <v>552.8911665060001</v>
+        <v>567.3541799016001</v>
       </c>
       <c r="Q24">
-        <v>1307.991166506</v>
+        <v>1322.4541799016</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1002996069133034</v>
+        <v>0.1002645685116471</v>
       </c>
       <c r="T24">
         <v>1.2578422289064</v>
       </c>
       <c r="U24">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.706040168539023</v>
+        <v>2.832446889214721</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3408,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08798434862778615</v>
+        <v>0.08749631142882985</v>
       </c>
       <c r="C25">
-        <v>24105.58652719713</v>
+        <v>24454.92085087459</v>
       </c>
       <c r="D25">
-        <v>31652.96752719713</v>
+        <v>32002.30185087458</v>
       </c>
       <c r="E25">
         <v>-1671.919</v>
@@ -3331,37 +3441,37 @@
         <v>1181.9</v>
       </c>
       <c r="M25">
-        <v>456.6165505</v>
+        <v>436.2386218</v>
       </c>
       <c r="N25">
-        <v>725.2834495000002</v>
+        <v>745.6613782000002</v>
       </c>
       <c r="O25">
-        <v>187.1231299710001</v>
+        <v>192.3806355756001</v>
       </c>
       <c r="P25">
-        <v>538.1603195290002</v>
+        <v>553.2807426244001</v>
       </c>
       <c r="Q25">
-        <v>1293.260319529</v>
+        <v>1308.3807426244</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1008563878282937</v>
+        <v>0.1008209914660128</v>
       </c>
       <c r="T25">
         <v>1.270692643556877</v>
       </c>
       <c r="U25">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.588386248167762</v>
+        <v>2.709297024466256</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3490,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08833979986319566</v>
+        <v>0.08735098741857494</v>
       </c>
       <c r="C26">
-        <v>23512.95576262602</v>
+        <v>24238.70146394205</v>
       </c>
       <c r="D26">
-        <v>31388.48376262602</v>
+        <v>32114.22946394205</v>
       </c>
       <c r="E26">
         <v>-1343.772</v>
@@ -3413,45 +3523,45 @@
         <v>1181.9</v>
       </c>
       <c r="M26">
-        <v>497.7333696</v>
+        <v>455.2055184</v>
       </c>
       <c r="N26">
-        <v>684.1666304</v>
+        <v>726.6944816</v>
       </c>
       <c r="O26">
-        <v>176.5149906432</v>
+        <v>187.4871762528</v>
       </c>
       <c r="P26">
-        <v>507.6516397568</v>
+        <v>539.2073053472</v>
       </c>
       <c r="Q26">
-        <v>1262.7516397568</v>
+        <v>1294.3073053472</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1014278208726259</v>
+        <v>0.1013920571297039</v>
       </c>
       <c r="T26">
         <v>1.283881227013946</v>
       </c>
       <c r="U26">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.374564520256751</v>
+        <v>2.596409648446828</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3572,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08823446909860518</v>
+        <v>0.08785491340832002</v>
       </c>
       <c r="C27">
-        <v>23262.72120183602</v>
+        <v>23525.74342627823</v>
       </c>
       <c r="D27">
-        <v>31466.39620183601</v>
+        <v>31729.41842627823</v>
       </c>
       <c r="E27">
         <v>-1015.625</v>
@@ -3495,37 +3605,37 @@
         <v>1181.9</v>
       </c>
       <c r="M27">
-        <v>518.47226</v>
+        <v>502.8852775</v>
       </c>
       <c r="N27">
-        <v>663.4277400000001</v>
+        <v>679.0147225000001</v>
       </c>
       <c r="O27">
-        <v>171.16435692</v>
+        <v>175.185798405</v>
       </c>
       <c r="P27">
-        <v>492.26338308</v>
+        <v>503.828924095</v>
       </c>
       <c r="Q27">
-        <v>1247.36338308</v>
+        <v>1258.928924095</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1020144921314736</v>
+        <v>0.1019783512110934</v>
       </c>
       <c r="T27">
         <v>1.29742150602987</v>
       </c>
       <c r="U27">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0468944</v>
+        <v>0.0454846</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3643,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.279581939446481</v>
+        <v>2.350237823377122</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3654,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08903586233401467</v>
+        <v>0.08773555939806513</v>
       </c>
       <c r="C28">
-        <v>22351.33252010303</v>
+        <v>23287.90244309523</v>
       </c>
       <c r="D28">
-        <v>30883.15452010303</v>
+        <v>31819.72444309523</v>
       </c>
       <c r="E28">
         <v>-687.4779999999992</v>
@@ -3577,45 +3687,45 @@
         <v>1181.9</v>
       </c>
       <c r="M28">
-        <v>579.3107138</v>
+        <v>523.0006886</v>
       </c>
       <c r="N28">
-        <v>602.5892862000001</v>
+        <v>658.8993114000001</v>
       </c>
       <c r="O28">
-        <v>155.4680358396</v>
+        <v>169.9960223412</v>
       </c>
       <c r="P28">
-        <v>447.1212503604</v>
+        <v>488.9032890588001</v>
       </c>
       <c r="Q28">
-        <v>1202.2212503604</v>
+        <v>1244.0032890588</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1026170193702901</v>
+        <v>0.1025804910784664</v>
       </c>
       <c r="T28">
         <v>1.311327738532711</v>
       </c>
       <c r="U28">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.040183224382825</v>
+        <v>2.259844060939541</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3736,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09177016556942419</v>
+        <v>0.08817715738781022</v>
       </c>
       <c r="C29">
-        <v>20186.2569757313</v>
+        <v>22628.17288271435</v>
       </c>
       <c r="D29">
-        <v>29046.2259757313</v>
+        <v>31488.14188271435</v>
       </c>
       <c r="E29">
         <v>-359.3310000000001</v>
@@ -3659,45 +3769,45 @@
         <v>1181.9</v>
       </c>
       <c r="M29">
-        <v>725.6314610999999</v>
+        <v>567.9240129</v>
       </c>
       <c r="N29">
-        <v>456.2685389000002</v>
+        <v>613.9759871000001</v>
       </c>
       <c r="O29">
-        <v>117.7172830362</v>
+        <v>158.4058046718</v>
       </c>
       <c r="P29">
-        <v>338.5512558638001</v>
+        <v>455.5701824282</v>
       </c>
       <c r="Q29">
-        <v>1093.6512558638</v>
+        <v>1210.6701824282</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1032360542046907</v>
+        <v>0.1031991279285071</v>
       </c>
       <c r="T29">
         <v>1.325614963706863</v>
       </c>
       <c r="U29">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.62878825321098</v>
+        <v>2.081088267363171</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3818,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09180358880483369</v>
+        <v>0.08807857937755531</v>
       </c>
       <c r="C30">
-        <v>19837.00686456614</v>
+        <v>22373.44458360547</v>
       </c>
       <c r="D30">
-        <v>29025.12286456615</v>
+        <v>31561.56058360547</v>
       </c>
       <c r="E30">
         <v>-31.18399999999929</v>
@@ -3741,45 +3851,45 @@
         <v>1181.9</v>
       </c>
       <c r="M30">
-        <v>752.5067004</v>
+        <v>588.9582356000001</v>
       </c>
       <c r="N30">
-        <v>429.3932996000001</v>
+        <v>592.9417644</v>
       </c>
       <c r="O30">
-        <v>110.7834712968</v>
+        <v>152.9789752152</v>
       </c>
       <c r="P30">
-        <v>318.6098283032001</v>
+        <v>439.9627891848</v>
       </c>
       <c r="Q30">
-        <v>1073.7098283032</v>
+        <v>1195.0627891848</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1038722844511579</v>
+        <v>0.1038349491354935</v>
       </c>
       <c r="T30">
         <v>1.340299056246963</v>
       </c>
       <c r="U30">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.570617244167731</v>
+        <v>2.006763686385915</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3900,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09183701204024321</v>
+        <v>0.09049760736730039</v>
       </c>
       <c r="C31">
-        <v>19487.78739545272</v>
+        <v>20337.19052936455</v>
       </c>
       <c r="D31">
-        <v>29004.05039545272</v>
+        <v>29853.45352936455</v>
       </c>
       <c r="E31">
         <v>296.9629999999997</v>
@@ -3823,37 +3933,37 @@
         <v>1181.9</v>
       </c>
       <c r="M31">
-        <v>779.3819397</v>
+        <v>721.3327353999999</v>
       </c>
       <c r="N31">
-        <v>402.5180603000001</v>
+        <v>460.5672646000002</v>
       </c>
       <c r="O31">
-        <v>103.8496595574</v>
+        <v>118.8263542668</v>
       </c>
       <c r="P31">
-        <v>298.6684007426001</v>
+        <v>341.7409103332001</v>
       </c>
       <c r="Q31">
-        <v>1053.7684007426</v>
+        <v>1096.8409103332</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1045264366763989</v>
+        <v>0.1044886807990146</v>
       </c>
       <c r="T31">
         <v>1.355396785196643</v>
       </c>
       <c r="U31">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.516458028851602</v>
+        <v>1.638494888693222</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3982,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1039059271843251</v>
+        <v>0.0904858433570455</v>
       </c>
       <c r="C32">
-        <v>13135.34235874873</v>
+        <v>20016.90275965047</v>
       </c>
       <c r="D32">
-        <v>22979.75235874873</v>
+        <v>29861.31275965046</v>
       </c>
       <c r="E32">
         <v>625.1099999999988</v>
@@ -3905,45 +4015,45 @@
         <v>1181.9</v>
       </c>
       <c r="M32">
-        <v>1288.633269</v>
+        <v>746.2062779999999</v>
       </c>
       <c r="N32">
-        <v>-106.7332689999996</v>
+        <v>435.6937220000002</v>
       </c>
       <c r="O32">
-        <v>-27.5371834019999</v>
+        <v>112.4089802760001</v>
       </c>
       <c r="P32">
-        <v>-79.19608559799971</v>
+        <v>323.2847417240001</v>
       </c>
       <c r="Q32">
-        <v>675.9039144020002</v>
+        <v>1078.384741724</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1056120214318354</v>
+        <v>0.105161090510065</v>
       </c>
       <c r="T32">
-        <v>1.380451908082525</v>
+        <v>1.3709258778306</v>
       </c>
       <c r="U32">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
-        <v>0.2366307058303956</v>
+        <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.09992504060680121</v>
+        <v>0.0562436</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.9171732784123862</v>
+        <v>1.583878392403448</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4064,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1047569271843251</v>
+        <v>0.09047407934679058</v>
       </c>
       <c r="C33">
-        <v>12475.49948870864</v>
+        <v>19696.61912907333</v>
       </c>
       <c r="D33">
-        <v>22648.05648870864</v>
+        <v>29869.17612907332</v>
       </c>
       <c r="E33">
         <v>953.2569999999996</v>
@@ -3987,45 +4097,45 @@
         <v>1181.9</v>
       </c>
       <c r="M33">
-        <v>1331.5877113</v>
+        <v>771.0798205999999</v>
       </c>
       <c r="N33">
-        <v>-149.6877112999996</v>
+        <v>410.8201794000001</v>
       </c>
       <c r="O33">
-        <v>-38.61942951539989</v>
+        <v>105.9916062852</v>
       </c>
       <c r="P33">
-        <v>-111.0682817845997</v>
+        <v>304.8285731148001</v>
       </c>
       <c r="Q33">
-        <v>644.0317182154002</v>
+        <v>1059.9285731148</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1064788623221519</v>
+        <v>0.1058529903576675</v>
       </c>
       <c r="T33">
-        <v>1.400458457475025</v>
+        <v>1.386905089091629</v>
       </c>
       <c r="U33">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
-        <v>0.2289974572552216</v>
+        <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.1009242328452915</v>
+        <v>0.0562436</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.8875870436248898</v>
+        <v>1.532785541035595</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4146,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1056079271843251</v>
+        <v>0.09383396333653567</v>
       </c>
       <c r="C34">
-        <v>11825.0959421393</v>
+        <v>17279.18030945335</v>
       </c>
       <c r="D34">
-        <v>22325.7999421393</v>
+        <v>27779.88430945335</v>
       </c>
       <c r="E34">
         <v>1281.404</v>
@@ -4069,45 +4179,45 @@
         <v>1181.9</v>
       </c>
       <c r="M34">
-        <v>1374.5421536</v>
+        <v>945.06336</v>
       </c>
       <c r="N34">
-        <v>-192.6421535999998</v>
+        <v>236.8366400000001</v>
       </c>
       <c r="O34">
-        <v>-49.70167562879995</v>
+        <v>61.10385312000003</v>
       </c>
       <c r="P34">
-        <v>-142.9404779711999</v>
+        <v>175.7327868800001</v>
       </c>
       <c r="Q34">
-        <v>612.1595220288</v>
+        <v>930.83278688</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1073711985327717</v>
+        <v>0.1065652402007878</v>
       </c>
       <c r="T34">
-        <v>1.421053434790834</v>
+        <v>1.403354277154452</v>
       </c>
       <c r="U34">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
-        <v>0.2218412867159959</v>
+        <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.1018609755688761</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.8598499485116119</v>
+        <v>1.250603980668556</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4228,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1064589271843251</v>
+        <v>0.102041421186614</v>
       </c>
       <c r="C35">
-        <v>11183.73443880615</v>
+        <v>12897.04205639878</v>
       </c>
       <c r="D35">
-        <v>22012.58543880615</v>
+        <v>23725.89305639877</v>
       </c>
       <c r="E35">
         <v>1609.550999999999</v>
@@ -4151,37 +4261,37 @@
         <v>1181.9</v>
       </c>
       <c r="M35">
-        <v>1417.4965959</v>
+        <v>1284.3017286</v>
       </c>
       <c r="N35">
-        <v>-235.5965958999996</v>
+        <v>-102.4017285999998</v>
       </c>
       <c r="O35">
-        <v>-60.78392174219989</v>
+        <v>-26.41964597879996</v>
       </c>
       <c r="P35">
-        <v>-174.8126741577997</v>
+        <v>-75.98208262119988</v>
       </c>
       <c r="Q35">
-        <v>580.2873258422003</v>
+        <v>679.1179173788</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1082901716452012</v>
+        <v>0.1077550880665278</v>
       </c>
       <c r="T35">
-        <v>1.442263187548906</v>
+        <v>1.430833442644985</v>
       </c>
       <c r="U35">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.2151188234821779</v>
+        <v>0.237428785782606</v>
       </c>
       <c r="W35">
-        <v>0.1027409460061829</v>
+        <v>0.09044094600618292</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4299,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8337938894658057</v>
+        <v>0.9202666115604885</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4310,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1073099271843251</v>
+        <v>0.102769421186614</v>
       </c>
       <c r="C36">
-        <v>10551.03968422519</v>
+        <v>12265.70696381699</v>
       </c>
       <c r="D36">
-        <v>21708.03768422519</v>
+        <v>23422.70496381698</v>
       </c>
       <c r="E36">
         <v>1937.698</v>
@@ -4233,37 +4343,37 @@
         <v>1181.9</v>
       </c>
       <c r="M36">
-        <v>1460.4510382</v>
+        <v>1323.2199628</v>
       </c>
       <c r="N36">
-        <v>-278.5510381999998</v>
+        <v>-141.3199628</v>
       </c>
       <c r="O36">
-        <v>-71.86616785559994</v>
+        <v>-36.4605504024</v>
       </c>
       <c r="P36">
-        <v>-206.6848703443998</v>
+        <v>-104.8594123976</v>
       </c>
       <c r="Q36">
-        <v>548.4151296556001</v>
+        <v>650.2405876024</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1092369924277042</v>
+        <v>0.1086938015220813</v>
       </c>
       <c r="T36">
-        <v>1.464115660087526</v>
+        <v>1.452512737230515</v>
       </c>
       <c r="U36">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.2087917992621138</v>
+        <v>0.2304455862007647</v>
       </c>
       <c r="W36">
-        <v>0.1035691534765893</v>
+        <v>0.09126915347658933</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4381,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8092705397756348</v>
+        <v>0.8931999465145917</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4392,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1391346043883145</v>
+        <v>0.103497421186614</v>
       </c>
       <c r="C37">
-        <v>2821.015357373857</v>
+        <v>11642.02285205409</v>
       </c>
       <c r="D37">
-        <v>14306.16035737386</v>
+        <v>23127.1678520541</v>
       </c>
       <c r="E37">
         <v>2265.845000000001</v>
@@ -4315,45 +4425,45 @@
         <v>1181.9</v>
       </c>
       <c r="M37">
-        <v>2478.494291</v>
+        <v>1362.138197</v>
       </c>
       <c r="N37">
-        <v>-1296.594291</v>
+        <v>-180.2381970000001</v>
       </c>
       <c r="O37">
-        <v>-334.5213270780001</v>
+        <v>-46.50145482600004</v>
       </c>
       <c r="P37">
-        <v>-962.0729639220003</v>
+        <v>-133.7367421740001</v>
       </c>
       <c r="Q37">
-        <v>-206.9729639220004</v>
+        <v>621.3632578259999</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1121493726250372</v>
+        <v>0.1096613984685749</v>
       </c>
       <c r="T37">
-        <v>1.531332930198551</v>
+        <v>1.474859087034061</v>
       </c>
       <c r="U37">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.1230304225865171</v>
+        <v>0.2238614265950285</v>
       </c>
       <c r="W37">
-        <v>0.1892500348058296</v>
+        <v>0.09205003480582963</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.4768621030485157</v>
+        <v>0.8676799480427462</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4474,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1408346043883145</v>
+        <v>0.104225421186614</v>
       </c>
       <c r="C38">
-        <v>2236.956600134768</v>
+        <v>11025.70371988379</v>
       </c>
       <c r="D38">
-        <v>14050.24860013477</v>
+        <v>22838.99571988378</v>
       </c>
       <c r="E38">
         <v>2593.991999999998</v>
@@ -4397,45 +4507,45 @@
         <v>1181.9</v>
       </c>
       <c r="M38">
-        <v>2549.3084136</v>
+        <v>1401.0564312</v>
       </c>
       <c r="N38">
-        <v>-1367.4084136</v>
+        <v>-219.1564311999998</v>
       </c>
       <c r="O38">
-        <v>-352.7913707087999</v>
+        <v>-56.54235924959995</v>
       </c>
       <c r="P38">
-        <v>-1014.6170428912</v>
+        <v>-162.6140719503999</v>
       </c>
       <c r="Q38">
-        <v>-259.5170428911998</v>
+        <v>592.4859280496</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1131860815723034</v>
+        <v>0.1106592328196463</v>
       </c>
       <c r="T38">
-        <v>1.555260007232903</v>
+        <v>1.497903760268968</v>
       </c>
       <c r="U38">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.1196129108480027</v>
+        <v>0.2176430536340555</v>
       </c>
       <c r="W38">
-        <v>0.189987533839001</v>
+        <v>0.09278753383900101</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.4636159335193903</v>
+        <v>0.8435777272637812</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4556,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1425346043883146</v>
+        <v>0.104953421186614</v>
       </c>
       <c r="C39">
-        <v>1661.892555595587</v>
+        <v>10416.47764532574</v>
       </c>
       <c r="D39">
-        <v>13803.33155559559</v>
+        <v>22557.91664532574</v>
       </c>
       <c r="E39">
         <v>2922.138999999999</v>
@@ -4479,45 +4589,45 @@
         <v>1181.9</v>
       </c>
       <c r="M39">
-        <v>2620.1225362</v>
+        <v>1439.9746654</v>
       </c>
       <c r="N39">
-        <v>-1438.2225362</v>
+        <v>-258.0746654</v>
       </c>
       <c r="O39">
-        <v>-371.0614143396</v>
+        <v>-66.58326367319999</v>
       </c>
       <c r="P39">
-        <v>-1067.1611218604</v>
+        <v>-191.4914017267999</v>
       </c>
       <c r="Q39">
-        <v>-312.0611218603999</v>
+        <v>563.6085982732</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1142557019147209</v>
+        <v>0.1116887444517042</v>
       </c>
       <c r="T39">
-        <v>1.579946674014378</v>
+        <v>1.521680010431968</v>
       </c>
       <c r="U39">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.1163801294737324</v>
+        <v>0.2117608089412432</v>
       </c>
       <c r="W39">
-        <v>0.1906851680595686</v>
+        <v>0.09348516805956857</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.4510857731540014</v>
+        <v>0.8207783292296248</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4638,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1442346043883146</v>
+        <v>0.1383620021281568</v>
       </c>
       <c r="C40">
-        <v>1095.357198266056</v>
+        <v>1946.458529438451</v>
       </c>
       <c r="D40">
-        <v>13564.94319826606</v>
+        <v>14416.04452943845</v>
       </c>
       <c r="E40">
         <v>3250.286</v>
@@ -4561,37 +4671,37 @@
         <v>1181.9</v>
       </c>
       <c r="M40">
-        <v>2690.9366588</v>
+        <v>2503.8928688</v>
       </c>
       <c r="N40">
-        <v>-1509.0366588</v>
+        <v>-1321.9928688</v>
       </c>
       <c r="O40">
-        <v>-389.3314579704</v>
+        <v>-341.0741601504</v>
       </c>
       <c r="P40">
-        <v>-1119.7052008296</v>
+        <v>-980.9187086495999</v>
       </c>
       <c r="Q40">
-        <v>-364.6052008296001</v>
+        <v>-225.8187086496</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1153598261391519</v>
+        <v>0.1150814353969619</v>
       </c>
       <c r="T40">
-        <v>1.605429684885578</v>
+        <v>1.600033150045311</v>
       </c>
       <c r="U40">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1133174944875815</v>
+        <v>0.1217824467650403</v>
       </c>
       <c r="W40">
-        <v>0.1913460846895799</v>
+        <v>0.1763460846895799</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4392150949131066</v>
+        <v>0.4720249874613964</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4720,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1459346043883145</v>
+        <v>0.1399120021281568</v>
       </c>
       <c r="C41">
-        <v>536.916149790808</v>
+        <v>1380.883055754488</v>
       </c>
       <c r="D41">
-        <v>13334.64914979081</v>
+        <v>14178.61605575449</v>
       </c>
       <c r="E41">
         <v>3578.433000000001</v>
@@ -4643,37 +4753,37 @@
         <v>1181.9</v>
       </c>
       <c r="M41">
-        <v>2761.750781400001</v>
+        <v>2569.7847864</v>
       </c>
       <c r="N41">
-        <v>-1579.8507814</v>
+        <v>-1387.8847864</v>
       </c>
       <c r="O41">
-        <v>-407.6015016012001</v>
+        <v>-358.0742748912</v>
       </c>
       <c r="P41">
-        <v>-1172.2492797988</v>
+        <v>-1029.8105115088</v>
       </c>
       <c r="Q41">
-        <v>-417.1492797988003</v>
+        <v>-274.7105115088</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1165001511578265</v>
+        <v>0.1162171966329777</v>
       </c>
       <c r="T41">
-        <v>1.631748204309931</v>
+        <v>1.626263201685398</v>
       </c>
       <c r="U41">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1104119177058486</v>
+        <v>0.1186598199249111</v>
       </c>
       <c r="W41">
-        <v>0.1919731081590779</v>
+        <v>0.1769731081590779</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.427953169402514</v>
+        <v>0.459921782654694</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4802,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1476346043883145</v>
+        <v>0.1414620021281568</v>
       </c>
       <c r="C42">
-        <v>-13.8359625951889</v>
+        <v>823.0016324985645</v>
       </c>
       <c r="D42">
-        <v>13112.04403740481</v>
+        <v>13948.88163249856</v>
       </c>
       <c r="E42">
         <v>3906.58</v>
@@ -4725,37 +4835,37 @@
         <v>1181.9</v>
       </c>
       <c r="M42">
-        <v>2832.564904</v>
+        <v>2635.676704</v>
       </c>
       <c r="N42">
-        <v>-1650.664904</v>
+        <v>-1453.776704</v>
       </c>
       <c r="O42">
-        <v>-425.8715452320001</v>
+        <v>-375.074389632</v>
       </c>
       <c r="P42">
-        <v>-1224.793358768</v>
+        <v>-1078.702314368</v>
       </c>
       <c r="Q42">
-        <v>-469.6933587680003</v>
+        <v>-323.602314368</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.117678487010457</v>
+        <v>0.1173908165768607</v>
       </c>
       <c r="T42">
-        <v>1.658944007715097</v>
+        <v>1.653367588380155</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1076516197632024</v>
+        <v>0.1156933244267883</v>
       </c>
       <c r="W42">
-        <v>0.1925687804551009</v>
+        <v>0.1775687804551009</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4172543401674512</v>
+        <v>0.4484237380883267</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4884,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1493346043883146</v>
+        <v>0.1430120021281568</v>
       </c>
       <c r="C43">
-        <v>-557.277887372089</v>
+        <v>272.4462255420876</v>
       </c>
       <c r="D43">
-        <v>12896.74911262791</v>
+        <v>13726.47322554209</v>
       </c>
       <c r="E43">
         <v>4234.727000000001</v>
@@ -4807,37 +4917,37 @@
         <v>1181.9</v>
       </c>
       <c r="M43">
-        <v>2903.3790266</v>
+        <v>2701.5686216</v>
       </c>
       <c r="N43">
-        <v>-1721.4790266</v>
+        <v>-1519.6686216</v>
       </c>
       <c r="O43">
-        <v>-444.1415888628</v>
+        <v>-392.0745043728</v>
       </c>
       <c r="P43">
-        <v>-1277.3374377372</v>
+        <v>-1127.5941172272</v>
       </c>
       <c r="Q43">
-        <v>-522.2374377372</v>
+        <v>-372.4941172271999</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1188967664513122</v>
+        <v>0.1186042202476549</v>
       </c>
       <c r="T43">
-        <v>1.687061702761115</v>
+        <v>1.681390767844225</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1050259705006853</v>
+        <v>0.1128715360261349</v>
       </c>
       <c r="W43">
-        <v>0.1931353955659521</v>
+        <v>0.1781353955659521</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4955,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4070774050414159</v>
+        <v>0.437486573744709</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4966,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1510346043883146</v>
+        <v>0.1445620021281568</v>
       </c>
       <c r="C44">
-        <v>-1093.763899229507</v>
+        <v>-271.1280950987148</v>
       </c>
       <c r="D44">
-        <v>12688.41010077049</v>
+        <v>13511.04590490128</v>
       </c>
       <c r="E44">
         <v>4562.874</v>
@@ -4889,37 +4999,37 @@
         <v>1181.9</v>
       </c>
       <c r="M44">
-        <v>2974.1931492</v>
+        <v>2767.4605392</v>
       </c>
       <c r="N44">
-        <v>-1792.2931492</v>
+        <v>-1585.5605392</v>
       </c>
       <c r="O44">
-        <v>-462.4116324935999</v>
+        <v>-409.0746191136</v>
       </c>
       <c r="P44">
-        <v>-1329.8815167064</v>
+        <v>-1176.4859200864</v>
       </c>
       <c r="Q44">
-        <v>-574.7815167064</v>
+        <v>-421.3859200863999</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1201570555280589</v>
+        <v>0.1198594654243386</v>
       </c>
       <c r="T44">
-        <v>1.716148973498376</v>
+        <v>1.710380263841539</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1025253521554309</v>
+        <v>0.1101841185017031</v>
       </c>
       <c r="W44">
-        <v>0.193675029004858</v>
+        <v>0.178675029004858</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +5037,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3973850858737632</v>
+        <v>0.4270702267507873</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5048,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1527346043883145</v>
+        <v>0.1461120021281568</v>
       </c>
       <c r="C45">
-        <v>-1623.62574443509</v>
+        <v>-808.0449402648155</v>
       </c>
       <c r="D45">
-        <v>12486.69525556491</v>
+        <v>13302.27605973518</v>
       </c>
       <c r="E45">
         <v>4891.020999999999</v>
@@ -4971,37 +5081,37 @@
         <v>1181.9</v>
       </c>
       <c r="M45">
-        <v>3045.0072718</v>
+        <v>2833.3524568</v>
       </c>
       <c r="N45">
-        <v>-1863.1072718</v>
+        <v>-1651.4524568</v>
       </c>
       <c r="O45">
-        <v>-480.6816761243999</v>
+        <v>-426.0747338543999</v>
       </c>
       <c r="P45">
-        <v>-1382.4255956756</v>
+        <v>-1225.3777229456</v>
       </c>
       <c r="Q45">
-        <v>-627.3255956755997</v>
+        <v>-470.2777229455999</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1214615652741652</v>
+        <v>0.1211587542914323</v>
       </c>
       <c r="T45">
-        <v>1.746256850226418</v>
+        <v>1.740386935137004</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1001410416401883</v>
+        <v>0.1076216971411984</v>
       </c>
       <c r="W45">
-        <v>0.1941895632140474</v>
+        <v>0.1791895632140474</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5119,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3881435722487919</v>
+        <v>0.4171383610123969</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5130,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1544346043883146</v>
+        <v>0.1476620021281568</v>
       </c>
       <c r="C46">
-        <v>-2147.174403547164</v>
+        <v>-1338.608223685684</v>
       </c>
       <c r="D46">
-        <v>12291.29359645284</v>
+        <v>13099.85977631432</v>
       </c>
       <c r="E46">
         <v>5219.168</v>
@@ -5053,37 +5163,37 @@
         <v>1181.9</v>
       </c>
       <c r="M46">
-        <v>3115.8213944</v>
+        <v>2899.2443744</v>
       </c>
       <c r="N46">
-        <v>-1933.9213944</v>
+        <v>-1717.3443744</v>
       </c>
       <c r="O46">
-        <v>-498.9517197552</v>
+        <v>-443.0748485951999</v>
       </c>
       <c r="P46">
-        <v>-1434.9696746448</v>
+        <v>-1274.2695258048</v>
       </c>
       <c r="Q46">
-        <v>-679.8696746447999</v>
+        <v>-519.1695258047998</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.122812664654061</v>
+        <v>0.1225044463323507</v>
       </c>
       <c r="T46">
-        <v>1.777440008266175</v>
+        <v>1.771465273264451</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.09786510887563858</v>
+        <v>0.1051757494788984</v>
       </c>
       <c r="W46">
-        <v>0.1946807095046372</v>
+        <v>0.1796807095046372</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5201,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3793221274249557</v>
+        <v>0.4076579437166606</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5212,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1561346043883146</v>
+        <v>0.1492120021281568</v>
       </c>
       <c r="C47">
-        <v>-2664.701691171444</v>
+        <v>-1863.103638138806</v>
       </c>
       <c r="D47">
-        <v>12101.91330882856</v>
+        <v>12903.51136186119</v>
       </c>
       <c r="E47">
         <v>5547.315000000001</v>
@@ -5135,37 +5245,37 @@
         <v>1181.9</v>
       </c>
       <c r="M47">
-        <v>3186.635517</v>
+        <v>2965.136292</v>
       </c>
       <c r="N47">
-        <v>-2004.735517</v>
+        <v>-1783.236292</v>
       </c>
       <c r="O47">
-        <v>-517.221763386</v>
+        <v>-460.0749633360001</v>
       </c>
       <c r="P47">
-        <v>-1487.513753614</v>
+        <v>-1323.161328664</v>
       </c>
       <c r="Q47">
-        <v>-732.4137536140001</v>
+        <v>-568.061328664</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1242128949204985</v>
+        <v>0.1238990726293026</v>
       </c>
       <c r="T47">
-        <v>1.80975709932556</v>
+        <v>1.803673732778351</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.09569032867840217</v>
+        <v>0.1028385106015896</v>
       </c>
       <c r="W47">
-        <v>0.1951500270712008</v>
+        <v>0.1801500270712008</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3708927468155123</v>
+        <v>0.3985988783007348</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5294,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1578346043883145</v>
+        <v>0.1507620021281568</v>
       </c>
       <c r="C48">
-        <v>-3176.481710070682</v>
+        <v>-2381.800000816402</v>
       </c>
       <c r="D48">
-        <v>11918.28028992932</v>
+        <v>12712.9619991836</v>
       </c>
       <c r="E48">
         <v>5875.462</v>
@@ -5217,37 +5327,37 @@
         <v>1181.9</v>
       </c>
       <c r="M48">
-        <v>3257.4496396</v>
+        <v>3031.0282096</v>
       </c>
       <c r="N48">
-        <v>-2075.5496396</v>
+        <v>-1849.1282096</v>
       </c>
       <c r="O48">
-        <v>-535.4918070168</v>
+        <v>-477.0750780768</v>
       </c>
       <c r="P48">
-        <v>-1540.0578325832</v>
+        <v>-1372.0531315232</v>
       </c>
       <c r="Q48">
-        <v>-784.9578325831999</v>
+        <v>-616.9531315232</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1256649855671744</v>
+        <v>0.1253453517520674</v>
       </c>
       <c r="T48">
-        <v>1.843271119683441</v>
+        <v>1.837075098200172</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.09361010414191517</v>
+        <v>0.1006028908059028</v>
       </c>
       <c r="W48">
-        <v>0.1955989395261747</v>
+        <v>0.1805989395261747</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5365,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3628298610151751</v>
+        <v>0.3899336852941971</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5376,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1595346043883146</v>
+        <v>0.1523120021281568</v>
       </c>
       <c r="C49">
-        <v>-3682.77217486619</v>
+        <v>-2894.95048122254</v>
       </c>
       <c r="D49">
-        <v>11740.13682513381</v>
+        <v>12527.95851877746</v>
       </c>
       <c r="E49">
         <v>6203.609</v>
@@ -5299,37 +5409,37 @@
         <v>1181.9</v>
       </c>
       <c r="M49">
-        <v>3328.2637622</v>
+        <v>3096.9201272</v>
       </c>
       <c r="N49">
-        <v>-2146.3637622</v>
+        <v>-1915.0201272</v>
       </c>
       <c r="O49">
-        <v>-553.7618506476</v>
+        <v>-494.0751928176</v>
       </c>
       <c r="P49">
-        <v>-1592.6019115524</v>
+        <v>-1420.9449343824</v>
       </c>
       <c r="Q49">
-        <v>-837.5019115524001</v>
+        <v>-665.8449343824</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1271718720873098</v>
+        <v>0.1268462074455027</v>
       </c>
       <c r="T49">
-        <v>1.878049820054827</v>
+        <v>1.871736892505835</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.09161839979847015</v>
+        <v>0.09846240376747939</v>
       </c>
       <c r="W49">
-        <v>0.1960287493234902</v>
+        <v>0.1810287493234901</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5447,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3551100767382565</v>
+        <v>0.3816372239049589</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5458,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1612346043883146</v>
+        <v>0.1538620021281568</v>
       </c>
       <c r="C50">
-        <v>-4183.815618774715</v>
+        <v>-3402.793723395396</v>
       </c>
       <c r="D50">
-        <v>11567.24038122528</v>
+        <v>12348.2622766046</v>
       </c>
       <c r="E50">
         <v>6531.755999999999</v>
@@ -5381,37 +5491,37 @@
         <v>1181.9</v>
       </c>
       <c r="M50">
-        <v>3399.0778848</v>
+        <v>3162.8120448</v>
       </c>
       <c r="N50">
-        <v>-2217.1778848</v>
+        <v>-1980.9120448</v>
       </c>
       <c r="O50">
-        <v>-572.0318942784</v>
+        <v>-511.0753075584</v>
       </c>
       <c r="P50">
-        <v>-1645.1459905216</v>
+        <v>-1469.8367372416</v>
       </c>
       <c r="Q50">
-        <v>-890.0459905215998</v>
+        <v>-714.7367372415999</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1287367157812965</v>
+        <v>0.1284047883579162</v>
       </c>
       <c r="T50">
-        <v>1.914166162748189</v>
+        <v>1.907731832746332</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.08970968313600203</v>
+        <v>0.09641110368899024</v>
       </c>
       <c r="W50">
-        <v>0.1964406503792508</v>
+        <v>0.1814406503792508</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5529,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3477119501395428</v>
+        <v>0.3736864484069389</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5540,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1629346043883145</v>
+        <v>0.1554120021281568</v>
       </c>
       <c r="C51">
-        <v>-4679.840495263656</v>
+        <v>-3905.55487291489</v>
       </c>
       <c r="D51">
-        <v>11399.36250473634</v>
+        <v>12173.64812708511</v>
       </c>
       <c r="E51">
         <v>6859.902999999998</v>
@@ -5463,37 +5573,37 @@
         <v>1181.9</v>
       </c>
       <c r="M51">
-        <v>3469.8920074</v>
+        <v>3228.703962399999</v>
       </c>
       <c r="N51">
-        <v>-2287.9920074</v>
+        <v>-2046.803962399999</v>
       </c>
       <c r="O51">
-        <v>-590.3019379092</v>
+        <v>-528.0754222991999</v>
       </c>
       <c r="P51">
-        <v>-1697.6900694908</v>
+        <v>-1518.728540100799</v>
       </c>
       <c r="Q51">
-        <v>-942.5900694907998</v>
+        <v>-763.6285401007995</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1303629258946552</v>
+        <v>0.1300244900904243</v>
       </c>
       <c r="T51">
-        <v>1.951698832605996</v>
+        <v>1.94513833927077</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.08787887327608364</v>
+        <v>0.09444353014431697</v>
       </c>
       <c r="W51">
-        <v>0.1968357391470212</v>
+        <v>0.1818357391470212</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5611,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.340615787891797</v>
+        <v>0.3660601943578178</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5622,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1646346043883146</v>
+        <v>0.1569620021281568</v>
       </c>
       <c r="C52">
-        <v>-5171.062185147153</v>
+        <v>-4403.446517989094</v>
       </c>
       <c r="D52">
-        <v>11236.28781485285</v>
+        <v>12003.9034820109</v>
       </c>
       <c r="E52">
         <v>7188.049999999999</v>
@@ -5545,37 +5655,37 @@
         <v>1181.9</v>
       </c>
       <c r="M52">
-        <v>3540.70613</v>
+        <v>3294.59588</v>
       </c>
       <c r="N52">
-        <v>-2358.80613</v>
+        <v>-2112.69588</v>
       </c>
       <c r="O52">
-        <v>-608.57198154</v>
+        <v>-545.07553704</v>
       </c>
       <c r="P52">
-        <v>-1750.23414846</v>
+        <v>-1567.62034296</v>
       </c>
       <c r="Q52">
-        <v>-995.13414846</v>
+        <v>-812.5203429599999</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1320541844125483</v>
+        <v>0.1317089798922328</v>
       </c>
       <c r="T52">
-        <v>1.990732809258116</v>
+        <v>1.984041106056185</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.08612129581056195</v>
+        <v>0.09255465954143062</v>
       </c>
       <c r="W52">
-        <v>0.1972150243640808</v>
+        <v>0.1822150243640807</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.333803472133961</v>
+        <v>0.3587389904706614</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5704,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1663346043883145</v>
+        <v>0.1585120021281568</v>
       </c>
       <c r="C53">
-        <v>-5657.683918458688</v>
+        <v>-4896.669552890518</v>
       </c>
       <c r="D53">
-        <v>11077.81308154131</v>
+        <v>11838.82744710948</v>
       </c>
       <c r="E53">
         <v>7516.197</v>
@@ -5627,37 +5737,37 @@
         <v>1181.9</v>
       </c>
       <c r="M53">
-        <v>3611.5202526</v>
+        <v>3360.4877976</v>
       </c>
       <c r="N53">
-        <v>-2429.6202526</v>
+        <v>-2178.5877976</v>
       </c>
       <c r="O53">
-        <v>-626.8420251708001</v>
+        <v>-562.0756517807999</v>
       </c>
       <c r="P53">
-        <v>-1802.7782274292</v>
+        <v>-1616.5121458192</v>
       </c>
       <c r="Q53">
-        <v>-1047.6782274292</v>
+        <v>-861.4121458191998</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1338144738903554</v>
+        <v>0.1334622243798294</v>
       </c>
       <c r="T53">
-        <v>2.031360009447057</v>
+        <v>2.024531740873659</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.08443264295153131</v>
+        <v>0.09073986229552024</v>
       </c>
       <c r="W53">
-        <v>0.1975794356510596</v>
+        <v>0.1825794356510596</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5775,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3272583060136873</v>
+        <v>0.3517048926182954</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5786,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1680346043883145</v>
+        <v>0.1600620021281568</v>
       </c>
       <c r="C54">
-        <v>-6139.897619397107</v>
+        <v>-5385.413971115684</v>
       </c>
       <c r="D54">
-        <v>10923.74638060289</v>
+        <v>11678.23002888432</v>
       </c>
       <c r="E54">
         <v>7844.344000000001</v>
@@ -5709,37 +5819,37 @@
         <v>1181.9</v>
       </c>
       <c r="M54">
-        <v>3682.334375200001</v>
+        <v>3426.3797152</v>
       </c>
       <c r="N54">
-        <v>-2500.4343752</v>
+        <v>-2244.4797152</v>
       </c>
       <c r="O54">
-        <v>-645.1120688016001</v>
+        <v>-579.0757665216</v>
       </c>
       <c r="P54">
-        <v>-1855.3223063984</v>
+        <v>-1665.4039486784</v>
       </c>
       <c r="Q54">
-        <v>-1100.2223063984</v>
+        <v>-910.3039486784</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1356481087630712</v>
+        <v>0.1352885207210759</v>
       </c>
       <c r="T54">
-        <v>2.073680009643871</v>
+        <v>2.066709485475193</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.08280893827938648</v>
+        <v>0.08899486494368329</v>
       </c>
       <c r="W54">
-        <v>0.1979298311193084</v>
+        <v>0.1829298311193084</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3209648770518856</v>
+        <v>0.3449413369910205</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5868,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1697346043883146</v>
+        <v>0.1616120021281568</v>
       </c>
       <c r="C55">
-        <v>-6617.884681732239</v>
+        <v>-5869.859594851932</v>
       </c>
       <c r="D55">
-        <v>10773.90631826776</v>
+        <v>11521.93140514807</v>
       </c>
       <c r="E55">
         <v>8172.491000000002</v>
@@ -5791,37 +5901,37 @@
         <v>1181.9</v>
       </c>
       <c r="M55">
-        <v>3753.148497800001</v>
+        <v>3492.2716328</v>
       </c>
       <c r="N55">
-        <v>-2571.248497800001</v>
+        <v>-2310.3716328</v>
       </c>
       <c r="O55">
-        <v>-663.3821124324002</v>
+        <v>-596.0758812624</v>
       </c>
       <c r="P55">
-        <v>-1907.866385367601</v>
+        <v>-1714.2957515376</v>
       </c>
       <c r="Q55">
-        <v>-1152.766385367601</v>
+        <v>-959.1957515376002</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1375597706516472</v>
+        <v>0.1371925318002477</v>
       </c>
       <c r="T55">
-        <v>2.11780086091289</v>
+        <v>2.110682027719347</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08124650548166221</v>
+        <v>0.08731571654851945</v>
       </c>
       <c r="W55">
-        <v>0.1982670041170573</v>
+        <v>0.1832670041170573</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5939,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3149089359754349</v>
+        <v>0.3384330098779824</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5950,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1714346043883146</v>
+        <v>0.1631620021281568</v>
       </c>
       <c r="C56">
-        <v>-7091.816681257093</v>
+        <v>-6350.176746639881</v>
       </c>
       <c r="D56">
-        <v>10628.12131874291</v>
+        <v>11369.76125336012</v>
       </c>
       <c r="E56">
         <v>8500.637999999999</v>
@@ -5873,37 +5983,37 @@
         <v>1181.9</v>
       </c>
       <c r="M56">
-        <v>3823.9626204</v>
+        <v>3558.1635504</v>
       </c>
       <c r="N56">
-        <v>-2642.0626204</v>
+        <v>-2376.2635504</v>
       </c>
       <c r="O56">
-        <v>-681.6521560632</v>
+        <v>-613.0759960031999</v>
       </c>
       <c r="P56">
-        <v>-1960.4104643368</v>
+        <v>-1763.1875543968</v>
       </c>
       <c r="Q56">
-        <v>-1205.3104643368</v>
+        <v>-1008.0875543968</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1395545482745091</v>
+        <v>0.1391793259698183</v>
       </c>
       <c r="T56">
-        <v>2.16384001006317</v>
+        <v>2.156566419626289</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07974194056533515</v>
+        <v>0.085698758834658</v>
       </c>
       <c r="W56">
-        <v>0.1985916892260007</v>
+        <v>0.1835916892260007</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +6021,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3090772890129269</v>
+        <v>0.3321657319172791</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6032,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1731346043883146</v>
+        <v>0.1647120021281568</v>
       </c>
       <c r="C57">
-        <v>-7561.856031169798</v>
+        <v>-6826.526868505705</v>
       </c>
       <c r="D57">
-        <v>10486.2289688302</v>
+        <v>11221.55813149429</v>
       </c>
       <c r="E57">
         <v>8828.785</v>
@@ -5955,37 +6065,37 @@
         <v>1181.9</v>
       </c>
       <c r="M57">
-        <v>3894.776743</v>
+        <v>3624.055468</v>
       </c>
       <c r="N57">
-        <v>-2712.876743</v>
+        <v>-2442.155468</v>
       </c>
       <c r="O57">
-        <v>-699.9221996940001</v>
+        <v>-630.0761107439999</v>
       </c>
       <c r="P57">
-        <v>-2012.954543306</v>
+        <v>-1812.079357256</v>
       </c>
       <c r="Q57">
-        <v>-1257.854543306</v>
+        <v>-1056.979357256</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1416379826806093</v>
+        <v>0.1412544221024809</v>
       </c>
       <c r="T57">
-        <v>2.211925343620129</v>
+        <v>2.204490117840206</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.07829208710051086</v>
+        <v>0.08414059958311874</v>
       </c>
       <c r="W57">
-        <v>0.1989045676037098</v>
+        <v>0.1839045676037098</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +6103,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3034577019399646</v>
+        <v>0.3261263549733285</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6114,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1748346043883146</v>
+        <v>0.1662620021281568</v>
       </c>
       <c r="C58">
-        <v>-8028.1565856486</v>
+        <v>-7299.06309329471</v>
       </c>
       <c r="D58">
-        <v>10348.0754143514</v>
+        <v>11077.16890670529</v>
       </c>
       <c r="E58">
         <v>9156.932000000001</v>
@@ -6037,37 +6147,37 @@
         <v>1181.9</v>
       </c>
       <c r="M58">
-        <v>3965.5908656</v>
+        <v>3689.9473856</v>
       </c>
       <c r="N58">
-        <v>-2783.6908656</v>
+        <v>-2508.0473856</v>
       </c>
       <c r="O58">
-        <v>-718.1922433248001</v>
+        <v>-647.0762254848</v>
       </c>
       <c r="P58">
-        <v>-2065.4986222752</v>
+        <v>-1860.9711601152</v>
       </c>
       <c r="Q58">
-        <v>-1310.3986222752</v>
+        <v>-1105.8711601152</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1438161186506232</v>
+        <v>0.1434238407866282</v>
       </c>
       <c r="T58">
-        <v>2.262196374156951</v>
+        <v>2.254592165972938</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.07689401411657318</v>
+        <v>0.08263808887627735</v>
       </c>
       <c r="W58">
-        <v>0.1992062717536435</v>
+        <v>0.1842062717536435</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6185,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2980388144053223</v>
+        <v>0.3203026700630904</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6196,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1765346043883146</v>
+        <v>0.1678120021281568</v>
       </c>
       <c r="C59">
-        <v>-8490.864196335468</v>
+        <v>-7767.930772456742</v>
       </c>
       <c r="D59">
-        <v>10213.51480366453</v>
+        <v>10936.44822754326</v>
       </c>
       <c r="E59">
         <v>9485.079000000002</v>
@@ -6119,37 +6229,37 @@
         <v>1181.9</v>
       </c>
       <c r="M59">
-        <v>4036.4049882</v>
+        <v>3755.8393032</v>
       </c>
       <c r="N59">
-        <v>-2854.5049882</v>
+        <v>-2573.9393032</v>
       </c>
       <c r="O59">
-        <v>-736.4622869556001</v>
+        <v>-664.0763402256001</v>
       </c>
       <c r="P59">
-        <v>-2118.0427012444</v>
+        <v>-1909.8629629744</v>
       </c>
       <c r="Q59">
-        <v>-1362.9427012444</v>
+        <v>-1154.7629629744</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1460955632704051</v>
+        <v>0.145694162665387</v>
       </c>
       <c r="T59">
-        <v>2.314805592160601</v>
+        <v>2.307024541925797</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.07554499632505435</v>
+        <v>0.08118829784336019</v>
       </c>
       <c r="W59">
-        <v>0.1994973897930533</v>
+        <v>0.1844973897930533</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6267,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2928100632754044</v>
+        <v>0.3146833249742643</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6278,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1782346043883145</v>
+        <v>0.1693620021281568</v>
       </c>
       <c r="C60">
-        <v>-8950.117225959859</v>
+        <v>-8233.267964107325</v>
       </c>
       <c r="D60">
-        <v>10082.40877404014</v>
+        <v>10799.25803589267</v>
       </c>
       <c r="E60">
         <v>9813.225999999999</v>
@@ -6201,37 +6311,37 @@
         <v>1181.9</v>
       </c>
       <c r="M60">
-        <v>4107.2191108</v>
+        <v>3821.7312208</v>
       </c>
       <c r="N60">
-        <v>-2925.3191108</v>
+        <v>-2639.8312208</v>
       </c>
       <c r="O60">
-        <v>-754.7323305863999</v>
+        <v>-681.0764549664</v>
       </c>
       <c r="P60">
-        <v>-2170.5867802136</v>
+        <v>-1958.7547658336</v>
       </c>
       <c r="Q60">
-        <v>-1415.4867802136</v>
+        <v>-1203.6547658336</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1484835528720813</v>
+        <v>0.148072595109801</v>
       </c>
       <c r="T60">
-        <v>2.369920011021566</v>
+        <v>2.361953697685935</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07424249638841549</v>
+        <v>0.07978849960468158</v>
       </c>
       <c r="W60">
-        <v>0.1997784692793799</v>
+        <v>0.1847784692793799</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6349,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2877616139085871</v>
+        <v>0.3092577504057425</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6360,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1799346043883145</v>
+        <v>0.1709120021281568</v>
       </c>
       <c r="C61">
-        <v>-9406.047022904997</v>
+        <v>-8695.20588480962</v>
       </c>
       <c r="D61">
-        <v>9954.625977095002</v>
+        <v>10665.46711519038</v>
       </c>
       <c r="E61">
         <v>10141.373</v>
@@ -6283,37 +6393,37 @@
         <v>1181.9</v>
       </c>
       <c r="M61">
-        <v>4178.0332334</v>
+        <v>3887.6231384</v>
       </c>
       <c r="N61">
-        <v>-2996.1332334</v>
+        <v>-2705.7231384</v>
       </c>
       <c r="O61">
-        <v>-773.0023742172001</v>
+        <v>-698.0765697072</v>
       </c>
       <c r="P61">
-        <v>-2223.1308591828</v>
+        <v>-2007.6465686928</v>
       </c>
       <c r="Q61">
-        <v>-1468.0308591828</v>
+        <v>-1252.5465686928</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1509880297714004</v>
+        <v>0.1505670486490644</v>
       </c>
       <c r="T61">
-        <v>2.427722938119654</v>
+        <v>2.419562324458763</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07298414899200165</v>
+        <v>0.07843615215375478</v>
       </c>
       <c r="W61">
-        <v>0.2000500206475261</v>
+        <v>0.185050020647526</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2828842984186111</v>
+        <v>0.3040160936192046</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6442,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1816346043883146</v>
+        <v>0.1724620021281568</v>
       </c>
       <c r="C62">
-        <v>-9858.778360138263</v>
+        <v>-9153.869328184786</v>
       </c>
       <c r="D62">
-        <v>9830.041639861733</v>
+        <v>10534.95067181521</v>
       </c>
       <c r="E62">
         <v>10469.52</v>
@@ -6365,37 +6475,37 @@
         <v>1181.9</v>
       </c>
       <c r="M62">
-        <v>4248.847355999999</v>
+        <v>3953.515055999999</v>
       </c>
       <c r="N62">
-        <v>-3066.947355999999</v>
+        <v>-2771.615055999999</v>
       </c>
       <c r="O62">
-        <v>-791.2724178479998</v>
+        <v>-715.0766844479998</v>
       </c>
       <c r="P62">
-        <v>-2275.674938151999</v>
+        <v>-2056.538371551999</v>
       </c>
       <c r="Q62">
-        <v>-1520.574938152</v>
+        <v>-1301.438371551999</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1536177305156854</v>
+        <v>0.153186224865291</v>
       </c>
       <c r="T62">
-        <v>2.488416011572645</v>
+        <v>2.480051382570231</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.07176774650880163</v>
+        <v>0.0771288829511922</v>
       </c>
       <c r="W62">
-        <v>0.2003125203034006</v>
+        <v>0.1853125203034006</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2781695601116343</v>
+        <v>0.2989491587255512</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6524,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1833346043883146</v>
+        <v>0.1740120021281568</v>
       </c>
       <c r="C63">
-        <v>-10308.42984158922</v>
+        <v>-9609.377053158034</v>
       </c>
       <c r="D63">
-        <v>9708.537158410772</v>
+        <v>10407.58994684196</v>
       </c>
       <c r="E63">
         <v>10797.667</v>
@@ -6447,37 +6557,37 @@
         <v>1181.9</v>
       </c>
       <c r="M63">
-        <v>4319.6614786</v>
+        <v>4019.4069736</v>
       </c>
       <c r="N63">
-        <v>-3137.7614786</v>
+        <v>-2837.5069736</v>
       </c>
       <c r="O63">
-        <v>-809.5424614788</v>
+        <v>-732.0767991887999</v>
       </c>
       <c r="P63">
-        <v>-2328.2190171212</v>
+        <v>-2105.4301744112</v>
       </c>
       <c r="Q63">
-        <v>-1573.1190171212</v>
+        <v>-1350.3301744112</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1563822877083953</v>
+        <v>0.1559397178105549</v>
       </c>
       <c r="T63">
-        <v>2.552221550330918</v>
+        <v>2.543642443661776</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.0705912260742311</v>
+        <v>0.07586447503395954</v>
       </c>
       <c r="W63">
-        <v>0.200566413413181</v>
+        <v>0.1855664134131809</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6595,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2736094033884927</v>
+        <v>0.2940483528448044</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6606,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1850346043883145</v>
+        <v>0.1755620021281568</v>
       </c>
       <c r="C64">
-        <v>-10755.11427875727</v>
+        <v>-10061.84214437917</v>
       </c>
       <c r="D64">
-        <v>9589.999721242726</v>
+        <v>10283.27185562083</v>
       </c>
       <c r="E64">
         <v>11125.814</v>
@@ -6529,37 +6639,37 @@
         <v>1181.9</v>
       </c>
       <c r="M64">
-        <v>4390.4756012</v>
+        <v>4085.2988912</v>
       </c>
       <c r="N64">
-        <v>-3208.5756012</v>
+        <v>-2903.3988912</v>
       </c>
       <c r="O64">
-        <v>-827.8125051095999</v>
+        <v>-749.0769139295999</v>
       </c>
       <c r="P64">
-        <v>-2380.7630960904</v>
+        <v>-2154.3219772704</v>
       </c>
       <c r="Q64">
-        <v>-1625.6630960904</v>
+        <v>-1399.2219772704</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1592923479112478</v>
+        <v>0.1588381314371484</v>
       </c>
       <c r="T64">
-        <v>2.619385275339626</v>
+        <v>2.610580402705507</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06945265791174351</v>
+        <v>0.07464085446889568</v>
       </c>
       <c r="W64">
-        <v>0.2008121164226458</v>
+        <v>0.1858121164226458</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2691963484951299</v>
+        <v>0.2893056374763399</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6688,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1867346043883146</v>
+        <v>0.1771120021281568</v>
       </c>
       <c r="C65">
-        <v>-11198.93904006275</v>
+        <v>-10511.37234711685</v>
       </c>
       <c r="D65">
-        <v>9474.321959937251</v>
+        <v>10161.88865288315</v>
       </c>
       <c r="E65">
         <v>11453.961</v>
@@ -6611,37 +6721,37 @@
         <v>1181.9</v>
       </c>
       <c r="M65">
-        <v>4461.289723800001</v>
+        <v>4151.1908088</v>
       </c>
       <c r="N65">
-        <v>-3279.3897238</v>
+        <v>-2969.2908088</v>
       </c>
       <c r="O65">
-        <v>-846.0825487404002</v>
+        <v>-766.0770286704</v>
       </c>
       <c r="P65">
-        <v>-2433.3071750596</v>
+        <v>-2203.2137801296</v>
       </c>
       <c r="Q65">
-        <v>-1678.2071750596</v>
+        <v>-1448.1137801296</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1623597086656059</v>
+        <v>0.1618932160705849</v>
       </c>
       <c r="T65">
-        <v>2.690179471970427</v>
+        <v>2.681136629805656</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.06835023477028726</v>
+        <v>0.07345607900113542</v>
       </c>
       <c r="W65">
-        <v>0.201050019336572</v>
+        <v>0.186050019336572</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2649233905825088</v>
+        <v>0.2847134845005249</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6770,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1884346043883146</v>
+        <v>0.1786620021281568</v>
       </c>
       <c r="C66">
-        <v>-11640.00637521539</v>
+        <v>-10958.07037871109</v>
       </c>
       <c r="D66">
-        <v>9361.401624784605</v>
+        <v>10043.33762128891</v>
       </c>
       <c r="E66">
         <v>11782.108</v>
@@ -6693,37 +6803,37 @@
         <v>1181.9</v>
       </c>
       <c r="M66">
-        <v>4532.1038464</v>
+        <v>4217.0827264</v>
       </c>
       <c r="N66">
-        <v>-3350.2038464</v>
+        <v>-3035.1827264</v>
       </c>
       <c r="O66">
-        <v>-864.3525923712001</v>
+        <v>-783.0771434112</v>
       </c>
       <c r="P66">
-        <v>-2485.8512540288</v>
+        <v>-2252.1055829888</v>
       </c>
       <c r="Q66">
-        <v>-1730.7512540288</v>
+        <v>-1497.0055829888</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1655974783507616</v>
+        <v>0.1651180276281011</v>
       </c>
       <c r="T66">
-        <v>2.764906679525161</v>
+        <v>2.755612647300257</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.06728226235200153</v>
+        <v>0.07230832776674267</v>
       </c>
       <c r="W66">
-        <v>0.2012804877844381</v>
+        <v>0.1862804877844381</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2607839626046571</v>
+        <v>0.2802648363052042</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6852,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1901346043883146</v>
+        <v>0.1802120021281568</v>
       </c>
       <c r="C67">
-        <v>-12078.41371666004</v>
+        <v>-11402.0342184763</v>
       </c>
       <c r="D67">
-        <v>9251.141283339955</v>
+        <v>9927.520781523703</v>
       </c>
       <c r="E67">
         <v>12110.255</v>
@@ -6775,37 +6885,37 @@
         <v>1181.9</v>
       </c>
       <c r="M67">
-        <v>4602.917969</v>
+        <v>4282.974644</v>
       </c>
       <c r="N67">
-        <v>-3421.017969</v>
+        <v>-3101.074644</v>
       </c>
       <c r="O67">
-        <v>-882.622636002</v>
+        <v>-800.077258152</v>
       </c>
       <c r="P67">
-        <v>-2538.395332998</v>
+        <v>-2300.997385848</v>
       </c>
       <c r="Q67">
-        <v>-1783.295332998</v>
+        <v>-1545.897385848</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1690202634464976</v>
+        <v>0.1685271141317612</v>
       </c>
       <c r="T67">
-        <v>2.843904013225881</v>
+        <v>2.834344437223122</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.06624715062350919</v>
+        <v>0.07119589195494663</v>
       </c>
       <c r="W67">
-        <v>0.2015038648954467</v>
+        <v>0.1865038648954467</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6923,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2567719016415085</v>
+        <v>0.2759530695928164</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6934,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1918346043883146</v>
+        <v>0.1817620021281568</v>
       </c>
       <c r="C68">
-        <v>-12514.25395996735</v>
+        <v>-11843.35737777452</v>
       </c>
       <c r="D68">
-        <v>9143.448040032645</v>
+        <v>9814.344622225479</v>
       </c>
       <c r="E68">
         <v>12438.402</v>
@@ -6857,37 +6967,37 @@
         <v>1181.9</v>
       </c>
       <c r="M68">
-        <v>4673.7320916</v>
+        <v>4348.8665616</v>
       </c>
       <c r="N68">
-        <v>-3491.8320916</v>
+        <v>-3166.9665616</v>
       </c>
       <c r="O68">
-        <v>-900.8926796328</v>
+        <v>-817.0773728928</v>
       </c>
       <c r="P68">
-        <v>-2590.9394119672</v>
+        <v>-2349.8891887072</v>
       </c>
       <c r="Q68">
-        <v>-1835.8394119672</v>
+        <v>-1594.7891887072</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1726443888419829</v>
+        <v>0.1721367351356365</v>
       </c>
       <c r="T68">
-        <v>2.927548248908995</v>
+        <v>2.917707508906155</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.06524340591709239</v>
+        <v>0.07011716631926562</v>
       </c>
       <c r="W68">
-        <v>0.2017204730030915</v>
+        <v>0.1867204730030915</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +7005,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2528814182833038</v>
+        <v>0.2717719624777738</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7016,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1935346043883146</v>
+        <v>0.1833120021281568</v>
       </c>
       <c r="C69">
-        <v>-12947.61572486562</v>
+        <v>-12282.1291518235</v>
       </c>
       <c r="D69">
-        <v>9038.233275134375</v>
+        <v>9703.719848176501</v>
       </c>
       <c r="E69">
         <v>12766.549</v>
@@ -6939,37 +7049,37 @@
         <v>1181.9</v>
       </c>
       <c r="M69">
-        <v>4744.5462142</v>
+        <v>4414.7584792</v>
       </c>
       <c r="N69">
-        <v>-3562.6462142</v>
+        <v>-3232.8584792</v>
       </c>
       <c r="O69">
-        <v>-919.1627232635999</v>
+        <v>-834.0774876336</v>
       </c>
       <c r="P69">
-        <v>-2643.4834909364</v>
+        <v>-2398.7809915664</v>
       </c>
       <c r="Q69">
-        <v>-1888.3834909364</v>
+        <v>-1643.6809915664</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1764881582008309</v>
+        <v>0.1759651210488377</v>
       </c>
       <c r="T69">
-        <v>3.016261832209267</v>
+        <v>3.006122887963918</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06426962373922535</v>
+        <v>0.06907064144882882</v>
       </c>
       <c r="W69">
-        <v>0.2019306151970752</v>
+        <v>0.1869306151970752</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +7087,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2491070687566874</v>
+        <v>0.2677156645303443</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7098,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1952346043883146</v>
+        <v>0.1848620021281568</v>
       </c>
       <c r="C70">
-        <v>-13378.58359845526</v>
+        <v>-12718.43485466464</v>
       </c>
       <c r="D70">
-        <v>8935.412401544736</v>
+        <v>9595.561145335363</v>
       </c>
       <c r="E70">
         <v>13094.696</v>
@@ -7021,37 +7131,37 @@
         <v>1181.9</v>
       </c>
       <c r="M70">
-        <v>4815.3603368</v>
+        <v>4480.6503968</v>
       </c>
       <c r="N70">
-        <v>-3633.4603368</v>
+        <v>-3298.7503968</v>
       </c>
       <c r="O70">
-        <v>-937.4327668944001</v>
+        <v>-851.0776023743999</v>
       </c>
       <c r="P70">
-        <v>-2696.0275699056</v>
+        <v>-2447.6727944256</v>
       </c>
       <c r="Q70">
-        <v>-1940.9275699056</v>
+        <v>-1692.5727944256</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1805721631446068</v>
+        <v>0.1800327810816138</v>
       </c>
       <c r="T70">
-        <v>3.110520014465807</v>
+        <v>3.10006422821279</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.06332448221364849</v>
+        <v>0.06805489672164017</v>
       </c>
       <c r="W70">
-        <v>0.2021345767382947</v>
+        <v>0.1871345767382947</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7169,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2454437295102655</v>
+        <v>0.2637786694637216</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7180,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1969346043883146</v>
+        <v>0.1864120021281568</v>
       </c>
       <c r="C71">
-        <v>-13807.23836200885</v>
+        <v>-13152.35603859037</v>
       </c>
       <c r="D71">
-        <v>8834.904637991147</v>
+        <v>9489.786961409625</v>
       </c>
       <c r="E71">
         <v>13422.843</v>
@@ -7103,37 +7213,37 @@
         <v>1181.9</v>
       </c>
       <c r="M71">
-        <v>4886.1744594</v>
+        <v>4546.542314400001</v>
       </c>
       <c r="N71">
-        <v>-3704.2744594</v>
+        <v>-3364.6423144</v>
       </c>
       <c r="O71">
-        <v>-955.7028105252</v>
+        <v>-868.0777171152001</v>
       </c>
       <c r="P71">
-        <v>-2748.5716488748</v>
+        <v>-2496.564597284801</v>
       </c>
       <c r="Q71">
-        <v>-1993.4716488748</v>
+        <v>-1741.464597284801</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1849196522783038</v>
+        <v>0.1843628707939239</v>
       </c>
       <c r="T71">
-        <v>3.210859369771156</v>
+        <v>3.200066300090622</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.06240673609461011</v>
+        <v>0.06706859387060189</v>
       </c>
       <c r="W71">
-        <v>0.2023326263507832</v>
+        <v>0.1873326263507831</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7251,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2418865740101167</v>
+        <v>0.2599557901961314</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7262,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1986346043883146</v>
+        <v>0.1879620021281568</v>
       </c>
       <c r="C72">
-        <v>-14233.65720263485</v>
+        <v>-13583.97069921691</v>
       </c>
       <c r="D72">
-        <v>8736.632797365153</v>
+        <v>9386.319300783089</v>
       </c>
       <c r="E72">
         <v>13750.99</v>
@@ -7185,37 +7295,37 @@
         <v>1181.9</v>
       </c>
       <c r="M72">
-        <v>4956.988582000001</v>
+        <v>4612.434232000001</v>
       </c>
       <c r="N72">
-        <v>-3775.088582000001</v>
+        <v>-3430.534232</v>
       </c>
       <c r="O72">
-        <v>-973.9728541560003</v>
+        <v>-885.0778318560001</v>
       </c>
       <c r="P72">
-        <v>-2801.115727844001</v>
+        <v>-2545.456400144</v>
       </c>
       <c r="Q72">
-        <v>-2046.015727844001</v>
+        <v>-1790.356400144</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.189556974020914</v>
+        <v>0.1889816331537214</v>
       </c>
       <c r="T72">
-        <v>3.317888015430194</v>
+        <v>3.30673517676031</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.06151521129325853</v>
+        <v>0.06611047110102188</v>
       </c>
       <c r="W72">
-        <v>0.2025250174029148</v>
+        <v>0.1875250174029148</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2384310515242578</v>
+        <v>0.2562421360504723</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7344,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2003346043883146</v>
+        <v>0.1895120021281568</v>
       </c>
       <c r="C73">
-        <v>-14657.91391097046</v>
+        <v>-14013.35346728616</v>
       </c>
       <c r="D73">
-        <v>8640.523089029537</v>
+        <v>9285.083532713839</v>
       </c>
       <c r="E73">
         <v>14079.137</v>
@@ -7267,37 +7377,37 @@
         <v>1181.9</v>
       </c>
       <c r="M73">
-        <v>5027.8027046</v>
+        <v>4678.3261496</v>
       </c>
       <c r="N73">
-        <v>-3845.9027046</v>
+        <v>-3496.426149599999</v>
       </c>
       <c r="O73">
-        <v>-992.2428977868</v>
+        <v>-902.0779465967998</v>
       </c>
       <c r="P73">
-        <v>-2853.6598068132</v>
+        <v>-2594.3482030032</v>
       </c>
       <c r="Q73">
-        <v>-2098.5598068132</v>
+        <v>-1839.2482030032</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1945141110561178</v>
+        <v>0.1939189308486773</v>
       </c>
       <c r="T73">
-        <v>3.432297946996752</v>
+        <v>3.420760527683078</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.06064879986659293</v>
+        <v>0.06517933770523285</v>
       </c>
       <c r="W73">
-        <v>0.2027119889887893</v>
+        <v>0.1877119889887892</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2350728676999726</v>
+        <v>0.2526330918807475</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7426,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2020346043883146</v>
+        <v>0.1910620021281568</v>
       </c>
       <c r="C74">
-        <v>-15080.07906596793</v>
+        <v>-14440.5757881881</v>
       </c>
       <c r="D74">
-        <v>8546.504934032062</v>
+        <v>9186.008211811892</v>
       </c>
       <c r="E74">
         <v>14407.284</v>
@@ -7349,37 +7459,37 @@
         <v>1181.9</v>
       </c>
       <c r="M74">
-        <v>5098.6168272</v>
+        <v>4744.218067199999</v>
       </c>
       <c r="N74">
-        <v>-3916.716827199999</v>
+        <v>-3562.318067199999</v>
       </c>
       <c r="O74">
-        <v>-1010.5129414176</v>
+        <v>-919.0780613375998</v>
       </c>
       <c r="P74">
-        <v>-2906.2038857824</v>
+        <v>-2643.2400058624</v>
       </c>
       <c r="Q74">
-        <v>-2151.1038857824</v>
+        <v>-1888.1400058624</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1998253293081221</v>
+        <v>0.1992088926647015</v>
       </c>
       <c r="T74">
-        <v>3.55488001653235</v>
+        <v>3.542930546528902</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05980645542400136</v>
+        <v>0.0642740691259935</v>
       </c>
       <c r="W74">
-        <v>0.2028937669195005</v>
+        <v>0.1878937669195005</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7497,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2318079667596952</v>
+        <v>0.2491242989379593</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7508,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2037346043883146</v>
+        <v>0.1926120021281568</v>
       </c>
       <c r="C75">
-        <v>-15500.22020774659</v>
+        <v>-14865.70609011106</v>
       </c>
       <c r="D75">
-        <v>8454.510792253404</v>
+        <v>9089.024909888938</v>
       </c>
       <c r="E75">
         <v>14735.431</v>
@@ -7431,37 +7541,37 @@
         <v>1181.9</v>
       </c>
       <c r="M75">
-        <v>5169.430949799999</v>
+        <v>4810.109984799999</v>
       </c>
       <c r="N75">
-        <v>-3987.530949799999</v>
+        <v>-3628.209984799999</v>
       </c>
       <c r="O75">
-        <v>-1028.7829850484</v>
+        <v>-936.0781760783999</v>
       </c>
       <c r="P75">
-        <v>-2958.747964751599</v>
+        <v>-2692.1318087216</v>
       </c>
       <c r="Q75">
-        <v>-2203.647964751599</v>
+        <v>-1937.0318087216</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2055299711343488</v>
+        <v>0.2048907035041349</v>
       </c>
       <c r="T75">
-        <v>3.686542239366881</v>
+        <v>3.674150196400343</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05898718891134381</v>
+        <v>0.06339360242563742</v>
       </c>
       <c r="W75">
-        <v>0.203070564632932</v>
+        <v>0.188070564632932</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7579,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2286325151602473</v>
+        <v>0.2457116373086722</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7590,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2054346043883145</v>
+        <v>0.1941620021281568</v>
       </c>
       <c r="C76">
-        <v>-15918.40199940034</v>
+        <v>-15288.80994165151</v>
       </c>
       <c r="D76">
-        <v>8364.476000599654</v>
+        <v>8994.068058348485</v>
       </c>
       <c r="E76">
         <v>15063.578</v>
@@ -7513,37 +7623,37 @@
         <v>1181.9</v>
       </c>
       <c r="M76">
-        <v>5240.2450724</v>
+        <v>4876.001902399999</v>
       </c>
       <c r="N76">
-        <v>-4058.3450724</v>
+        <v>-3694.101902399999</v>
       </c>
       <c r="O76">
-        <v>-1047.0530286792</v>
+        <v>-953.0782908191999</v>
       </c>
       <c r="P76">
-        <v>-3011.2920437208</v>
+        <v>-2741.023611580799</v>
       </c>
       <c r="Q76">
-        <v>-2256.1920437208</v>
+        <v>-1985.923611580799</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.211673431562593</v>
+        <v>0.2110095767158323</v>
       </c>
       <c r="T76">
-        <v>3.828332325496377</v>
+        <v>3.815463665492664</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05819006473686619</v>
+        <v>0.06253693212258828</v>
       </c>
       <c r="W76">
-        <v>0.2032425840297843</v>
+        <v>0.1882425840297843</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2255428865770007</v>
+        <v>0.2423912097774739</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7672,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2071346043883145</v>
+        <v>0.1957120021281568</v>
       </c>
       <c r="C77">
-        <v>-16334.68637857533</v>
+        <v>-15709.95019964644</v>
       </c>
       <c r="D77">
-        <v>8276.338621424669</v>
+        <v>8901.074800353554</v>
       </c>
       <c r="E77">
         <v>15391.725</v>
@@ -7595,37 +7705,37 @@
         <v>1181.9</v>
       </c>
       <c r="M77">
-        <v>5311.059195</v>
+        <v>4941.893819999999</v>
       </c>
       <c r="N77">
-        <v>-4129.159195</v>
+        <v>-3759.993819999999</v>
       </c>
       <c r="O77">
-        <v>-1065.32307231</v>
+        <v>-970.0784055599999</v>
       </c>
       <c r="P77">
-        <v>-3063.83612269</v>
+        <v>-2789.915414439999</v>
       </c>
       <c r="Q77">
-        <v>-2308.73612269</v>
+        <v>-2034.81541444</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2183083688250967</v>
+        <v>0.2176179597844657</v>
       </c>
       <c r="T77">
-        <v>3.981465618516232</v>
+        <v>3.968082212112371</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.0574141972070413</v>
+        <v>0.06170310636095376</v>
       </c>
       <c r="W77">
-        <v>0.2034100162427205</v>
+        <v>0.1884100162427205</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2225356480893073</v>
+        <v>0.239159326980441</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7754,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2088346043883146</v>
+        <v>0.1972620021281568</v>
       </c>
       <c r="C78">
-        <v>-16749.13269956433</v>
+        <v>-16129.18714792848</v>
       </c>
       <c r="D78">
-        <v>8190.039300435667</v>
+        <v>8809.984852071515</v>
       </c>
       <c r="E78">
         <v>15719.872</v>
@@ -7677,37 +7787,37 @@
         <v>1181.9</v>
       </c>
       <c r="M78">
-        <v>5381.873317600001</v>
+        <v>5007.7857376</v>
       </c>
       <c r="N78">
-        <v>-4199.973317600001</v>
+        <v>-3825.8857376</v>
       </c>
       <c r="O78">
-        <v>-1083.5931159408</v>
+        <v>-987.0785203008001</v>
       </c>
       <c r="P78">
-        <v>-3116.380201659201</v>
+        <v>-2838.8072172992</v>
       </c>
       <c r="Q78">
-        <v>-2361.280201659201</v>
+        <v>-2083.7072172992</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2254962175261424</v>
+        <v>0.2247770414421517</v>
       </c>
       <c r="T78">
-        <v>4.147360019287742</v>
+        <v>4.133418970950387</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05665874724379075</v>
+        <v>0.06089122338252015</v>
       </c>
       <c r="W78">
-        <v>0.20357304234479</v>
+        <v>0.1885730423447899</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2196075474565532</v>
+        <v>0.2360124937306982</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7836,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2105346043883146</v>
+        <v>0.1988120021281568</v>
       </c>
       <c r="C79">
-        <v>-17161.797866603</v>
+        <v>-16546.57862764762</v>
       </c>
       <c r="D79">
-        <v>8105.521133396996</v>
+        <v>8720.740372352375</v>
       </c>
       <c r="E79">
         <v>16048.019</v>
@@ -7759,37 +7869,37 @@
         <v>1181.9</v>
       </c>
       <c r="M79">
-        <v>5452.6874402</v>
+        <v>5073.6776552</v>
       </c>
       <c r="N79">
-        <v>-4270.7874402</v>
+        <v>-3891.7776552</v>
       </c>
       <c r="O79">
-        <v>-1101.8631595716</v>
+        <v>-1004.0786350416</v>
       </c>
       <c r="P79">
-        <v>-3168.9242806284</v>
+        <v>-2887.6990201584</v>
       </c>
       <c r="Q79">
-        <v>-2413.8242806284</v>
+        <v>-2132.5990201584</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2333090965490182</v>
+        <v>0.2325586519396366</v>
       </c>
       <c r="T79">
-        <v>4.327680020126341</v>
+        <v>4.313132839252577</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.05592291935750776</v>
+        <v>0.06010042827365625</v>
       </c>
       <c r="W79">
-        <v>0.2037318340026499</v>
+        <v>0.1887318340026498</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2167555013856891</v>
+        <v>0.2329473964095203</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7918,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2122346043883146</v>
+        <v>0.2003620021281568</v>
       </c>
       <c r="C80">
-        <v>-17572.73645899701</v>
+        <v>-16962.18015975143</v>
       </c>
       <c r="D80">
-        <v>8022.72954100299</v>
+        <v>8633.285840248565</v>
       </c>
       <c r="E80">
         <v>16376.166</v>
@@ -7841,37 +7951,37 @@
         <v>1181.9</v>
       </c>
       <c r="M80">
-        <v>5523.501562800001</v>
+        <v>5139.5695728</v>
       </c>
       <c r="N80">
-        <v>-4341.6015628</v>
+        <v>-3957.6695728</v>
       </c>
       <c r="O80">
-        <v>-1120.1332032024</v>
+        <v>-1021.0787497824</v>
       </c>
       <c r="P80">
-        <v>-3221.4683595976</v>
+        <v>-2936.5908230176</v>
       </c>
       <c r="Q80">
-        <v>-2466.3683595976</v>
+        <v>-2181.4908230176</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2418322373012463</v>
+        <v>0.2410476815732565</v>
       </c>
       <c r="T80">
-        <v>4.524392748313901</v>
+        <v>4.509184331945876</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05520595885292432</v>
+        <v>0.05932990996245553</v>
       </c>
       <c r="W80">
-        <v>0.203886554079539</v>
+        <v>0.1888865540795389</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7989,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2139765847012571</v>
+        <v>0.229960891327347</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8000,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2139346043883146</v>
+        <v>0.2019120021281568</v>
       </c>
       <c r="C81">
-        <v>-17982.00084865824</v>
+        <v>-17376.04506016885</v>
       </c>
       <c r="D81">
-        <v>7941.612151341755</v>
+        <v>8547.567939831146</v>
       </c>
       <c r="E81">
         <v>16704.313</v>
@@ -7923,37 +8033,37 @@
         <v>1181.9</v>
       </c>
       <c r="M81">
-        <v>5594.3156854</v>
+        <v>5205.4614904</v>
       </c>
       <c r="N81">
-        <v>-4412.415685399999</v>
+        <v>-4023.5614904</v>
       </c>
       <c r="O81">
-        <v>-1138.4032468332</v>
+        <v>-1038.0788645232</v>
       </c>
       <c r="P81">
-        <v>-3274.0124385668</v>
+        <v>-2985.4826258768</v>
       </c>
       <c r="Q81">
-        <v>-2518.9124385668</v>
+        <v>-2230.3826258768</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2511671057441628</v>
+        <v>0.250345190219602</v>
       </c>
       <c r="T81">
-        <v>4.739840022043134</v>
+        <v>4.723907395371871</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05450714924719111</v>
+        <v>0.05857889844394343</v>
       </c>
       <c r="W81">
-        <v>0.2040373571924562</v>
+        <v>0.1890373571924562</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2112680203379501</v>
+        <v>0.227049993968773</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8082,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2156346043883146</v>
+        <v>0.2034620021281568</v>
       </c>
       <c r="C82">
-        <v>-18389.64131058201</v>
+        <v>-17788.2245481996</v>
       </c>
       <c r="D82">
-        <v>7862.118689417988</v>
+        <v>8463.535451800399</v>
       </c>
       <c r="E82">
         <v>17032.46</v>
@@ -8005,37 +8115,37 @@
         <v>1181.9</v>
       </c>
       <c r="M82">
-        <v>5665.129808000001</v>
+        <v>5271.353408</v>
       </c>
       <c r="N82">
-        <v>-4483.229808</v>
+        <v>-4089.453408</v>
       </c>
       <c r="O82">
-        <v>-1156.673290464</v>
+        <v>-1055.078979264</v>
       </c>
       <c r="P82">
-        <v>-3326.556517536</v>
+        <v>-3034.374428736</v>
       </c>
       <c r="Q82">
-        <v>-2571.456517536</v>
+        <v>-2279.274428736</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2614354610313709</v>
+        <v>0.2605724497305821</v>
       </c>
       <c r="T82">
-        <v>4.976832023145291</v>
+        <v>4.960102765140464</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.05382580988160122</v>
+        <v>0.05784666221339414</v>
       </c>
       <c r="W82">
-        <v>0.2041843902275505</v>
+        <v>0.1891843902275505</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2086271700837257</v>
+        <v>0.2242118690441633</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8164,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2173346043883146</v>
+        <v>0.2050120021281568</v>
       </c>
       <c r="C83">
-        <v>-18795.70612675486</v>
+        <v>-18198.7678485723</v>
       </c>
       <c r="D83">
-        <v>7784.200873245138</v>
+        <v>8381.139151427695</v>
       </c>
       <c r="E83">
         <v>17360.607</v>
@@ -8087,37 +8197,37 @@
         <v>1181.9</v>
       </c>
       <c r="M83">
-        <v>5735.9439306</v>
+        <v>5337.2453256</v>
       </c>
       <c r="N83">
-        <v>-4554.043930600001</v>
+        <v>-4155.345325599999</v>
       </c>
       <c r="O83">
-        <v>-1174.9433340948</v>
+        <v>-1072.0790940048</v>
       </c>
       <c r="P83">
-        <v>-3379.1005965052</v>
+        <v>-3083.266231595199</v>
       </c>
       <c r="Q83">
-        <v>-2624.000596505201</v>
+        <v>-2328.166231595199</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2727846958224957</v>
+        <v>0.2718762628742969</v>
       </c>
       <c r="T83">
-        <v>5.238770550679255</v>
+        <v>5.221160805411015</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.05316129371022343</v>
+        <v>0.05713250588977199</v>
       </c>
       <c r="W83">
-        <v>0.2043277928173338</v>
+        <v>0.1893277928173338</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8235,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2060515260086179</v>
+        <v>0.2214438212781861</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8246,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2190346043883146</v>
+        <v>0.2065620021281568</v>
       </c>
       <c r="C84">
-        <v>-19200.24168394436</v>
+        <v>-18607.72228759858</v>
       </c>
       <c r="D84">
-        <v>7707.812316055643</v>
+        <v>8300.331712401423</v>
       </c>
       <c r="E84">
         <v>17688.754</v>
@@ -8169,37 +8279,37 @@
         <v>1181.9</v>
       </c>
       <c r="M84">
-        <v>5806.7580532</v>
+        <v>5403.1372432</v>
       </c>
       <c r="N84">
-        <v>-4624.8580532</v>
+        <v>-4221.237243199999</v>
       </c>
       <c r="O84">
-        <v>-1193.2133777256</v>
+        <v>-1089.0792087456</v>
       </c>
       <c r="P84">
-        <v>-3431.6446754744</v>
+        <v>-3132.1580344544</v>
       </c>
       <c r="Q84">
-        <v>-2676.5446754744</v>
+        <v>-2377.0580344544</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2853949567015232</v>
+        <v>0.2844360552562023</v>
       </c>
       <c r="T84">
-        <v>5.529813359050324</v>
+        <v>5.511225294600516</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.05251298525034265</v>
+        <v>0.05643576801306745</v>
       </c>
       <c r="W84">
-        <v>0.2044676977829761</v>
+        <v>0.1894676977829761</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.203538702520708</v>
+        <v>0.2187432868723546</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8328,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2207346043883146</v>
+        <v>0.2081120021281568</v>
       </c>
       <c r="C85">
-        <v>-19603.29256578702</v>
+        <v>-19015.13338381781</v>
       </c>
       <c r="D85">
-        <v>7632.908434212983</v>
+        <v>8221.06761618219</v>
       </c>
       <c r="E85">
         <v>18016.901</v>
@@ -8251,37 +8361,37 @@
         <v>1181.9</v>
       </c>
       <c r="M85">
-        <v>5877.572175800001</v>
+        <v>5469.029160800001</v>
       </c>
       <c r="N85">
-        <v>-4695.6721758</v>
+        <v>-4287.129160800001</v>
       </c>
       <c r="O85">
-        <v>-1211.4834213564</v>
+        <v>-1106.0793234864</v>
       </c>
       <c r="P85">
-        <v>-3484.1887544436</v>
+        <v>-3181.049837313601</v>
       </c>
       <c r="Q85">
-        <v>-2729.0887544436</v>
+        <v>-2425.949837313601</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2994887776839659</v>
+        <v>0.2984734702712731</v>
       </c>
       <c r="T85">
-        <v>5.855096497817991</v>
+        <v>5.835415017812313</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.05188029868106141</v>
+        <v>0.05575581900086182</v>
       </c>
       <c r="W85">
-        <v>0.204604231544627</v>
+        <v>0.189604231544627</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2010864289963621</v>
+        <v>0.2161078255847356</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8410,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2478714611019549</v>
+        <v>0.2096620021281568</v>
       </c>
       <c r="C86">
-        <v>-20956.48853290992</v>
+        <v>-19421.04493349734</v>
       </c>
       <c r="D86">
-        <v>6607.859467090082</v>
+        <v>8143.303066502659</v>
       </c>
       <c r="E86">
         <v>18345.048</v>
@@ -8333,45 +8443,45 @@
         <v>1181.9</v>
       </c>
       <c r="M86">
-        <v>6775.3167384</v>
+        <v>5534.9210784</v>
       </c>
       <c r="N86">
-        <v>-5593.416738399999</v>
+        <v>-4353.021078399999</v>
       </c>
       <c r="O86">
-        <v>-1443.1015185072</v>
+        <v>-1123.0794382272</v>
       </c>
       <c r="P86">
-        <v>-4150.315219892799</v>
+        <v>-3229.941640172799</v>
       </c>
       <c r="Q86">
-        <v>-3395.215219892799</v>
+        <v>-2474.8416401728</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3168246807494657</v>
+        <v>0.3142655621632275</v>
       </c>
       <c r="T86">
-        <v>6.25520637359566</v>
+        <v>6.200128456425579</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.04500604352144424</v>
+        <v>0.05509205925085157</v>
       </c>
       <c r="W86">
-        <v>0.234737514502429</v>
+        <v>0.189737514502429</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.1744420291528848</v>
+        <v>0.2135351133753938</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8492,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2498714611019549</v>
+        <v>0.2112120021281568</v>
       </c>
       <c r="C87">
-        <v>-21349.39578337716</v>
+        <v>-19825.49909132558</v>
       </c>
       <c r="D87">
-        <v>6543.099216622831</v>
+        <v>8066.995908674416</v>
       </c>
       <c r="E87">
         <v>18673.195</v>
@@ -8415,45 +8525,45 @@
         <v>1181.9</v>
       </c>
       <c r="M87">
-        <v>6855.975270999999</v>
+        <v>5600.812996</v>
       </c>
       <c r="N87">
-        <v>-5674.075271</v>
+        <v>-4418.912995999999</v>
       </c>
       <c r="O87">
-        <v>-1463.911419918</v>
+        <v>-1140.079552968</v>
       </c>
       <c r="P87">
-        <v>-4210.163851081999</v>
+        <v>-3278.833443031999</v>
       </c>
       <c r="Q87">
-        <v>-3455.063851081999</v>
+        <v>-2523.733443031999</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3348929927994301</v>
+        <v>0.3321632663074427</v>
       </c>
       <c r="T87">
-        <v>6.672220131835371</v>
+        <v>6.613470353520617</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.04447656065648608</v>
+        <v>0.05444391737731213</v>
       </c>
       <c r="W87">
-        <v>0.2348676613906358</v>
+        <v>0.1898676613906357</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.1723897699863801</v>
+        <v>0.2110229355709774</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8574,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2518714611019549</v>
+        <v>0.2127620021281568</v>
       </c>
       <c r="C88">
-        <v>-21741.04598931974</v>
+        <v>-20228.53644661042</v>
       </c>
       <c r="D88">
-        <v>6479.596010680251</v>
+        <v>7992.105553389575</v>
       </c>
       <c r="E88">
         <v>19001.342</v>
@@ -8497,45 +8607,45 @@
         <v>1181.9</v>
       </c>
       <c r="M88">
-        <v>6936.6338036</v>
+        <v>5666.7049136</v>
       </c>
       <c r="N88">
-        <v>-5754.7338036</v>
+        <v>-4484.804913599999</v>
       </c>
       <c r="O88">
-        <v>-1484.7213213288</v>
+        <v>-1157.0796677088</v>
       </c>
       <c r="P88">
-        <v>-4270.0124822712</v>
+        <v>-3327.725245891199</v>
       </c>
       <c r="Q88">
-        <v>-3514.912482271201</v>
+        <v>-2572.625245891199</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3555424922851037</v>
+        <v>0.3526177853294029</v>
       </c>
       <c r="T88">
-        <v>7.148807284109326</v>
+        <v>7.085861093057804</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.04395939134652693</v>
+        <v>0.05381084857059921</v>
       </c>
       <c r="W88">
-        <v>0.2349947816070237</v>
+        <v>0.1899947816070237</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.1703852377772361</v>
+        <v>0.2085691805061985</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8656,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2538714611019549</v>
+        <v>0.2143120021281568</v>
       </c>
       <c r="C89">
-        <v>-22131.47539918378</v>
+        <v>-20630.19609527228</v>
       </c>
       <c r="D89">
-        <v>6417.313600816218</v>
+        <v>7918.592904727721</v>
       </c>
       <c r="E89">
         <v>19329.489</v>
@@ -8579,45 +8689,45 @@
         <v>1181.9</v>
       </c>
       <c r="M89">
-        <v>7017.2923362</v>
+        <v>5732.5968312</v>
       </c>
       <c r="N89">
-        <v>-5835.3923362</v>
+        <v>-4550.696831199999</v>
       </c>
       <c r="O89">
-        <v>-1505.5312227396</v>
+        <v>-1174.0797824496</v>
       </c>
       <c r="P89">
-        <v>-4329.8611134604</v>
+        <v>-3376.617048750399</v>
       </c>
       <c r="Q89">
-        <v>-3574.7611134604</v>
+        <v>-2621.517048750399</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3793688378454962</v>
+        <v>0.3762191534316647</v>
       </c>
       <c r="T89">
-        <v>7.698715536733121</v>
+        <v>7.630927330985328</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.04345411098622202</v>
+        <v>0.05319233306978773</v>
       </c>
       <c r="W89">
-        <v>0.2351189795195867</v>
+        <v>0.1901189795195866</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.1684267867683024</v>
+        <v>0.2061718336038284</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8738,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2558714611019549</v>
+        <v>0.2158620021281568</v>
       </c>
       <c r="C90">
-        <v>-22520.71888099196</v>
+        <v>-21030.51570790022</v>
       </c>
       <c r="D90">
-        <v>6356.217119008042</v>
+        <v>7846.420292099774</v>
       </c>
       <c r="E90">
         <v>19657.636</v>
@@ -8661,45 +8771,45 @@
         <v>1181.9</v>
       </c>
       <c r="M90">
-        <v>7097.9508688</v>
+        <v>5798.488748799999</v>
       </c>
       <c r="N90">
-        <v>-5916.050868799999</v>
+        <v>-4616.588748799999</v>
       </c>
       <c r="O90">
-        <v>-1526.3411241504</v>
+        <v>-1191.0798971904</v>
       </c>
       <c r="P90">
-        <v>-4389.709744649599</v>
+        <v>-3425.508851609599</v>
       </c>
       <c r="Q90">
-        <v>-3634.609744649599</v>
+        <v>-2670.408851609599</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4071662409992877</v>
+        <v>0.4037540828843035</v>
       </c>
       <c r="T90">
-        <v>8.340275164794216</v>
+        <v>8.266837941900773</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.04296031427046951</v>
+        <v>0.05258787473944922</v>
       </c>
       <c r="W90">
-        <v>0.2352403547523186</v>
+        <v>0.1902403547523186</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.1665128460095717</v>
+        <v>0.2038289718583304</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8820,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2578714611019549</v>
+        <v>0.2174120021281568</v>
       </c>
       <c r="C91">
-        <v>-22908.80998743589</v>
+        <v>-21429.53159411992</v>
       </c>
       <c r="D91">
-        <v>6296.273012564108</v>
+        <v>7775.551405880082</v>
       </c>
       <c r="E91">
         <v>19985.783</v>
@@ -8743,45 +8853,45 @@
         <v>1181.9</v>
       </c>
       <c r="M91">
-        <v>7178.6094014</v>
+        <v>5864.3806664</v>
       </c>
       <c r="N91">
-        <v>-5996.709401399999</v>
+        <v>-4682.480666400001</v>
       </c>
       <c r="O91">
-        <v>-1547.1510255612</v>
+        <v>-1208.0800119312</v>
       </c>
       <c r="P91">
-        <v>-4449.558375838799</v>
+        <v>-3474.4006544688</v>
       </c>
       <c r="Q91">
-        <v>-3694.458375838799</v>
+        <v>-2719.300654468801</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4400177174537683</v>
+        <v>0.436295363146513</v>
       </c>
       <c r="T91">
-        <v>9.098481997957325</v>
+        <v>9.018368663891755</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.04247761411012714</v>
+        <v>0.05199699974237675</v>
       </c>
       <c r="W91">
-        <v>0.2353590024517307</v>
+        <v>0.1903590024517308</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.1646419151555316</v>
+        <v>0.2015387586913827</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8902,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2598714611019549</v>
+        <v>0.2507713726970718</v>
       </c>
       <c r="C92">
-        <v>-23295.78101731968</v>
+        <v>-23023.16019437124</v>
       </c>
       <c r="D92">
-        <v>6237.448982680319</v>
+        <v>6510.069805628753</v>
       </c>
       <c r="E92">
         <v>20313.93</v>
@@ -8825,37 +8935,37 @@
         <v>1181.9</v>
       </c>
       <c r="M92">
-        <v>7259.267934</v>
+        <v>6963.935634</v>
       </c>
       <c r="N92">
-        <v>-6077.367934</v>
+        <v>-5782.035634</v>
       </c>
       <c r="O92">
-        <v>-1567.960926972</v>
+        <v>-1491.765193572</v>
       </c>
       <c r="P92">
-        <v>-4509.407007027999</v>
+        <v>-4290.270440427999</v>
       </c>
       <c r="Q92">
-        <v>-3754.307007028</v>
+        <v>-3535.170440427999</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4794394891991452</v>
+        <v>0.4784386051503148</v>
       </c>
       <c r="T92">
-        <v>10.00833019775306</v>
+        <v>9.991653698621588</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04200564062001462</v>
+        <v>0.04378705031551991</v>
       </c>
       <c r="W92">
-        <v>0.2354750135356004</v>
+        <v>0.2254750135356004</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8973,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1628125605426924</v>
+        <v>0.1697172492849609</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8984,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2618714611019549</v>
+        <v>0.2526713726970718</v>
       </c>
       <c r="C93">
-        <v>-23681.66307359106</v>
+        <v>-23411.09861195326</v>
       </c>
       <c r="D93">
-        <v>6179.713926408937</v>
+        <v>6450.27838804674</v>
       </c>
       <c r="E93">
         <v>20642.077</v>
@@ -8907,37 +9017,37 @@
         <v>1181.9</v>
       </c>
       <c r="M93">
-        <v>7339.9264666</v>
+        <v>7041.312696599999</v>
       </c>
       <c r="N93">
-        <v>-6158.0264666</v>
+        <v>-5859.412696599999</v>
       </c>
       <c r="O93">
-        <v>-1588.7708283828</v>
+        <v>-1511.7284757228</v>
       </c>
       <c r="P93">
-        <v>-4569.255638217201</v>
+        <v>-4347.684220877199</v>
       </c>
       <c r="Q93">
-        <v>-3814.155638217201</v>
+        <v>-3592.584220877199</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.527621654665717</v>
+        <v>0.5265095612781275</v>
       </c>
       <c r="T93">
-        <v>11.12036688639229</v>
+        <v>11.10183744291288</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04154404017364084</v>
+        <v>0.04330587393842629</v>
       </c>
       <c r="W93">
-        <v>0.2355884749253191</v>
+        <v>0.2255884749253191</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1610234115257396</v>
+        <v>0.1678522245675438</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9066,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2638714611019549</v>
+        <v>0.2545713726970719</v>
       </c>
       <c r="C94">
-        <v>-24066.48611817921</v>
+        <v>-23797.94872234125</v>
       </c>
       <c r="D94">
-        <v>6123.037881820787</v>
+        <v>6391.57527765875</v>
       </c>
       <c r="E94">
         <v>20970.224</v>
@@ -8989,37 +9099,37 @@
         <v>1181.9</v>
       </c>
       <c r="M94">
-        <v>7420.5849992</v>
+        <v>7118.6897592</v>
       </c>
       <c r="N94">
-        <v>-6238.684999200001</v>
+        <v>-5936.789759199999</v>
       </c>
       <c r="O94">
-        <v>-1609.5807297936</v>
+        <v>-1531.6917578736</v>
       </c>
       <c r="P94">
-        <v>-4629.1042694064</v>
+        <v>-4405.0980013264</v>
       </c>
       <c r="Q94">
-        <v>-3874.0042694064</v>
+        <v>-3649.9980013264</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5878493614989317</v>
+        <v>0.5865982564378937</v>
       </c>
       <c r="T94">
-        <v>12.51041274719133</v>
+        <v>12.48956712327699</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04109247451957952</v>
+        <v>0.04283515791735643</v>
       </c>
       <c r="W94">
-        <v>0.2356994697630874</v>
+        <v>0.2256994697630874</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1592731570526338</v>
+        <v>0.1660277438657227</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9148,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2658714611019549</v>
+        <v>0.2564713726970719</v>
       </c>
       <c r="C95">
-        <v>-24450.27902384241</v>
+        <v>-24183.73997116386</v>
       </c>
       <c r="D95">
-        <v>6067.391976157587</v>
+        <v>6333.931028836132</v>
       </c>
       <c r="E95">
         <v>21298.371</v>
@@ -9071,37 +9181,37 @@
         <v>1181.9</v>
       </c>
       <c r="M95">
-        <v>7501.2435318</v>
+        <v>7196.0668218</v>
       </c>
       <c r="N95">
-        <v>-6319.343531799999</v>
+        <v>-6014.1668218</v>
       </c>
       <c r="O95">
-        <v>-1630.3906312044</v>
+        <v>-1551.6550400244</v>
       </c>
       <c r="P95">
-        <v>-4688.952900595599</v>
+        <v>-4462.5117817756</v>
       </c>
       <c r="Q95">
-        <v>-3933.852900595599</v>
+        <v>-3707.4117817756</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6652849845702078</v>
+        <v>0.6638551502147356</v>
       </c>
       <c r="T95">
-        <v>14.29761456821866</v>
+        <v>14.27379099803085</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04065061995485286</v>
+        <v>0.04237456482147087</v>
       </c>
       <c r="W95">
-        <v>0.2358080776150972</v>
+        <v>0.2258080776150972</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1575605424606701</v>
+        <v>0.1642424993080267</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9230,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2678714611019549</v>
+        <v>0.2583713726970718</v>
       </c>
       <c r="C96">
-        <v>-24833.06962321399</v>
+        <v>-24568.50075128909</v>
       </c>
       <c r="D96">
-        <v>6012.748376786015</v>
+        <v>6277.317248710911</v>
       </c>
       <c r="E96">
         <v>21626.518</v>
@@ -9153,37 +9263,37 @@
         <v>1181.9</v>
       </c>
       <c r="M96">
-        <v>7581.9020644</v>
+        <v>7273.443884400001</v>
       </c>
       <c r="N96">
-        <v>-6400.0020644</v>
+        <v>-6091.5438844</v>
       </c>
       <c r="O96">
-        <v>-1651.2005326152</v>
+        <v>-1571.6183221752</v>
       </c>
       <c r="P96">
-        <v>-4748.801531784799</v>
+        <v>-4519.9255622248</v>
       </c>
       <c r="Q96">
-        <v>-3993.701531784799</v>
+        <v>-3764.8255622248</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7685324819985759</v>
+        <v>0.7668643419171919</v>
       </c>
       <c r="T96">
-        <v>16.68055032958845</v>
+        <v>16.65275616436933</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04021816655107783</v>
+        <v>0.04192377157868928</v>
       </c>
       <c r="W96">
-        <v>0.2359143746617451</v>
+        <v>0.2259143746617451</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9301,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.155884366477046</v>
+        <v>0.1624952386770903</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9312,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2698714611019549</v>
+        <v>0.2602713726970719</v>
       </c>
       <c r="C97">
-        <v>-25214.88475522166</v>
+        <v>-24952.25844945624</v>
       </c>
       <c r="D97">
-        <v>5959.080244778342</v>
+        <v>6221.706550543762</v>
       </c>
       <c r="E97">
         <v>21954.665</v>
@@ -9235,37 +9345,37 @@
         <v>1181.9</v>
       </c>
       <c r="M97">
-        <v>7662.560597000001</v>
+        <v>7350.820947</v>
       </c>
       <c r="N97">
-        <v>-6480.660597</v>
+        <v>-6168.920947000001</v>
       </c>
       <c r="O97">
-        <v>-1672.010434026</v>
+        <v>-1591.581604326</v>
       </c>
       <c r="P97">
-        <v>-4808.650162974</v>
+        <v>-4577.339342674</v>
       </c>
       <c r="Q97">
-        <v>-4053.550162974</v>
+        <v>-3822.239342674</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.9130789783982914</v>
+        <v>0.9110772103006307</v>
       </c>
       <c r="T97">
-        <v>20.01666039550614</v>
+        <v>19.98330739724321</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03979481742948753</v>
+        <v>0.04148246871996623</v>
       </c>
       <c r="W97">
-        <v>0.236018433875832</v>
+        <v>0.226018433875832</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1542434784088664</v>
+        <v>0.1607847624804892</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9394,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2718714611019549</v>
+        <v>0.2621713726970718</v>
       </c>
       <c r="C98">
-        <v>-25595.75030904293</v>
+        <v>-25335.03949045103</v>
       </c>
       <c r="D98">
-        <v>5906.36169095707</v>
+        <v>6167.072509548967</v>
       </c>
       <c r="E98">
         <v>22282.812</v>
@@ -9317,37 +9427,37 @@
         <v>1181.9</v>
       </c>
       <c r="M98">
-        <v>7743.2191296</v>
+        <v>7428.1980096</v>
       </c>
       <c r="N98">
-        <v>-6561.3191296</v>
+        <v>-6246.298009599999</v>
       </c>
       <c r="O98">
-        <v>-1692.8203354368</v>
+        <v>-1611.5448864768</v>
       </c>
       <c r="P98">
-        <v>-4868.498794163201</v>
+        <v>-4634.7531231232</v>
       </c>
       <c r="Q98">
-        <v>-4113.3987941632</v>
+        <v>-3879.6531231232</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.129898722997862</v>
+        <v>1.127396512875786</v>
       </c>
       <c r="T98">
-        <v>25.02082549438262</v>
+        <v>24.97913424655394</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0393802880812637</v>
+        <v>0.04105035967079992</v>
       </c>
       <c r="W98">
-        <v>0.2361203251896254</v>
+        <v>0.2261203251896254</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.152636775508774</v>
+        <v>0.1591099212046508</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9476,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2738714611019549</v>
+        <v>0.2640713726970718</v>
       </c>
       <c r="C99">
-        <v>-25975.69126574772</v>
+        <v>-25716.8693789735</v>
       </c>
       <c r="D99">
-        <v>5854.567734252274</v>
+        <v>6113.389621026497</v>
       </c>
       <c r="E99">
         <v>22610.959</v>
@@ -9399,37 +9509,37 @@
         <v>1181.9</v>
       </c>
       <c r="M99">
-        <v>7823.8776622</v>
+        <v>7505.575072199999</v>
       </c>
       <c r="N99">
-        <v>-6641.977662199999</v>
+        <v>-6323.6750722</v>
       </c>
       <c r="O99">
-        <v>-1713.6302368476</v>
+        <v>-1631.5081686276</v>
       </c>
       <c r="P99">
-        <v>-4928.347425352399</v>
+        <v>-4692.1669035724</v>
       </c>
       <c r="Q99">
-        <v>-4173.2474253524</v>
+        <v>-3937.0669035724</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.49126496399715</v>
+        <v>1.487928683834381</v>
       </c>
       <c r="T99">
-        <v>33.36110065917683</v>
+        <v>33.3055123287386</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03897430572991048</v>
+        <v>0.04062716008656486</v>
       </c>
       <c r="W99">
-        <v>0.236220115651588</v>
+        <v>0.226220115651588</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1510632005035291</v>
+        <v>0.1574696127386235</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9558,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2758714611019549</v>
+        <v>0.2659713726970718</v>
       </c>
       <c r="C100">
-        <v>-26354.73173776907</v>
+        <v>-26097.77273933799</v>
       </c>
       <c r="D100">
-        <v>5803.67426223092</v>
+        <v>6060.63326066201</v>
       </c>
       <c r="E100">
         <v>22939.106</v>
@@ -9481,37 +9591,37 @@
         <v>1181.9</v>
       </c>
       <c r="M100">
-        <v>7904.536194799999</v>
+        <v>7582.952134799999</v>
       </c>
       <c r="N100">
-        <v>-6722.636194799999</v>
+        <v>-6401.052134799998</v>
       </c>
       <c r="O100">
-        <v>-1734.4401382584</v>
+        <v>-1651.4714507784</v>
       </c>
       <c r="P100">
-        <v>-4988.196056541599</v>
+        <v>-4749.580684021599</v>
       </c>
       <c r="Q100">
-        <v>-4233.096056541599</v>
+        <v>-3994.480684021599</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.213997445995724</v>
+        <v>2.208993025751572</v>
       </c>
       <c r="T100">
-        <v>50.04165098876525</v>
+        <v>49.95826849310789</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0385766087326665</v>
+        <v>0.0402125972285387</v>
       </c>
       <c r="W100">
-        <v>0.2363178695735106</v>
+        <v>0.2263178695735106</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9629,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1495217392739011</v>
+        <v>0.1558627799555764</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9640,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2778714611019549</v>
+        <v>0.2678713726970718</v>
       </c>
       <c r="C101">
-        <v>-26732.89500633284</v>
+        <v>-26477.77335313523</v>
       </c>
       <c r="D101">
-        <v>5753.657993667151</v>
+        <v>6008.779646864766</v>
       </c>
       <c r="E101">
         <v>23267.253</v>
@@ -9563,37 +9673,37 @@
         <v>1181.9</v>
       </c>
       <c r="M101">
-        <v>7985.194727399999</v>
+        <v>7660.329197399999</v>
       </c>
       <c r="N101">
-        <v>-6803.2947274</v>
+        <v>-6478.429197399999</v>
       </c>
       <c r="O101">
-        <v>-1755.2500396692</v>
+        <v>-1671.4347329292</v>
       </c>
       <c r="P101">
-        <v>-5048.0446877308</v>
+        <v>-4806.994464470799</v>
       </c>
       <c r="Q101">
-        <v>-4292.9446877308</v>
+        <v>-4051.894464470799</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.382194891991447</v>
+        <v>4.372186051503142</v>
       </c>
       <c r="T101">
-        <v>100.0833019775305</v>
+        <v>99.91653698621577</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.03818694601819512</v>
+        <v>0.03980640937774538</v>
       </c>
       <c r="W101">
-        <v>0.2364136486687276</v>
+        <v>0.2264136486687277</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9711,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1480114186751748</v>
+        <v>0.1542884084408735</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_healthcare_products.xlsx
@@ -1382,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1519,22 +1519,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09083876366469271</v>
+        <v>0.09063778965443781</v>
       </c>
       <c r="C2">
-        <v>29627.32179656933</v>
+        <v>29431.97174576014</v>
       </c>
       <c r="D2">
-        <v>29627.32179656933</v>
+        <v>29760.11874576014</v>
       </c>
       <c r="E2">
-        <v>-9219.299999999999</v>
+        <v>-8891.152999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>328.147</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1555,28 +1555,28 @@
         <v>1181.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>16.5057941</v>
       </c>
       <c r="N2">
-        <v>1181.9</v>
+        <v>1165.3942059</v>
       </c>
       <c r="O2">
-        <v>304.9302</v>
+        <v>300.6717051222</v>
       </c>
       <c r="P2">
-        <v>876.9698000000001</v>
+        <v>864.7225007778001</v>
       </c>
       <c r="Q2">
-        <v>1632.0698</v>
+        <v>1619.8225007778</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09083876366469271</v>
+        <v>0.09117632692367454</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.047952122948604</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>71.60515833648986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1601,22 +1601,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09063778965443781</v>
+        <v>0.09043681564418288</v>
       </c>
       <c r="C3">
-        <v>29431.97174576014</v>
+        <v>29237.8175121276</v>
       </c>
       <c r="D3">
-        <v>29760.11874576014</v>
+        <v>29894.1115121276</v>
       </c>
       <c r="E3">
-        <v>-8891.152999999998</v>
+        <v>-8563.005999999999</v>
       </c>
       <c r="F3">
-        <v>328.147</v>
+        <v>656.294</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1637,28 +1637,28 @@
         <v>1181.9</v>
       </c>
       <c r="M3">
-        <v>16.5057941</v>
+        <v>33.0115882</v>
       </c>
       <c r="N3">
-        <v>1165.3942059</v>
+        <v>1148.8884118</v>
       </c>
       <c r="O3">
-        <v>300.6717051222</v>
+        <v>296.4132102444</v>
       </c>
       <c r="P3">
-        <v>864.7225007778001</v>
+        <v>852.4752015556001</v>
       </c>
       <c r="Q3">
-        <v>1619.8225007778</v>
+        <v>1607.5752015556</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09117632692367454</v>
+        <v>0.09152077922875805</v>
       </c>
       <c r="T3">
-        <v>1.047952122948604</v>
+        <v>1.055907141541756</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>71.60515833648986</v>
+        <v>35.80257916824493</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1683,22 +1683,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09043681564418288</v>
+        <v>0.09023584163392798</v>
       </c>
       <c r="C4">
-        <v>29237.8175121276</v>
+        <v>29044.875320964</v>
       </c>
       <c r="D4">
-        <v>29894.1115121276</v>
+        <v>30029.316320964</v>
       </c>
       <c r="E4">
-        <v>-8563.005999999999</v>
+        <v>-8234.858999999999</v>
       </c>
       <c r="F4">
-        <v>656.294</v>
+        <v>984.4409999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1719,28 +1719,28 @@
         <v>1181.9</v>
       </c>
       <c r="M4">
-        <v>33.0115882</v>
+        <v>49.51738229999999</v>
       </c>
       <c r="N4">
-        <v>1148.8884118</v>
+        <v>1132.3826177</v>
       </c>
       <c r="O4">
-        <v>296.4132102444</v>
+        <v>292.1547153666</v>
       </c>
       <c r="P4">
-        <v>852.4752015556001</v>
+        <v>840.2279023334</v>
       </c>
       <c r="Q4">
-        <v>1607.5752015556</v>
+        <v>1595.3279023334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09152077922875805</v>
+        <v>0.09187233364322472</v>
       </c>
       <c r="T4">
-        <v>1.055907141541756</v>
+        <v>1.06402618113683</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.80257916824493</v>
+        <v>23.86838611216329</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1765,22 +1765,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09023584163392798</v>
+        <v>0.09003486762367308</v>
       </c>
       <c r="C5">
-        <v>29044.875320964</v>
+        <v>28853.1616924297</v>
       </c>
       <c r="D5">
-        <v>30029.316320964</v>
+        <v>30165.7496924297</v>
       </c>
       <c r="E5">
-        <v>-8234.858999999999</v>
+        <v>-7906.712</v>
       </c>
       <c r="F5">
-        <v>984.4409999999999</v>
+        <v>1312.588</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1801,28 +1801,28 @@
         <v>1181.9</v>
       </c>
       <c r="M5">
-        <v>49.51738229999999</v>
+        <v>66.0231764</v>
       </c>
       <c r="N5">
-        <v>1132.3826177</v>
+        <v>1115.8768236</v>
       </c>
       <c r="O5">
-        <v>292.1547153666</v>
+        <v>287.8962204888001</v>
       </c>
       <c r="P5">
-        <v>840.2279023334</v>
+        <v>827.9806031112</v>
       </c>
       <c r="Q5">
-        <v>1595.3279023334</v>
+        <v>1583.0806031112</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09187233364322472</v>
+        <v>0.09223121210799279</v>
       </c>
       <c r="T5">
-        <v>1.06402618113683</v>
+        <v>1.072314367390134</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.86838611216329</v>
+        <v>17.90128958412247</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09003486762367308</v>
+        <v>0.08983389361341818</v>
       </c>
       <c r="C6">
-        <v>28853.1616924297</v>
+        <v>28662.69344828212</v>
       </c>
       <c r="D6">
-        <v>30165.7496924297</v>
+        <v>30303.42844828212</v>
       </c>
       <c r="E6">
-        <v>-7906.712</v>
+        <v>-7578.565</v>
       </c>
       <c r="F6">
-        <v>1312.588</v>
+        <v>1640.735</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1883,28 +1883,28 @@
         <v>1181.9</v>
       </c>
       <c r="M6">
-        <v>66.0231764</v>
+        <v>82.52897049999999</v>
       </c>
       <c r="N6">
-        <v>1115.8768236</v>
+        <v>1099.3710295</v>
       </c>
       <c r="O6">
-        <v>287.8962204888001</v>
+        <v>283.637725611</v>
       </c>
       <c r="P6">
-        <v>827.9806031112</v>
+        <v>815.7333038890001</v>
       </c>
       <c r="Q6">
-        <v>1583.0806031112</v>
+        <v>1570.833303889</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09223121210799279</v>
+        <v>0.09259764590886124</v>
       </c>
       <c r="T6">
-        <v>1.072314367390134</v>
+        <v>1.080777041775086</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.90128958412247</v>
+        <v>14.32103166729797</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08983389361341818</v>
+        <v>0.08963291960316326</v>
       </c>
       <c r="C7">
-        <v>28662.69344828212</v>
+        <v>28473.48771878979</v>
       </c>
       <c r="D7">
-        <v>30303.42844828212</v>
+        <v>30442.36971878979</v>
       </c>
       <c r="E7">
-        <v>-7578.565</v>
+        <v>-7250.418</v>
       </c>
       <c r="F7">
-        <v>1640.735</v>
+        <v>1968.882</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1965,28 +1965,28 @@
         <v>1181.9</v>
       </c>
       <c r="M7">
-        <v>82.52897049999999</v>
+        <v>99.0347646</v>
       </c>
       <c r="N7">
-        <v>1099.3710295</v>
+        <v>1082.8652354</v>
       </c>
       <c r="O7">
-        <v>283.637725611</v>
+        <v>279.3792307332</v>
       </c>
       <c r="P7">
-        <v>815.7333038890001</v>
+        <v>803.4860046668</v>
       </c>
       <c r="Q7">
-        <v>1570.833303889</v>
+        <v>1558.5860046668</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09259764590886124</v>
+        <v>0.09297187617357794</v>
       </c>
       <c r="T7">
-        <v>1.080777041775086</v>
+        <v>1.089419773061846</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>14.32103166729797</v>
+        <v>11.93419305608164</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2011,22 +2011,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08963291960316326</v>
+        <v>0.08943194559290837</v>
       </c>
       <c r="C8">
-        <v>28473.48771878979</v>
+        <v>28285.56194983757</v>
       </c>
       <c r="D8">
-        <v>30442.36971878979</v>
+        <v>30582.59094983757</v>
       </c>
       <c r="E8">
-        <v>-7250.418</v>
+        <v>-6922.271</v>
       </c>
       <c r="F8">
-        <v>1968.882</v>
+        <v>2297.029</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2047,28 +2047,28 @@
         <v>1181.9</v>
       </c>
       <c r="M8">
-        <v>99.03476459999999</v>
+        <v>115.5405587</v>
       </c>
       <c r="N8">
-        <v>1082.8652354</v>
+        <v>1066.3594413</v>
       </c>
       <c r="O8">
-        <v>279.3792307332</v>
+        <v>275.1207358554</v>
       </c>
       <c r="P8">
-        <v>803.4860046668</v>
+        <v>791.2387054446001</v>
       </c>
       <c r="Q8">
-        <v>1558.5860046668</v>
+        <v>1546.3387054446</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09297187617357794</v>
+        <v>0.09335415440097673</v>
       </c>
       <c r="T8">
-        <v>1.089419773061846</v>
+        <v>1.098248369537569</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.93419305608164</v>
+        <v>10.22930833378427</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08943194559290836</v>
+        <v>0.08923097158265346</v>
       </c>
       <c r="C9">
-        <v>28285.56194983758</v>
+        <v>28098.93391022917</v>
       </c>
       <c r="D9">
-        <v>30582.59094983758</v>
+        <v>30724.10991022917</v>
       </c>
       <c r="E9">
-        <v>-6922.270999999999</v>
+        <v>-6594.124</v>
       </c>
       <c r="F9">
-        <v>2297.029</v>
+        <v>2625.176</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2129,28 +2129,28 @@
         <v>1181.9</v>
       </c>
       <c r="M9">
-        <v>115.5405587</v>
+        <v>132.0463528</v>
       </c>
       <c r="N9">
-        <v>1066.3594413</v>
+        <v>1049.8536472</v>
       </c>
       <c r="O9">
-        <v>275.1207358554</v>
+        <v>270.8622409776</v>
       </c>
       <c r="P9">
-        <v>791.2387054446001</v>
+        <v>778.9914062224</v>
       </c>
       <c r="Q9">
-        <v>1546.3387054446</v>
+        <v>1534.0914062224</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09335415440097673</v>
+        <v>0.09374474302462331</v>
       </c>
       <c r="T9">
-        <v>1.098248369537569</v>
+        <v>1.107268892023633</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.22930833378427</v>
+        <v>8.950644792061233</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08923097158265346</v>
+        <v>0.08913016757239853</v>
       </c>
       <c r="C10">
-        <v>28098.93391022917</v>
+        <v>27842.26398183961</v>
       </c>
       <c r="D10">
-        <v>30724.10991022917</v>
+        <v>30795.58698183961</v>
       </c>
       <c r="E10">
-        <v>-6594.124</v>
+        <v>-6265.977</v>
       </c>
       <c r="F10">
-        <v>2625.176</v>
+        <v>2953.322999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2211,45 +2211,45 @@
         <v>1181.9</v>
       </c>
       <c r="M10">
-        <v>132.0463528</v>
+        <v>152.9821314</v>
       </c>
       <c r="N10">
-        <v>1049.8536472</v>
+        <v>1028.9178686</v>
       </c>
       <c r="O10">
-        <v>270.8622409776</v>
+        <v>265.4608100988</v>
       </c>
       <c r="P10">
-        <v>778.9914062224</v>
+        <v>763.4570585012</v>
       </c>
       <c r="Q10">
-        <v>1534.0914062224</v>
+        <v>1518.5570585012</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09374474302462331</v>
+        <v>0.09414391601362476</v>
       </c>
       <c r="T10">
-        <v>1.107268892023633</v>
+        <v>1.116487667751149</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.950644792061233</v>
+        <v>7.725738876716947</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08913016757239853</v>
+        <v>0.08894032356214364</v>
       </c>
       <c r="C11">
-        <v>27842.26398183961</v>
+        <v>27649.63654330892</v>
       </c>
       <c r="D11">
-        <v>30795.58698183961</v>
+        <v>30931.10654330891</v>
       </c>
       <c r="E11">
-        <v>-6265.977</v>
+        <v>-5937.83</v>
       </c>
       <c r="F11">
-        <v>2953.322999999999</v>
+        <v>3281.469999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2293,28 +2293,28 @@
         <v>1181.9</v>
       </c>
       <c r="M11">
-        <v>152.9821314</v>
+        <v>169.980146</v>
       </c>
       <c r="N11">
-        <v>1028.9178686</v>
+        <v>1011.919854</v>
       </c>
       <c r="O11">
-        <v>265.4608100988</v>
+        <v>261.075322332</v>
       </c>
       <c r="P11">
-        <v>763.4570585012</v>
+        <v>750.8445316680001</v>
       </c>
       <c r="Q11">
-        <v>1518.5570585012</v>
+        <v>1505.944531668</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09414391601362476</v>
+        <v>0.09455195951349293</v>
       </c>
       <c r="T11">
-        <v>1.116487667751149</v>
+        <v>1.1259113051615</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.725738876716947</v>
+        <v>6.953164989045252</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2339,22 +2339,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08894032356214364</v>
+        <v>0.08888923355188874</v>
       </c>
       <c r="C12">
-        <v>27649.63654330891</v>
+        <v>27358.16391461306</v>
       </c>
       <c r="D12">
-        <v>30931.10654330891</v>
+        <v>30967.78091461306</v>
       </c>
       <c r="E12">
-        <v>-5937.83</v>
+        <v>-5609.682999999999</v>
       </c>
       <c r="F12">
-        <v>3281.47</v>
+        <v>3609.617</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2375,45 +2375,45 @@
         <v>1181.9</v>
       </c>
       <c r="M12">
-        <v>169.980146</v>
+        <v>193.1145095</v>
       </c>
       <c r="N12">
-        <v>1011.919854</v>
+        <v>988.7854905000002</v>
       </c>
       <c r="O12">
-        <v>261.075322332</v>
+        <v>255.106656549</v>
       </c>
       <c r="P12">
-        <v>750.8445316680001</v>
+        <v>733.6788339510001</v>
       </c>
       <c r="Q12">
-        <v>1505.944531668</v>
+        <v>1488.778833951</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09455195951349293</v>
+        <v>0.09496917253021206</v>
       </c>
       <c r="T12">
-        <v>1.1259113051615</v>
+        <v>1.135546709704666</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.953164989045251</v>
+        <v>6.120202998004147</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2421,22 +2421,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08888923355188874</v>
+        <v>0.08871200354163382</v>
       </c>
       <c r="C13">
-        <v>27358.16391461306</v>
+        <v>27157.91632913804</v>
       </c>
       <c r="D13">
-        <v>30967.78091461306</v>
+        <v>31095.68032913804</v>
       </c>
       <c r="E13">
-        <v>-5609.682999999999</v>
+        <v>-5281.536</v>
       </c>
       <c r="F13">
-        <v>3609.617</v>
+        <v>3937.764</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2457,28 +2457,28 @@
         <v>1181.9</v>
       </c>
       <c r="M13">
-        <v>193.1145095</v>
+        <v>210.670374</v>
       </c>
       <c r="N13">
-        <v>988.7854905000002</v>
+        <v>971.2296260000001</v>
       </c>
       <c r="O13">
-        <v>255.106656549</v>
+        <v>250.577243508</v>
       </c>
       <c r="P13">
-        <v>733.6788339510001</v>
+        <v>720.652382492</v>
       </c>
       <c r="Q13">
-        <v>1488.778833951</v>
+        <v>1475.752382492</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09496917253021206</v>
+        <v>0.09539586766094753</v>
       </c>
       <c r="T13">
-        <v>1.135546709704666</v>
+        <v>1.145401100714724</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.120202998004147</v>
+        <v>5.610186081503801</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2503,22 +2503,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08871200354163382</v>
+        <v>0.08861194153137891</v>
       </c>
       <c r="C14">
-        <v>27157.91632913804</v>
+        <v>26902.44756265606</v>
       </c>
       <c r="D14">
-        <v>31095.68032913804</v>
+        <v>31168.35856265606</v>
       </c>
       <c r="E14">
-        <v>-5281.536</v>
+        <v>-4953.388999999999</v>
       </c>
       <c r="F14">
-        <v>3937.764</v>
+        <v>4265.911</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2539,45 +2539,45 @@
         <v>1181.9</v>
       </c>
       <c r="M14">
-        <v>210.670374</v>
+        <v>231.6389673</v>
       </c>
       <c r="N14">
-        <v>971.2296260000001</v>
+        <v>950.2610327000001</v>
       </c>
       <c r="O14">
-        <v>250.577243508</v>
+        <v>245.1673464366</v>
       </c>
       <c r="P14">
-        <v>720.652382492</v>
+        <v>705.0936862634001</v>
       </c>
       <c r="Q14">
-        <v>1475.752382492</v>
+        <v>1460.1936862634</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09539586766094753</v>
+        <v>0.09583237187514818</v>
       </c>
       <c r="T14">
-        <v>1.145401100714724</v>
+        <v>1.15548202944915</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>5.610186081503801</v>
+        <v>5.102336682710638</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08861194153137891</v>
+        <v>0.08844064752112402</v>
       </c>
       <c r="C15">
-        <v>26902.44756265606</v>
+        <v>26699.50863152076</v>
       </c>
       <c r="D15">
-        <v>31168.35856265606</v>
+        <v>31293.56663152076</v>
       </c>
       <c r="E15">
-        <v>-4953.388999999999</v>
+        <v>-4625.241999999999</v>
       </c>
       <c r="F15">
-        <v>4265.911</v>
+        <v>4594.058</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2621,28 +2621,28 @@
         <v>1181.9</v>
       </c>
       <c r="M15">
-        <v>231.6389673</v>
+        <v>249.4573494</v>
       </c>
       <c r="N15">
-        <v>950.2610327000001</v>
+        <v>932.4426506000001</v>
       </c>
       <c r="O15">
-        <v>245.1673464366</v>
+        <v>240.5702038548</v>
       </c>
       <c r="P15">
-        <v>705.0936862634001</v>
+        <v>691.8724467452</v>
       </c>
       <c r="Q15">
-        <v>1460.1936862634</v>
+        <v>1446.9724467452</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09583237187514818</v>
+        <v>0.09627902735014419</v>
       </c>
       <c r="T15">
-        <v>1.15548202944915</v>
+        <v>1.165797398386702</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.102336682710638</v>
+        <v>4.737884062517022</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2667,22 +2667,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08844064752112402</v>
+        <v>0.08826935351086911</v>
       </c>
       <c r="C16">
-        <v>26699.50863152076</v>
+        <v>26497.57971774899</v>
       </c>
       <c r="D16">
-        <v>31293.56663152076</v>
+        <v>31419.784717749</v>
       </c>
       <c r="E16">
-        <v>-4625.241999999999</v>
+        <v>-4297.094999999999</v>
       </c>
       <c r="F16">
-        <v>4594.058</v>
+        <v>4922.205</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2703,28 +2703,28 @@
         <v>1181.9</v>
       </c>
       <c r="M16">
-        <v>249.4573494</v>
+        <v>267.2757315</v>
       </c>
       <c r="N16">
-        <v>932.4426506000001</v>
+        <v>914.6242685000001</v>
       </c>
       <c r="O16">
-        <v>240.5702038548</v>
+        <v>235.973061273</v>
       </c>
       <c r="P16">
-        <v>691.8724467452</v>
+        <v>678.651207227</v>
       </c>
       <c r="Q16">
-        <v>1446.9724467452</v>
+        <v>1433.751207227</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09627902735014419</v>
+        <v>0.09673619236572836</v>
       </c>
       <c r="T16">
-        <v>1.165797398386702</v>
+        <v>1.176355481887491</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.737884062517022</v>
+        <v>4.422025125015887</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2749,22 +2749,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08826935351086911</v>
+        <v>0.08821677950061418</v>
       </c>
       <c r="C17">
-        <v>26497.579717749</v>
+        <v>26208.37636465963</v>
       </c>
       <c r="D17">
-        <v>31419.784717749</v>
+        <v>31458.72836465963</v>
       </c>
       <c r="E17">
-        <v>-4297.095</v>
+        <v>-3968.947999999999</v>
       </c>
       <c r="F17">
-        <v>4922.204999999999</v>
+        <v>5250.352</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2785,45 +2785,45 @@
         <v>1181.9</v>
       </c>
       <c r="M17">
-        <v>267.2757314999999</v>
+        <v>290.3444656</v>
       </c>
       <c r="N17">
-        <v>914.6242685000002</v>
+        <v>891.5555344000002</v>
       </c>
       <c r="O17">
-        <v>235.9730612730001</v>
+        <v>230.0213278752001</v>
       </c>
       <c r="P17">
-        <v>678.6512072270001</v>
+        <v>661.5342065248001</v>
       </c>
       <c r="Q17">
-        <v>1433.751207227</v>
+        <v>1416.6342065248</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09673619236572836</v>
+        <v>0.09720424226263594</v>
       </c>
       <c r="T17">
-        <v>1.176355481887491</v>
+        <v>1.187164948328775</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.422025125015888</v>
+        <v>4.070682034725859</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2831,22 +2831,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08821677950061418</v>
+        <v>0.08805290549035928</v>
       </c>
       <c r="C18">
-        <v>26208.37636465963</v>
+        <v>26002.23915108279</v>
       </c>
       <c r="D18">
-        <v>31458.72836465963</v>
+        <v>31580.73815108279</v>
       </c>
       <c r="E18">
-        <v>-3968.947999999999</v>
+        <v>-3640.800999999999</v>
       </c>
       <c r="F18">
-        <v>5250.352</v>
+        <v>5578.499</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2867,28 +2867,28 @@
         <v>1181.9</v>
       </c>
       <c r="M18">
-        <v>290.3444656</v>
+        <v>308.4909947</v>
       </c>
       <c r="N18">
-        <v>891.5555344000002</v>
+        <v>873.4090053000001</v>
       </c>
       <c r="O18">
-        <v>230.0213278752001</v>
+        <v>225.3395233674</v>
       </c>
       <c r="P18">
-        <v>661.5342065248001</v>
+        <v>648.0694819326001</v>
       </c>
       <c r="Q18">
-        <v>1416.6342065248</v>
+        <v>1403.1694819326</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09720424226263594</v>
+        <v>0.0976835704703124</v>
       </c>
       <c r="T18">
-        <v>1.187164948328775</v>
+        <v>1.198234883840933</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.070682034725859</v>
+        <v>3.83123015033022</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08805290549035928</v>
+        <v>0.08788903148010438</v>
       </c>
       <c r="C19">
-        <v>26002.23915108279</v>
+        <v>25797.05202983586</v>
       </c>
       <c r="D19">
-        <v>31580.73815108279</v>
+        <v>31703.69802983586</v>
       </c>
       <c r="E19">
-        <v>-3640.800999999999</v>
+        <v>-3312.654</v>
       </c>
       <c r="F19">
-        <v>5578.499</v>
+        <v>5906.646</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2949,28 +2949,28 @@
         <v>1181.9</v>
       </c>
       <c r="M19">
-        <v>308.4909947</v>
+        <v>326.6375238</v>
       </c>
       <c r="N19">
-        <v>873.4090053000001</v>
+        <v>855.2624762</v>
       </c>
       <c r="O19">
-        <v>225.3395233674</v>
+        <v>220.6577188596</v>
       </c>
       <c r="P19">
-        <v>648.0694819326001</v>
+        <v>634.6047573404001</v>
       </c>
       <c r="Q19">
-        <v>1403.1694819326</v>
+        <v>1389.7047573404</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0976835704703124</v>
+        <v>0.09817458960988339</v>
       </c>
       <c r="T19">
-        <v>1.198234883840933</v>
+        <v>1.209574817780217</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.83123015033022</v>
+        <v>3.61838403086743</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2995,22 +2995,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08788903148010439</v>
+        <v>0.08772515746984949</v>
       </c>
       <c r="C20">
-        <v>25797.05202983585</v>
+        <v>25592.82614187451</v>
       </c>
       <c r="D20">
-        <v>31703.69802983585</v>
+        <v>31827.61914187451</v>
       </c>
       <c r="E20">
-        <v>-3312.654</v>
+        <v>-2984.507</v>
       </c>
       <c r="F20">
-        <v>5906.645999999999</v>
+        <v>6234.793</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3031,28 +3031,28 @@
         <v>1181.9</v>
       </c>
       <c r="M20">
-        <v>326.6375237999999</v>
+        <v>344.7840529</v>
       </c>
       <c r="N20">
-        <v>855.2624762000002</v>
+        <v>837.1159471000001</v>
       </c>
       <c r="O20">
-        <v>220.6577188596</v>
+        <v>215.9759143518</v>
       </c>
       <c r="P20">
-        <v>634.6047573404001</v>
+        <v>621.1400327482</v>
       </c>
       <c r="Q20">
-        <v>1389.7047573404</v>
+        <v>1376.2400327482</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09817458960988339</v>
+        <v>0.09867773267882651</v>
       </c>
       <c r="T20">
-        <v>1.209574817780217</v>
+        <v>1.221194750088372</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.618384030867431</v>
+        <v>3.427942766084934</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3077,22 +3077,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08772515746984949</v>
+        <v>0.08756128345959456</v>
       </c>
       <c r="C21">
-        <v>25592.82614187451</v>
+        <v>25389.5728030258</v>
       </c>
       <c r="D21">
-        <v>31827.61914187451</v>
+        <v>31952.5128030258</v>
       </c>
       <c r="E21">
-        <v>-2984.507</v>
+        <v>-2656.36</v>
       </c>
       <c r="F21">
-        <v>6234.793</v>
+        <v>6562.94</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3113,28 +3113,28 @@
         <v>1181.9</v>
       </c>
       <c r="M21">
-        <v>344.7840529</v>
+        <v>362.930582</v>
       </c>
       <c r="N21">
-        <v>837.1159471000001</v>
+        <v>818.9694180000001</v>
       </c>
       <c r="O21">
-        <v>215.9759143518</v>
+        <v>211.294109844</v>
       </c>
       <c r="P21">
-        <v>621.1400327482</v>
+        <v>607.675308156</v>
       </c>
       <c r="Q21">
-        <v>1376.2400327482</v>
+        <v>1362.775308156</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09867773267882651</v>
+        <v>0.0991934543244932</v>
       </c>
       <c r="T21">
-        <v>1.221194750088372</v>
+        <v>1.233105180704231</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.427942766084934</v>
+        <v>3.256545627780687</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3159,22 +3159,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08756128345959456</v>
+        <v>0.08739740944933966</v>
       </c>
       <c r="C22">
-        <v>25389.5728030258</v>
+        <v>25187.30350743261</v>
       </c>
       <c r="D22">
-        <v>31952.5128030258</v>
+        <v>32078.39050743261</v>
       </c>
       <c r="E22">
-        <v>-2656.36</v>
+        <v>-2328.212999999999</v>
       </c>
       <c r="F22">
-        <v>6562.94</v>
+        <v>6891.087</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3195,28 +3195,28 @@
         <v>1181.9</v>
       </c>
       <c r="M22">
-        <v>362.930582</v>
+        <v>381.0771111</v>
       </c>
       <c r="N22">
-        <v>818.9694180000001</v>
+        <v>800.8228889000001</v>
       </c>
       <c r="O22">
-        <v>211.294109844</v>
+        <v>206.6123053362</v>
       </c>
       <c r="P22">
-        <v>607.675308156</v>
+        <v>594.2105835638</v>
       </c>
       <c r="Q22">
-        <v>1362.775308156</v>
+        <v>1349.3105835638</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0991934543244932</v>
+        <v>0.099722232214354</v>
       </c>
       <c r="T22">
-        <v>1.233105180704231</v>
+        <v>1.245317141209099</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.256545627780687</v>
+        <v>3.101472026457797</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3241,22 +3241,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08739740944933964</v>
+        <v>0.08764163543908476</v>
       </c>
       <c r="C23">
-        <v>25187.30350743262</v>
+        <v>24671.91772986347</v>
       </c>
       <c r="D23">
-        <v>32078.39050743262</v>
+        <v>31891.15172986347</v>
       </c>
       <c r="E23">
-        <v>-2328.213</v>
+        <v>-2000.066</v>
       </c>
       <c r="F23">
-        <v>6891.087</v>
+        <v>7219.233999999999</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3277,45 +3277,45 @@
         <v>1181.9</v>
       </c>
       <c r="M23">
-        <v>381.0771111</v>
+        <v>417.2717252</v>
       </c>
       <c r="N23">
-        <v>800.8228889000002</v>
+        <v>764.6282748000001</v>
       </c>
       <c r="O23">
-        <v>206.6123053362001</v>
+        <v>197.2740948984</v>
       </c>
       <c r="P23">
-        <v>594.2105835638001</v>
+        <v>567.3541799016001</v>
       </c>
       <c r="Q23">
-        <v>1349.3105835638</v>
+        <v>1322.4541799016</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09972223221435399</v>
+        <v>0.1002645685116471</v>
       </c>
       <c r="T23">
-        <v>1.245317141209099</v>
+        <v>1.2578422289064</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.101472026457798</v>
+        <v>2.832446889214721</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3323,22 +3323,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08764163543908476</v>
+        <v>0.08749631142882985</v>
       </c>
       <c r="C24">
-        <v>24671.91772986347</v>
+        <v>24454.92085087459</v>
       </c>
       <c r="D24">
-        <v>31891.15172986347</v>
+        <v>32002.30185087458</v>
       </c>
       <c r="E24">
-        <v>-2000.066</v>
+        <v>-1671.919</v>
       </c>
       <c r="F24">
-        <v>7219.233999999999</v>
+        <v>7547.380999999999</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3359,28 +3359,28 @@
         <v>1181.9</v>
       </c>
       <c r="M24">
-        <v>417.2717252</v>
+        <v>436.2386218</v>
       </c>
       <c r="N24">
-        <v>764.6282748000001</v>
+        <v>745.6613782000002</v>
       </c>
       <c r="O24">
-        <v>197.2740948984</v>
+        <v>192.3806355756001</v>
       </c>
       <c r="P24">
-        <v>567.3541799016001</v>
+        <v>553.2807426244001</v>
       </c>
       <c r="Q24">
-        <v>1322.4541799016</v>
+        <v>1308.3807426244</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1002645685116471</v>
+        <v>0.1008209914660128</v>
       </c>
       <c r="T24">
-        <v>1.2578422289064</v>
+        <v>1.270692643556877</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.832446889214721</v>
+        <v>2.709297024466256</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3405,22 +3405,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08749631142882985</v>
+        <v>0.08735098741857494</v>
       </c>
       <c r="C25">
-        <v>24454.92085087459</v>
+        <v>24238.70146394204</v>
       </c>
       <c r="D25">
-        <v>32002.30185087458</v>
+        <v>32114.22946394205</v>
       </c>
       <c r="E25">
-        <v>-1671.919</v>
+        <v>-1343.771999999999</v>
       </c>
       <c r="F25">
-        <v>7547.380999999999</v>
+        <v>7875.528</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3441,28 +3441,28 @@
         <v>1181.9</v>
       </c>
       <c r="M25">
-        <v>436.2386218</v>
+        <v>455.2055184000001</v>
       </c>
       <c r="N25">
-        <v>745.6613782000002</v>
+        <v>726.6944816</v>
       </c>
       <c r="O25">
-        <v>192.3806355756001</v>
+        <v>187.4871762528</v>
       </c>
       <c r="P25">
-        <v>553.2807426244001</v>
+        <v>539.2073053472</v>
       </c>
       <c r="Q25">
-        <v>1308.3807426244</v>
+        <v>1294.3073053472</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1008209914660128</v>
+        <v>0.1013920571297039</v>
       </c>
       <c r="T25">
-        <v>1.270692643556877</v>
+        <v>1.283881227013946</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.709297024466256</v>
+        <v>2.596409648446827</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3487,22 +3487,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08735098741857494</v>
+        <v>0.08785491340832002</v>
       </c>
       <c r="C26">
-        <v>24238.70146394205</v>
+        <v>23525.74342627823</v>
       </c>
       <c r="D26">
-        <v>32114.22946394205</v>
+        <v>31729.41842627823</v>
       </c>
       <c r="E26">
-        <v>-1343.772</v>
+        <v>-1015.625</v>
       </c>
       <c r="F26">
-        <v>7875.527999999999</v>
+        <v>8203.674999999999</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3523,45 +3523,45 @@
         <v>1181.9</v>
       </c>
       <c r="M26">
-        <v>455.2055184</v>
+        <v>502.8852775</v>
       </c>
       <c r="N26">
-        <v>726.6944816</v>
+        <v>679.0147225000001</v>
       </c>
       <c r="O26">
-        <v>187.4871762528</v>
+        <v>175.185798405</v>
       </c>
       <c r="P26">
-        <v>539.2073053472</v>
+        <v>503.828924095</v>
       </c>
       <c r="Q26">
-        <v>1294.3073053472</v>
+        <v>1258.928924095</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1013920571297039</v>
+        <v>0.1019783512110934</v>
       </c>
       <c r="T26">
-        <v>1.283881227013946</v>
+        <v>1.29742150602987</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.596409648446828</v>
+        <v>2.350237823377122</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3569,22 +3569,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08785491340832002</v>
+        <v>0.08773555939806513</v>
       </c>
       <c r="C27">
-        <v>23525.74342627823</v>
+        <v>23287.90244309523</v>
       </c>
       <c r="D27">
-        <v>31729.41842627823</v>
+        <v>31819.72444309523</v>
       </c>
       <c r="E27">
-        <v>-1015.625</v>
+        <v>-687.4779999999992</v>
       </c>
       <c r="F27">
-        <v>8203.674999999999</v>
+        <v>8531.822</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3605,28 +3605,28 @@
         <v>1181.9</v>
       </c>
       <c r="M27">
-        <v>502.8852775</v>
+        <v>523.0006886</v>
       </c>
       <c r="N27">
-        <v>679.0147225000001</v>
+        <v>658.8993114000001</v>
       </c>
       <c r="O27">
-        <v>175.185798405</v>
+        <v>169.9960223412</v>
       </c>
       <c r="P27">
-        <v>503.828924095</v>
+        <v>488.9032890588001</v>
       </c>
       <c r="Q27">
-        <v>1258.928924095</v>
+        <v>1244.0032890588</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1019783512110934</v>
+        <v>0.1025804910784664</v>
       </c>
       <c r="T27">
-        <v>1.29742150602987</v>
+        <v>1.311327738532711</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.350237823377122</v>
+        <v>2.259844060939541</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3651,22 +3651,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08773555939806513</v>
+        <v>0.08817715738781022</v>
       </c>
       <c r="C28">
-        <v>23287.90244309523</v>
+        <v>22628.17288271435</v>
       </c>
       <c r="D28">
-        <v>31819.72444309523</v>
+        <v>31488.14188271435</v>
       </c>
       <c r="E28">
-        <v>-687.4779999999992</v>
+        <v>-359.3310000000001</v>
       </c>
       <c r="F28">
-        <v>8531.822</v>
+        <v>8859.968999999999</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3687,45 +3687,45 @@
         <v>1181.9</v>
       </c>
       <c r="M28">
-        <v>523.0006886</v>
+        <v>567.9240129</v>
       </c>
       <c r="N28">
-        <v>658.8993114000001</v>
+        <v>613.9759871000001</v>
       </c>
       <c r="O28">
-        <v>169.9960223412</v>
+        <v>158.4058046718</v>
       </c>
       <c r="P28">
-        <v>488.9032890588001</v>
+        <v>455.5701824282</v>
       </c>
       <c r="Q28">
-        <v>1244.0032890588</v>
+        <v>1210.6701824282</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1025804910784664</v>
+        <v>0.1031991279285071</v>
       </c>
       <c r="T28">
-        <v>1.311327738532711</v>
+        <v>1.325614963706863</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.259844060939541</v>
+        <v>2.081088267363171</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3733,22 +3733,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08817715738781022</v>
+        <v>0.08807857937755531</v>
       </c>
       <c r="C29">
-        <v>22628.17288271435</v>
+        <v>22373.44458360547</v>
       </c>
       <c r="D29">
-        <v>31488.14188271435</v>
+        <v>31561.56058360547</v>
       </c>
       <c r="E29">
-        <v>-359.3310000000001</v>
+        <v>-31.18399999999929</v>
       </c>
       <c r="F29">
-        <v>8859.968999999999</v>
+        <v>9188.116</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3769,28 +3769,28 @@
         <v>1181.9</v>
       </c>
       <c r="M29">
-        <v>567.9240129</v>
+        <v>588.9582356000001</v>
       </c>
       <c r="N29">
-        <v>613.9759871000001</v>
+        <v>592.9417644</v>
       </c>
       <c r="O29">
-        <v>158.4058046718</v>
+        <v>152.9789752152</v>
       </c>
       <c r="P29">
-        <v>455.5701824282</v>
+        <v>439.9627891848</v>
       </c>
       <c r="Q29">
-        <v>1210.6701824282</v>
+        <v>1195.0627891848</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1031991279285071</v>
+        <v>0.1038349491354935</v>
       </c>
       <c r="T29">
-        <v>1.325614963706863</v>
+        <v>1.340299056246963</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.081088267363171</v>
+        <v>2.006763686385915</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08807857937755531</v>
+        <v>0.09049760736730039</v>
       </c>
       <c r="C30">
-        <v>22373.44458360547</v>
+        <v>20337.19052936455</v>
       </c>
       <c r="D30">
-        <v>31561.56058360547</v>
+        <v>29853.45352936455</v>
       </c>
       <c r="E30">
-        <v>-31.18399999999929</v>
+        <v>296.9630000000016</v>
       </c>
       <c r="F30">
-        <v>9188.116</v>
+        <v>9516.263000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3851,45 +3851,45 @@
         <v>1181.9</v>
       </c>
       <c r="M30">
-        <v>588.9582356000001</v>
+        <v>721.3327354000002</v>
       </c>
       <c r="N30">
-        <v>592.9417644</v>
+        <v>460.5672645999999</v>
       </c>
       <c r="O30">
-        <v>152.9789752152</v>
+        <v>118.8263542668</v>
       </c>
       <c r="P30">
-        <v>439.9627891848</v>
+        <v>341.7409103332</v>
       </c>
       <c r="Q30">
-        <v>1195.0627891848</v>
+        <v>1096.8409103332</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1038349491354935</v>
+        <v>0.1044886807990146</v>
       </c>
       <c r="T30">
-        <v>1.340299056246963</v>
+        <v>1.355396785196643</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.04756220000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.006763686385915</v>
+        <v>1.638494888693221</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3897,22 +3897,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09049760736730039</v>
+        <v>0.0904858433570455</v>
       </c>
       <c r="C31">
-        <v>20337.19052936455</v>
+        <v>20016.90275965047</v>
       </c>
       <c r="D31">
-        <v>29853.45352936455</v>
+        <v>29861.31275965046</v>
       </c>
       <c r="E31">
-        <v>296.9629999999997</v>
+        <v>625.1099999999988</v>
       </c>
       <c r="F31">
-        <v>9516.262999999999</v>
+        <v>9844.409999999998</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3933,28 +3933,28 @@
         <v>1181.9</v>
       </c>
       <c r="M31">
-        <v>721.3327353999999</v>
+        <v>746.2062779999999</v>
       </c>
       <c r="N31">
-        <v>460.5672646000002</v>
+        <v>435.6937220000002</v>
       </c>
       <c r="O31">
-        <v>118.8263542668</v>
+        <v>112.4089802760001</v>
       </c>
       <c r="P31">
-        <v>341.7409103332001</v>
+        <v>323.2847417240001</v>
       </c>
       <c r="Q31">
-        <v>1096.8409103332</v>
+        <v>1078.384741724</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1044886807990146</v>
+        <v>0.105161090510065</v>
       </c>
       <c r="T31">
-        <v>1.355396785196643</v>
+        <v>1.3709258778306</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.638494888693222</v>
+        <v>1.583878392403448</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0904858433570455</v>
+        <v>0.09047407934679058</v>
       </c>
       <c r="C32">
-        <v>20016.90275965047</v>
+        <v>19696.61912907333</v>
       </c>
       <c r="D32">
-        <v>29861.31275965046</v>
+        <v>29869.17612907332</v>
       </c>
       <c r="E32">
-        <v>625.1099999999988</v>
+        <v>953.2569999999996</v>
       </c>
       <c r="F32">
-        <v>9844.409999999998</v>
+        <v>10172.557</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4015,28 +4015,28 @@
         <v>1181.9</v>
       </c>
       <c r="M32">
-        <v>746.2062779999999</v>
+        <v>771.0798205999999</v>
       </c>
       <c r="N32">
-        <v>435.6937220000002</v>
+        <v>410.8201794000001</v>
       </c>
       <c r="O32">
-        <v>112.4089802760001</v>
+        <v>105.9916062852</v>
       </c>
       <c r="P32">
-        <v>323.2847417240001</v>
+        <v>304.8285731148001</v>
       </c>
       <c r="Q32">
-        <v>1078.384741724</v>
+        <v>1059.9285731148</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.105161090510065</v>
+        <v>0.1058529903576675</v>
       </c>
       <c r="T32">
-        <v>1.3709258778306</v>
+        <v>1.386905089091629</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.583878392403448</v>
+        <v>1.532785541035595</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09047407934679058</v>
+        <v>0.09383396333653567</v>
       </c>
       <c r="C33">
-        <v>19696.61912907333</v>
+        <v>17279.18030945335</v>
       </c>
       <c r="D33">
-        <v>29869.17612907332</v>
+        <v>27779.88430945335</v>
       </c>
       <c r="E33">
-        <v>953.2569999999996</v>
+        <v>1281.404</v>
       </c>
       <c r="F33">
-        <v>10172.557</v>
+        <v>10500.704</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4097,45 +4097,45 @@
         <v>1181.9</v>
       </c>
       <c r="M33">
-        <v>771.0798205999999</v>
+        <v>945.06336</v>
       </c>
       <c r="N33">
-        <v>410.8201794000001</v>
+        <v>236.8366400000001</v>
       </c>
       <c r="O33">
-        <v>105.9916062852</v>
+        <v>61.10385312000003</v>
       </c>
       <c r="P33">
-        <v>304.8285731148001</v>
+        <v>175.7327868800001</v>
       </c>
       <c r="Q33">
-        <v>1059.9285731148</v>
+        <v>930.83278688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1058529903576675</v>
+        <v>0.1065652402007878</v>
       </c>
       <c r="T33">
-        <v>1.386905089091629</v>
+        <v>1.403354277154452</v>
       </c>
       <c r="U33">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.532785541035595</v>
+        <v>1.250603980668556</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4143,22 +4143,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09383396333653567</v>
+        <v>0.102041421186614</v>
       </c>
       <c r="C34">
-        <v>17279.18030945335</v>
+        <v>12897.04205639878</v>
       </c>
       <c r="D34">
-        <v>27779.88430945335</v>
+        <v>23725.89305639877</v>
       </c>
       <c r="E34">
-        <v>1281.404</v>
+        <v>1609.550999999999</v>
       </c>
       <c r="F34">
-        <v>10500.704</v>
+        <v>10828.851</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4179,45 +4179,45 @@
         <v>1181.9</v>
       </c>
       <c r="M34">
-        <v>945.06336</v>
+        <v>1284.3017286</v>
       </c>
       <c r="N34">
-        <v>236.8366400000001</v>
+        <v>-102.4017285999998</v>
       </c>
       <c r="O34">
-        <v>61.10385312000003</v>
+        <v>-26.41964597879996</v>
       </c>
       <c r="P34">
-        <v>175.7327868800001</v>
+        <v>-75.98208262119988</v>
       </c>
       <c r="Q34">
-        <v>930.83278688</v>
+        <v>679.1179173788</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1065652402007878</v>
+        <v>0.1077550880665278</v>
       </c>
       <c r="T34">
-        <v>1.403354277154452</v>
+        <v>1.430833442644985</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.258</v>
+        <v>0.237428785782606</v>
       </c>
       <c r="W34">
-        <v>0.06677999999999999</v>
+        <v>0.09044094600618292</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.250603980668556</v>
+        <v>0.9202666115604885</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4225,22 +4225,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.102041421186614</v>
+        <v>0.102769421186614</v>
       </c>
       <c r="C35">
-        <v>12897.04205639878</v>
+        <v>12265.70696381699</v>
       </c>
       <c r="D35">
-        <v>23725.89305639877</v>
+        <v>23422.70496381698</v>
       </c>
       <c r="E35">
-        <v>1609.550999999999</v>
+        <v>1937.698</v>
       </c>
       <c r="F35">
-        <v>10828.851</v>
+        <v>11156.998</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4261,37 +4261,37 @@
         <v>1181.9</v>
       </c>
       <c r="M35">
-        <v>1284.3017286</v>
+        <v>1323.2199628</v>
       </c>
       <c r="N35">
-        <v>-102.4017285999998</v>
+        <v>-141.3199628</v>
       </c>
       <c r="O35">
-        <v>-26.41964597879996</v>
+        <v>-36.4605504024</v>
       </c>
       <c r="P35">
-        <v>-75.98208262119988</v>
+        <v>-104.8594123976</v>
       </c>
       <c r="Q35">
-        <v>679.1179173788</v>
+        <v>650.2405876024</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1077550880665278</v>
+        <v>0.1086938015220813</v>
       </c>
       <c r="T35">
-        <v>1.430833442644985</v>
+        <v>1.452512737230515</v>
       </c>
       <c r="U35">
         <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.237428785782606</v>
+        <v>0.2304455862007647</v>
       </c>
       <c r="W35">
-        <v>0.09044094600618292</v>
+        <v>0.09126915347658933</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.9202666115604885</v>
+        <v>0.8931999465145917</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4307,22 +4307,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.102769421186614</v>
+        <v>0.103497421186614</v>
       </c>
       <c r="C36">
-        <v>12265.70696381699</v>
+        <v>11642.02285205409</v>
       </c>
       <c r="D36">
-        <v>23422.70496381698</v>
+        <v>23127.1678520541</v>
       </c>
       <c r="E36">
-        <v>1937.698</v>
+        <v>2265.845000000001</v>
       </c>
       <c r="F36">
-        <v>11156.998</v>
+        <v>11485.145</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4343,37 +4343,37 @@
         <v>1181.9</v>
       </c>
       <c r="M36">
-        <v>1323.2199628</v>
+        <v>1362.138197</v>
       </c>
       <c r="N36">
-        <v>-141.3199628</v>
+        <v>-180.2381970000001</v>
       </c>
       <c r="O36">
-        <v>-36.4605504024</v>
+        <v>-46.50145482600004</v>
       </c>
       <c r="P36">
-        <v>-104.8594123976</v>
+        <v>-133.7367421740001</v>
       </c>
       <c r="Q36">
-        <v>650.2405876024</v>
+        <v>621.3632578259999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1086938015220813</v>
+        <v>0.1096613984685749</v>
       </c>
       <c r="T36">
-        <v>1.452512737230515</v>
+        <v>1.474859087034061</v>
       </c>
       <c r="U36">
         <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.2304455862007647</v>
+        <v>0.2238614265950285</v>
       </c>
       <c r="W36">
-        <v>0.09126915347658933</v>
+        <v>0.09205003480582963</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8931999465145917</v>
+        <v>0.8676799480427462</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4389,22 +4389,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.103497421186614</v>
+        <v>0.104225421186614</v>
       </c>
       <c r="C37">
-        <v>11642.02285205409</v>
+        <v>11025.70371988378</v>
       </c>
       <c r="D37">
-        <v>23127.1678520541</v>
+        <v>22838.99571988378</v>
       </c>
       <c r="E37">
-        <v>2265.845000000001</v>
+        <v>2593.992</v>
       </c>
       <c r="F37">
-        <v>11485.145</v>
+        <v>11813.292</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4425,37 +4425,37 @@
         <v>1181.9</v>
       </c>
       <c r="M37">
-        <v>1362.138197</v>
+        <v>1401.0564312</v>
       </c>
       <c r="N37">
-        <v>-180.2381970000001</v>
+        <v>-219.1564312</v>
       </c>
       <c r="O37">
-        <v>-46.50145482600004</v>
+        <v>-56.54235924960001</v>
       </c>
       <c r="P37">
-        <v>-133.7367421740001</v>
+        <v>-162.6140719504</v>
       </c>
       <c r="Q37">
-        <v>621.3632578259999</v>
+        <v>592.4859280495998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1096613984685749</v>
+        <v>0.1106592328196463</v>
       </c>
       <c r="T37">
-        <v>1.474859087034061</v>
+        <v>1.497903760268968</v>
       </c>
       <c r="U37">
         <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.2238614265950285</v>
+        <v>0.2176430536340555</v>
       </c>
       <c r="W37">
-        <v>0.09205003480582963</v>
+        <v>0.09278753383900103</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8676799480427462</v>
+        <v>0.843577727263781</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4471,22 +4471,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.104225421186614</v>
+        <v>0.104953421186614</v>
       </c>
       <c r="C38">
-        <v>11025.70371988379</v>
+        <v>10416.47764532574</v>
       </c>
       <c r="D38">
-        <v>22838.99571988378</v>
+        <v>22557.91664532574</v>
       </c>
       <c r="E38">
-        <v>2593.991999999998</v>
+        <v>2922.138999999999</v>
       </c>
       <c r="F38">
-        <v>11813.292</v>
+        <v>12141.439</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4507,37 +4507,37 @@
         <v>1181.9</v>
       </c>
       <c r="M38">
-        <v>1401.0564312</v>
+        <v>1439.9746654</v>
       </c>
       <c r="N38">
-        <v>-219.1564311999998</v>
+        <v>-258.0746654</v>
       </c>
       <c r="O38">
-        <v>-56.54235924959995</v>
+        <v>-66.58326367319999</v>
       </c>
       <c r="P38">
-        <v>-162.6140719503999</v>
+        <v>-191.4914017267999</v>
       </c>
       <c r="Q38">
-        <v>592.4859280496</v>
+        <v>563.6085982732</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1106592328196463</v>
+        <v>0.1116887444517042</v>
       </c>
       <c r="T38">
-        <v>1.497903760268968</v>
+        <v>1.521680010431968</v>
       </c>
       <c r="U38">
         <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.2176430536340555</v>
+        <v>0.2117608089412432</v>
       </c>
       <c r="W38">
-        <v>0.09278753383900101</v>
+        <v>0.09348516805956857</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8435777272637812</v>
+        <v>0.8207783292296248</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4553,22 +4553,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.104953421186614</v>
+        <v>0.1383620021281568</v>
       </c>
       <c r="C39">
-        <v>10416.47764532574</v>
+        <v>1946.458529438451</v>
       </c>
       <c r="D39">
-        <v>22557.91664532574</v>
+        <v>14416.04452943845</v>
       </c>
       <c r="E39">
-        <v>2922.138999999999</v>
+        <v>3250.286</v>
       </c>
       <c r="F39">
-        <v>12141.439</v>
+        <v>12469.586</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4589,45 +4589,45 @@
         <v>1181.9</v>
       </c>
       <c r="M39">
-        <v>1439.9746654</v>
+        <v>2503.8928688</v>
       </c>
       <c r="N39">
-        <v>-258.0746654</v>
+        <v>-1321.9928688</v>
       </c>
       <c r="O39">
-        <v>-66.58326367319999</v>
+        <v>-341.0741601504</v>
       </c>
       <c r="P39">
-        <v>-191.4914017267999</v>
+        <v>-980.9187086495999</v>
       </c>
       <c r="Q39">
-        <v>563.6085982732</v>
+        <v>-225.8187086496</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1116887444517042</v>
+        <v>0.1150814353969619</v>
       </c>
       <c r="T39">
-        <v>1.521680010431968</v>
+        <v>1.600033150045311</v>
       </c>
       <c r="U39">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.2117608089412432</v>
+        <v>0.1217824467650403</v>
       </c>
       <c r="W39">
-        <v>0.09348516805956857</v>
+        <v>0.1763460846895799</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8207783292296248</v>
+        <v>0.4720249874613964</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4635,22 +4635,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1383620021281568</v>
+        <v>0.1399120021281568</v>
       </c>
       <c r="C40">
-        <v>1946.458529438451</v>
+        <v>1380.883055754488</v>
       </c>
       <c r="D40">
-        <v>14416.04452943845</v>
+        <v>14178.61605575449</v>
       </c>
       <c r="E40">
-        <v>3250.286</v>
+        <v>3578.433000000001</v>
       </c>
       <c r="F40">
-        <v>12469.586</v>
+        <v>12797.733</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4671,37 +4671,37 @@
         <v>1181.9</v>
       </c>
       <c r="M40">
-        <v>2503.8928688</v>
+        <v>2569.7847864</v>
       </c>
       <c r="N40">
-        <v>-1321.9928688</v>
+        <v>-1387.8847864</v>
       </c>
       <c r="O40">
-        <v>-341.0741601504</v>
+        <v>-358.0742748912</v>
       </c>
       <c r="P40">
-        <v>-980.9187086495999</v>
+        <v>-1029.8105115088</v>
       </c>
       <c r="Q40">
-        <v>-225.8187086496</v>
+        <v>-274.7105115088</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1150814353969619</v>
+        <v>0.1162171966329777</v>
       </c>
       <c r="T40">
-        <v>1.600033150045311</v>
+        <v>1.626263201685398</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1217824467650403</v>
+        <v>0.1186598199249111</v>
       </c>
       <c r="W40">
-        <v>0.1763460846895799</v>
+        <v>0.1769731081590779</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4720249874613964</v>
+        <v>0.459921782654694</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1399120021281568</v>
+        <v>0.1414620021281568</v>
       </c>
       <c r="C41">
-        <v>1380.883055754488</v>
+        <v>823.0016324985645</v>
       </c>
       <c r="D41">
-        <v>14178.61605575449</v>
+        <v>13948.88163249856</v>
       </c>
       <c r="E41">
-        <v>3578.433000000001</v>
+        <v>3906.58</v>
       </c>
       <c r="F41">
-        <v>12797.733</v>
+        <v>13125.88</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4753,37 +4753,37 @@
         <v>1181.9</v>
       </c>
       <c r="M41">
-        <v>2569.7847864</v>
+        <v>2635.676704</v>
       </c>
       <c r="N41">
-        <v>-1387.8847864</v>
+        <v>-1453.776704</v>
       </c>
       <c r="O41">
-        <v>-358.0742748912</v>
+        <v>-375.074389632</v>
       </c>
       <c r="P41">
-        <v>-1029.8105115088</v>
+        <v>-1078.702314368</v>
       </c>
       <c r="Q41">
-        <v>-274.7105115088</v>
+        <v>-323.602314368</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1162171966329777</v>
+        <v>0.1173908165768607</v>
       </c>
       <c r="T41">
-        <v>1.626263201685398</v>
+        <v>1.653367588380155</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1186598199249111</v>
+        <v>0.1156933244267883</v>
       </c>
       <c r="W41">
-        <v>0.1769731081590779</v>
+        <v>0.1775687804551009</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.459921782654694</v>
+        <v>0.4484237380883267</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4799,22 +4799,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1414620021281568</v>
+        <v>0.1430120021281568</v>
       </c>
       <c r="C42">
-        <v>823.0016324985645</v>
+        <v>272.4462255420876</v>
       </c>
       <c r="D42">
-        <v>13948.88163249856</v>
+        <v>13726.47322554209</v>
       </c>
       <c r="E42">
-        <v>3906.58</v>
+        <v>4234.727000000001</v>
       </c>
       <c r="F42">
-        <v>13125.88</v>
+        <v>13454.027</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4835,37 +4835,37 @@
         <v>1181.9</v>
       </c>
       <c r="M42">
-        <v>2635.676704</v>
+        <v>2701.5686216</v>
       </c>
       <c r="N42">
-        <v>-1453.776704</v>
+        <v>-1519.6686216</v>
       </c>
       <c r="O42">
-        <v>-375.074389632</v>
+        <v>-392.0745043728</v>
       </c>
       <c r="P42">
-        <v>-1078.702314368</v>
+        <v>-1127.5941172272</v>
       </c>
       <c r="Q42">
-        <v>-323.602314368</v>
+        <v>-372.4941172271999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1173908165768607</v>
+        <v>0.1186042202476549</v>
       </c>
       <c r="T42">
-        <v>1.653367588380155</v>
+        <v>1.681390767844225</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1156933244267883</v>
+        <v>0.1128715360261349</v>
       </c>
       <c r="W42">
-        <v>0.1775687804551009</v>
+        <v>0.1781353955659521</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4484237380883267</v>
+        <v>0.437486573744709</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4881,22 +4881,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1430120021281568</v>
+        <v>0.1445620021281568</v>
       </c>
       <c r="C43">
-        <v>272.4462255420876</v>
+        <v>-271.1280950987166</v>
       </c>
       <c r="D43">
-        <v>13726.47322554209</v>
+        <v>13511.04590490128</v>
       </c>
       <c r="E43">
-        <v>4234.727000000001</v>
+        <v>4562.874000000002</v>
       </c>
       <c r="F43">
-        <v>13454.027</v>
+        <v>13782.174</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4917,37 +4917,37 @@
         <v>1181.9</v>
       </c>
       <c r="M43">
-        <v>2701.5686216</v>
+        <v>2767.4605392</v>
       </c>
       <c r="N43">
-        <v>-1519.6686216</v>
+        <v>-1585.5605392</v>
       </c>
       <c r="O43">
-        <v>-392.0745043728</v>
+        <v>-409.0746191136001</v>
       </c>
       <c r="P43">
-        <v>-1127.5941172272</v>
+        <v>-1176.4859200864</v>
       </c>
       <c r="Q43">
-        <v>-372.4941172271999</v>
+        <v>-421.3859200864003</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1186042202476549</v>
+        <v>0.1198594654243386</v>
       </c>
       <c r="T43">
-        <v>1.681390767844225</v>
+        <v>1.710380263841539</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1128715360261349</v>
+        <v>0.1101841185017031</v>
       </c>
       <c r="W43">
-        <v>0.1781353955659521</v>
+        <v>0.178675029004858</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.437486573744709</v>
+        <v>0.4270702267507872</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1445620021281568</v>
+        <v>0.1461120021281568</v>
       </c>
       <c r="C44">
-        <v>-271.1280950987148</v>
+        <v>-808.0449402648155</v>
       </c>
       <c r="D44">
-        <v>13511.04590490128</v>
+        <v>13302.27605973518</v>
       </c>
       <c r="E44">
-        <v>4562.874</v>
+        <v>4891.020999999999</v>
       </c>
       <c r="F44">
-        <v>13782.174</v>
+        <v>14110.321</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4999,37 +4999,37 @@
         <v>1181.9</v>
       </c>
       <c r="M44">
-        <v>2767.4605392</v>
+        <v>2833.3524568</v>
       </c>
       <c r="N44">
-        <v>-1585.5605392</v>
+        <v>-1651.4524568</v>
       </c>
       <c r="O44">
-        <v>-409.0746191136</v>
+        <v>-426.0747338543999</v>
       </c>
       <c r="P44">
-        <v>-1176.4859200864</v>
+        <v>-1225.3777229456</v>
       </c>
       <c r="Q44">
-        <v>-421.3859200863999</v>
+        <v>-470.2777229455999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1198594654243386</v>
+        <v>0.1211587542914323</v>
       </c>
       <c r="T44">
-        <v>1.710380263841539</v>
+        <v>1.740386935137004</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1101841185017031</v>
+        <v>0.1076216971411984</v>
       </c>
       <c r="W44">
-        <v>0.178675029004858</v>
+        <v>0.1791895632140474</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4270702267507873</v>
+        <v>0.4171383610123969</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1461120021281568</v>
+        <v>0.1476620021281568</v>
       </c>
       <c r="C45">
-        <v>-808.0449402648155</v>
+        <v>-1338.608223685684</v>
       </c>
       <c r="D45">
-        <v>13302.27605973518</v>
+        <v>13099.85977631432</v>
       </c>
       <c r="E45">
-        <v>4891.020999999999</v>
+        <v>5219.168</v>
       </c>
       <c r="F45">
-        <v>14110.321</v>
+        <v>14438.468</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5081,37 +5081,37 @@
         <v>1181.9</v>
       </c>
       <c r="M45">
-        <v>2833.3524568</v>
+        <v>2899.2443744</v>
       </c>
       <c r="N45">
-        <v>-1651.4524568</v>
+        <v>-1717.3443744</v>
       </c>
       <c r="O45">
-        <v>-426.0747338543999</v>
+        <v>-443.0748485951999</v>
       </c>
       <c r="P45">
-        <v>-1225.3777229456</v>
+        <v>-1274.2695258048</v>
       </c>
       <c r="Q45">
-        <v>-470.2777229455999</v>
+        <v>-519.1695258047998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1211587542914323</v>
+        <v>0.1225044463323507</v>
       </c>
       <c r="T45">
-        <v>1.740386935137004</v>
+        <v>1.771465273264451</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1076216971411984</v>
+        <v>0.1051757494788984</v>
       </c>
       <c r="W45">
-        <v>0.1791895632140474</v>
+        <v>0.1796807095046372</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4171383610123969</v>
+        <v>0.4076579437166606</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1476620021281568</v>
+        <v>0.1492120021281568</v>
       </c>
       <c r="C46">
-        <v>-1338.608223685684</v>
+        <v>-1863.103638138806</v>
       </c>
       <c r="D46">
-        <v>13099.85977631432</v>
+        <v>12903.51136186119</v>
       </c>
       <c r="E46">
-        <v>5219.168</v>
+        <v>5547.315000000001</v>
       </c>
       <c r="F46">
-        <v>14438.468</v>
+        <v>14766.615</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5163,37 +5163,37 @@
         <v>1181.9</v>
       </c>
       <c r="M46">
-        <v>2899.2443744</v>
+        <v>2965.136292</v>
       </c>
       <c r="N46">
-        <v>-1717.3443744</v>
+        <v>-1783.236292</v>
       </c>
       <c r="O46">
-        <v>-443.0748485951999</v>
+        <v>-460.0749633360001</v>
       </c>
       <c r="P46">
-        <v>-1274.2695258048</v>
+        <v>-1323.161328664</v>
       </c>
       <c r="Q46">
-        <v>-519.1695258047998</v>
+        <v>-568.061328664</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1225044463323507</v>
+        <v>0.1238990726293026</v>
       </c>
       <c r="T46">
-        <v>1.771465273264451</v>
+        <v>1.803673732778351</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1051757494788984</v>
+        <v>0.1028385106015896</v>
       </c>
       <c r="W46">
-        <v>0.1796807095046372</v>
+        <v>0.1801500270712008</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4076579437166606</v>
+        <v>0.3985988783007348</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5209,22 +5209,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1492120021281568</v>
+        <v>0.1507620021281568</v>
       </c>
       <c r="C47">
-        <v>-1863.103638138806</v>
+        <v>-2381.800000816402</v>
       </c>
       <c r="D47">
-        <v>12903.51136186119</v>
+        <v>12712.9619991836</v>
       </c>
       <c r="E47">
-        <v>5547.315000000001</v>
+        <v>5875.462</v>
       </c>
       <c r="F47">
-        <v>14766.615</v>
+        <v>15094.762</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5245,37 +5245,37 @@
         <v>1181.9</v>
       </c>
       <c r="M47">
-        <v>2965.136292</v>
+        <v>3031.0282096</v>
       </c>
       <c r="N47">
-        <v>-1783.236292</v>
+        <v>-1849.1282096</v>
       </c>
       <c r="O47">
-        <v>-460.0749633360001</v>
+        <v>-477.0750780768</v>
       </c>
       <c r="P47">
-        <v>-1323.161328664</v>
+        <v>-1372.0531315232</v>
       </c>
       <c r="Q47">
-        <v>-568.061328664</v>
+        <v>-616.9531315232</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1238990726293026</v>
+        <v>0.1253453517520674</v>
       </c>
       <c r="T47">
-        <v>1.803673732778351</v>
+        <v>1.837075098200172</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1028385106015896</v>
+        <v>0.1006028908059028</v>
       </c>
       <c r="W47">
-        <v>0.1801500270712008</v>
+        <v>0.1805989395261747</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3985988783007348</v>
+        <v>0.3899336852941971</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5291,22 +5291,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1507620021281568</v>
+        <v>0.1523120021281568</v>
       </c>
       <c r="C48">
-        <v>-2381.800000816402</v>
+        <v>-2894.95048122254</v>
       </c>
       <c r="D48">
-        <v>12712.9619991836</v>
+        <v>12527.95851877746</v>
       </c>
       <c r="E48">
-        <v>5875.462</v>
+        <v>6203.609</v>
       </c>
       <c r="F48">
-        <v>15094.762</v>
+        <v>15422.909</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5327,37 +5327,37 @@
         <v>1181.9</v>
       </c>
       <c r="M48">
-        <v>3031.0282096</v>
+        <v>3096.9201272</v>
       </c>
       <c r="N48">
-        <v>-1849.1282096</v>
+        <v>-1915.0201272</v>
       </c>
       <c r="O48">
-        <v>-477.0750780768</v>
+        <v>-494.0751928176</v>
       </c>
       <c r="P48">
-        <v>-1372.0531315232</v>
+        <v>-1420.9449343824</v>
       </c>
       <c r="Q48">
-        <v>-616.9531315232</v>
+        <v>-665.8449343824</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1253453517520674</v>
+        <v>0.1268462074455027</v>
       </c>
       <c r="T48">
-        <v>1.837075098200172</v>
+        <v>1.871736892505835</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1006028908059028</v>
+        <v>0.09846240376747939</v>
       </c>
       <c r="W48">
-        <v>0.1805989395261747</v>
+        <v>0.1810287493234901</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3899336852941971</v>
+        <v>0.3816372239049589</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5373,22 +5373,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1523120021281568</v>
+        <v>0.1538620021281568</v>
       </c>
       <c r="C49">
-        <v>-2894.95048122254</v>
+        <v>-3402.793723395402</v>
       </c>
       <c r="D49">
-        <v>12527.95851877746</v>
+        <v>12348.2622766046</v>
       </c>
       <c r="E49">
-        <v>6203.609</v>
+        <v>6531.756000000001</v>
       </c>
       <c r="F49">
-        <v>15422.909</v>
+        <v>15751.056</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5409,37 +5409,37 @@
         <v>1181.9</v>
       </c>
       <c r="M49">
-        <v>3096.9201272</v>
+        <v>3162.8120448</v>
       </c>
       <c r="N49">
-        <v>-1915.0201272</v>
+        <v>-1980.9120448</v>
       </c>
       <c r="O49">
-        <v>-494.0751928176</v>
+        <v>-511.0753075584001</v>
       </c>
       <c r="P49">
-        <v>-1420.9449343824</v>
+        <v>-1469.8367372416</v>
       </c>
       <c r="Q49">
-        <v>-665.8449343824</v>
+        <v>-714.7367372416004</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1268462074455027</v>
+        <v>0.1284047883579162</v>
       </c>
       <c r="T49">
-        <v>1.871736892505835</v>
+        <v>1.907731832746332</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.09846240376747939</v>
+        <v>0.09641110368899022</v>
       </c>
       <c r="W49">
-        <v>0.1810287493234901</v>
+        <v>0.1814406503792508</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3816372239049589</v>
+        <v>0.3736864484069389</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1538620021281568</v>
+        <v>0.1554120021281568</v>
       </c>
       <c r="C50">
-        <v>-3402.793723395396</v>
+        <v>-3905.55487291489</v>
       </c>
       <c r="D50">
-        <v>12348.2622766046</v>
+        <v>12173.64812708511</v>
       </c>
       <c r="E50">
-        <v>6531.755999999999</v>
+        <v>6859.902999999998</v>
       </c>
       <c r="F50">
-        <v>15751.056</v>
+        <v>16079.203</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5491,37 +5491,37 @@
         <v>1181.9</v>
       </c>
       <c r="M50">
-        <v>3162.8120448</v>
+        <v>3228.703962399999</v>
       </c>
       <c r="N50">
-        <v>-1980.9120448</v>
+        <v>-2046.803962399999</v>
       </c>
       <c r="O50">
-        <v>-511.0753075584</v>
+        <v>-528.0754222991999</v>
       </c>
       <c r="P50">
-        <v>-1469.8367372416</v>
+        <v>-1518.728540100799</v>
       </c>
       <c r="Q50">
-        <v>-714.7367372415999</v>
+        <v>-763.6285401007995</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1284047883579162</v>
+        <v>0.1300244900904243</v>
       </c>
       <c r="T50">
-        <v>1.907731832746332</v>
+        <v>1.94513833927077</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.09641110368899024</v>
+        <v>0.09444353014431697</v>
       </c>
       <c r="W50">
-        <v>0.1814406503792508</v>
+        <v>0.1818357391470212</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3736864484069389</v>
+        <v>0.3660601943578178</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5537,22 +5537,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1554120021281568</v>
+        <v>0.1569620021281568</v>
       </c>
       <c r="C51">
-        <v>-3905.55487291489</v>
+        <v>-4403.446517989094</v>
       </c>
       <c r="D51">
-        <v>12173.64812708511</v>
+        <v>12003.9034820109</v>
       </c>
       <c r="E51">
-        <v>6859.902999999998</v>
+        <v>7188.049999999999</v>
       </c>
       <c r="F51">
-        <v>16079.203</v>
+        <v>16407.35</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5573,37 +5573,37 @@
         <v>1181.9</v>
       </c>
       <c r="M51">
-        <v>3228.703962399999</v>
+        <v>3294.59588</v>
       </c>
       <c r="N51">
-        <v>-2046.803962399999</v>
+        <v>-2112.69588</v>
       </c>
       <c r="O51">
-        <v>-528.0754222991999</v>
+        <v>-545.07553704</v>
       </c>
       <c r="P51">
-        <v>-1518.728540100799</v>
+        <v>-1567.62034296</v>
       </c>
       <c r="Q51">
-        <v>-763.6285401007995</v>
+        <v>-812.5203429599999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1300244900904243</v>
+        <v>0.1317089798922328</v>
       </c>
       <c r="T51">
-        <v>1.94513833927077</v>
+        <v>1.984041106056185</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.09444353014431697</v>
+        <v>0.09255465954143062</v>
       </c>
       <c r="W51">
-        <v>0.1818357391470212</v>
+        <v>0.1822150243640807</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3660601943578178</v>
+        <v>0.3587389904706614</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5619,22 +5619,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1569620021281568</v>
+        <v>0.1585120021281568</v>
       </c>
       <c r="C52">
-        <v>-4403.446517989094</v>
+        <v>-4896.669552890518</v>
       </c>
       <c r="D52">
-        <v>12003.9034820109</v>
+        <v>11838.82744710948</v>
       </c>
       <c r="E52">
-        <v>7188.049999999999</v>
+        <v>7516.197</v>
       </c>
       <c r="F52">
-        <v>16407.35</v>
+        <v>16735.497</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5655,37 +5655,37 @@
         <v>1181.9</v>
       </c>
       <c r="M52">
-        <v>3294.59588</v>
+        <v>3360.4877976</v>
       </c>
       <c r="N52">
-        <v>-2112.69588</v>
+        <v>-2178.5877976</v>
       </c>
       <c r="O52">
-        <v>-545.07553704</v>
+        <v>-562.0756517807999</v>
       </c>
       <c r="P52">
-        <v>-1567.62034296</v>
+        <v>-1616.5121458192</v>
       </c>
       <c r="Q52">
-        <v>-812.5203429599999</v>
+        <v>-861.4121458191998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1317089798922328</v>
+        <v>0.1334622243798294</v>
       </c>
       <c r="T52">
-        <v>1.984041106056185</v>
+        <v>2.024531740873659</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.09255465954143062</v>
+        <v>0.09073986229552024</v>
       </c>
       <c r="W52">
-        <v>0.1822150243640807</v>
+        <v>0.1825794356510596</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3587389904706614</v>
+        <v>0.3517048926182954</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5701,22 +5701,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1585120021281568</v>
+        <v>0.1600620021281568</v>
       </c>
       <c r="C53">
-        <v>-4896.669552890518</v>
+        <v>-5385.413971115684</v>
       </c>
       <c r="D53">
-        <v>11838.82744710948</v>
+        <v>11678.23002888432</v>
       </c>
       <c r="E53">
-        <v>7516.197</v>
+        <v>7844.344000000001</v>
       </c>
       <c r="F53">
-        <v>16735.497</v>
+        <v>17063.644</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5737,37 +5737,37 @@
         <v>1181.9</v>
       </c>
       <c r="M53">
-        <v>3360.4877976</v>
+        <v>3426.3797152</v>
       </c>
       <c r="N53">
-        <v>-2178.5877976</v>
+        <v>-2244.4797152</v>
       </c>
       <c r="O53">
-        <v>-562.0756517807999</v>
+        <v>-579.0757665216</v>
       </c>
       <c r="P53">
-        <v>-1616.5121458192</v>
+        <v>-1665.4039486784</v>
       </c>
       <c r="Q53">
-        <v>-861.4121458191998</v>
+        <v>-910.3039486784</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1334622243798294</v>
+        <v>0.1352885207210759</v>
       </c>
       <c r="T53">
-        <v>2.024531740873659</v>
+        <v>2.066709485475193</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.09073986229552024</v>
+        <v>0.08899486494368329</v>
       </c>
       <c r="W53">
-        <v>0.1825794356510596</v>
+        <v>0.1829298311193084</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3517048926182954</v>
+        <v>0.3449413369910205</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5783,22 +5783,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1600620021281568</v>
+        <v>0.1616120021281568</v>
       </c>
       <c r="C54">
-        <v>-5385.413971115684</v>
+        <v>-5869.859594851932</v>
       </c>
       <c r="D54">
-        <v>11678.23002888432</v>
+        <v>11521.93140514807</v>
       </c>
       <c r="E54">
-        <v>7844.344000000001</v>
+        <v>8172.491000000002</v>
       </c>
       <c r="F54">
-        <v>17063.644</v>
+        <v>17391.791</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5819,37 +5819,37 @@
         <v>1181.9</v>
       </c>
       <c r="M54">
-        <v>3426.3797152</v>
+        <v>3492.2716328</v>
       </c>
       <c r="N54">
-        <v>-2244.4797152</v>
+        <v>-2310.3716328</v>
       </c>
       <c r="O54">
-        <v>-579.0757665216</v>
+        <v>-596.0758812624</v>
       </c>
       <c r="P54">
-        <v>-1665.4039486784</v>
+        <v>-1714.2957515376</v>
       </c>
       <c r="Q54">
-        <v>-910.3039486784</v>
+        <v>-959.1957515376002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1352885207210759</v>
+        <v>0.1371925318002477</v>
       </c>
       <c r="T54">
-        <v>2.066709485475193</v>
+        <v>2.110682027719347</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.08899486494368329</v>
+        <v>0.08731571654851945</v>
       </c>
       <c r="W54">
-        <v>0.1829298311193084</v>
+        <v>0.1832670041170573</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3449413369910205</v>
+        <v>0.3384330098779824</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5865,22 +5865,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1616120021281568</v>
+        <v>0.1631620021281568</v>
       </c>
       <c r="C55">
-        <v>-5869.859594851932</v>
+        <v>-6350.176746639881</v>
       </c>
       <c r="D55">
-        <v>11521.93140514807</v>
+        <v>11369.76125336012</v>
       </c>
       <c r="E55">
-        <v>8172.491000000002</v>
+        <v>8500.637999999999</v>
       </c>
       <c r="F55">
-        <v>17391.791</v>
+        <v>17719.938</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5901,37 +5901,37 @@
         <v>1181.9</v>
       </c>
       <c r="M55">
-        <v>3492.2716328</v>
+        <v>3558.1635504</v>
       </c>
       <c r="N55">
-        <v>-2310.3716328</v>
+        <v>-2376.2635504</v>
       </c>
       <c r="O55">
-        <v>-596.0758812624</v>
+        <v>-613.0759960031999</v>
       </c>
       <c r="P55">
-        <v>-1714.2957515376</v>
+        <v>-1763.1875543968</v>
       </c>
       <c r="Q55">
-        <v>-959.1957515376002</v>
+        <v>-1008.0875543968</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1371925318002477</v>
+        <v>0.1391793259698183</v>
       </c>
       <c r="T55">
-        <v>2.110682027719347</v>
+        <v>2.156566419626289</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08731571654851945</v>
+        <v>0.085698758834658</v>
       </c>
       <c r="W55">
-        <v>0.1832670041170573</v>
+        <v>0.1835916892260007</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3384330098779824</v>
+        <v>0.3321657319172791</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5947,22 +5947,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1631620021281568</v>
+        <v>0.1647120021281568</v>
       </c>
       <c r="C56">
-        <v>-6350.176746639881</v>
+        <v>-6826.526868505705</v>
       </c>
       <c r="D56">
-        <v>11369.76125336012</v>
+        <v>11221.55813149429</v>
       </c>
       <c r="E56">
-        <v>8500.637999999999</v>
+        <v>8828.785</v>
       </c>
       <c r="F56">
-        <v>17719.938</v>
+        <v>18048.085</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5983,37 +5983,37 @@
         <v>1181.9</v>
       </c>
       <c r="M56">
-        <v>3558.1635504</v>
+        <v>3624.055468</v>
       </c>
       <c r="N56">
-        <v>-2376.2635504</v>
+        <v>-2442.155468</v>
       </c>
       <c r="O56">
-        <v>-613.0759960031999</v>
+        <v>-630.0761107439999</v>
       </c>
       <c r="P56">
-        <v>-1763.1875543968</v>
+        <v>-1812.079357256</v>
       </c>
       <c r="Q56">
-        <v>-1008.0875543968</v>
+        <v>-1056.979357256</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1391793259698183</v>
+        <v>0.1412544221024809</v>
       </c>
       <c r="T56">
-        <v>2.156566419626289</v>
+        <v>2.204490117840206</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.085698758834658</v>
+        <v>0.08414059958311874</v>
       </c>
       <c r="W56">
-        <v>0.1835916892260007</v>
+        <v>0.1839045676037098</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3321657319172791</v>
+        <v>0.3261263549733285</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6029,22 +6029,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1647120021281568</v>
+        <v>0.1662620021281568</v>
       </c>
       <c r="C57">
-        <v>-6826.526868505705</v>
+        <v>-7299.06309329471</v>
       </c>
       <c r="D57">
-        <v>11221.55813149429</v>
+        <v>11077.16890670529</v>
       </c>
       <c r="E57">
-        <v>8828.785</v>
+        <v>9156.932000000001</v>
       </c>
       <c r="F57">
-        <v>18048.085</v>
+        <v>18376.232</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6065,37 +6065,37 @@
         <v>1181.9</v>
       </c>
       <c r="M57">
-        <v>3624.055468</v>
+        <v>3689.9473856</v>
       </c>
       <c r="N57">
-        <v>-2442.155468</v>
+        <v>-2508.0473856</v>
       </c>
       <c r="O57">
-        <v>-630.0761107439999</v>
+        <v>-647.0762254848</v>
       </c>
       <c r="P57">
-        <v>-1812.079357256</v>
+        <v>-1860.9711601152</v>
       </c>
       <c r="Q57">
-        <v>-1056.979357256</v>
+        <v>-1105.8711601152</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1412544221024809</v>
+        <v>0.1434238407866282</v>
       </c>
       <c r="T57">
-        <v>2.204490117840206</v>
+        <v>2.254592165972938</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.08414059958311874</v>
+        <v>0.08263808887627735</v>
       </c>
       <c r="W57">
-        <v>0.1839045676037098</v>
+        <v>0.1842062717536435</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3261263549733285</v>
+        <v>0.3203026700630904</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1662620021281568</v>
+        <v>0.1678120021281568</v>
       </c>
       <c r="C58">
-        <v>-7299.06309329471</v>
+        <v>-7767.930772456742</v>
       </c>
       <c r="D58">
-        <v>11077.16890670529</v>
+        <v>10936.44822754326</v>
       </c>
       <c r="E58">
-        <v>9156.932000000001</v>
+        <v>9485.079000000002</v>
       </c>
       <c r="F58">
-        <v>18376.232</v>
+        <v>18704.379</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6147,37 +6147,37 @@
         <v>1181.9</v>
       </c>
       <c r="M58">
-        <v>3689.9473856</v>
+        <v>3755.8393032</v>
       </c>
       <c r="N58">
-        <v>-2508.0473856</v>
+        <v>-2573.9393032</v>
       </c>
       <c r="O58">
-        <v>-647.0762254848</v>
+        <v>-664.0763402256001</v>
       </c>
       <c r="P58">
-        <v>-1860.9711601152</v>
+        <v>-1909.8629629744</v>
       </c>
       <c r="Q58">
-        <v>-1105.8711601152</v>
+        <v>-1154.7629629744</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1434238407866282</v>
+        <v>0.145694162665387</v>
       </c>
       <c r="T58">
-        <v>2.254592165972938</v>
+        <v>2.307024541925797</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08263808887627735</v>
+        <v>0.08118829784336019</v>
       </c>
       <c r="W58">
-        <v>0.1842062717536435</v>
+        <v>0.1844973897930533</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3203026700630904</v>
+        <v>0.3146833249742643</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6193,22 +6193,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1678120021281568</v>
+        <v>0.1693620021281568</v>
       </c>
       <c r="C59">
-        <v>-7767.930772456742</v>
+        <v>-8233.267964107328</v>
       </c>
       <c r="D59">
-        <v>10936.44822754326</v>
+        <v>10799.25803589267</v>
       </c>
       <c r="E59">
-        <v>9485.079000000002</v>
+        <v>9813.226000000002</v>
       </c>
       <c r="F59">
-        <v>18704.379</v>
+        <v>19032.526</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6229,37 +6229,37 @@
         <v>1181.9</v>
       </c>
       <c r="M59">
-        <v>3755.8393032</v>
+        <v>3821.7312208</v>
       </c>
       <c r="N59">
-        <v>-2573.9393032</v>
+        <v>-2639.8312208</v>
       </c>
       <c r="O59">
-        <v>-664.0763402256001</v>
+        <v>-681.0764549664001</v>
       </c>
       <c r="P59">
-        <v>-1909.8629629744</v>
+        <v>-1958.7547658336</v>
       </c>
       <c r="Q59">
-        <v>-1154.7629629744</v>
+        <v>-1203.6547658336</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.145694162665387</v>
+        <v>0.148072595109801</v>
       </c>
       <c r="T59">
-        <v>2.307024541925797</v>
+        <v>2.361953697685935</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.08118829784336019</v>
+        <v>0.07978849960468157</v>
       </c>
       <c r="W59">
-        <v>0.1844973897930533</v>
+        <v>0.1847784692793799</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3146833249742643</v>
+        <v>0.3092577504057425</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6275,22 +6275,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1693620021281568</v>
+        <v>0.1709120021281568</v>
       </c>
       <c r="C60">
-        <v>-8233.267964107325</v>
+        <v>-8695.20588480962</v>
       </c>
       <c r="D60">
-        <v>10799.25803589267</v>
+        <v>10665.46711519038</v>
       </c>
       <c r="E60">
-        <v>9813.225999999999</v>
+        <v>10141.373</v>
       </c>
       <c r="F60">
-        <v>19032.526</v>
+        <v>19360.673</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6311,37 +6311,37 @@
         <v>1181.9</v>
       </c>
       <c r="M60">
-        <v>3821.7312208</v>
+        <v>3887.6231384</v>
       </c>
       <c r="N60">
-        <v>-2639.8312208</v>
+        <v>-2705.7231384</v>
       </c>
       <c r="O60">
-        <v>-681.0764549664</v>
+        <v>-698.0765697072</v>
       </c>
       <c r="P60">
-        <v>-1958.7547658336</v>
+        <v>-2007.6465686928</v>
       </c>
       <c r="Q60">
-        <v>-1203.6547658336</v>
+        <v>-1252.5465686928</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.148072595109801</v>
+        <v>0.1505670486490644</v>
       </c>
       <c r="T60">
-        <v>2.361953697685935</v>
+        <v>2.419562324458763</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07978849960468158</v>
+        <v>0.07843615215375478</v>
       </c>
       <c r="W60">
-        <v>0.1847784692793799</v>
+        <v>0.185050020647526</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3092577504057425</v>
+        <v>0.3040160936192046</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6357,22 +6357,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1709120021281568</v>
+        <v>0.1724620021281568</v>
       </c>
       <c r="C61">
-        <v>-8695.20588480962</v>
+        <v>-9153.869328184786</v>
       </c>
       <c r="D61">
-        <v>10665.46711519038</v>
+        <v>10534.95067181521</v>
       </c>
       <c r="E61">
-        <v>10141.373</v>
+        <v>10469.52</v>
       </c>
       <c r="F61">
-        <v>19360.673</v>
+        <v>19688.82</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6393,37 +6393,37 @@
         <v>1181.9</v>
       </c>
       <c r="M61">
-        <v>3887.6231384</v>
+        <v>3953.515055999999</v>
       </c>
       <c r="N61">
-        <v>-2705.7231384</v>
+        <v>-2771.615055999999</v>
       </c>
       <c r="O61">
-        <v>-698.0765697072</v>
+        <v>-715.0766844479998</v>
       </c>
       <c r="P61">
-        <v>-2007.6465686928</v>
+        <v>-2056.538371551999</v>
       </c>
       <c r="Q61">
-        <v>-1252.5465686928</v>
+        <v>-1301.438371551999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1505670486490644</v>
+        <v>0.153186224865291</v>
       </c>
       <c r="T61">
-        <v>2.419562324458763</v>
+        <v>2.480051382570231</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07843615215375478</v>
+        <v>0.0771288829511922</v>
       </c>
       <c r="W61">
-        <v>0.185050020647526</v>
+        <v>0.1853125203034006</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3040160936192046</v>
+        <v>0.2989491587255512</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6439,22 +6439,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1724620021281568</v>
+        <v>0.1740120021281568</v>
       </c>
       <c r="C62">
-        <v>-9153.869328184786</v>
+        <v>-9609.377053158034</v>
       </c>
       <c r="D62">
-        <v>10534.95067181521</v>
+        <v>10407.58994684196</v>
       </c>
       <c r="E62">
-        <v>10469.52</v>
+        <v>10797.667</v>
       </c>
       <c r="F62">
-        <v>19688.82</v>
+        <v>20016.967</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6475,37 +6475,37 @@
         <v>1181.9</v>
       </c>
       <c r="M62">
-        <v>3953.515055999999</v>
+        <v>4019.4069736</v>
       </c>
       <c r="N62">
-        <v>-2771.615055999999</v>
+        <v>-2837.5069736</v>
       </c>
       <c r="O62">
-        <v>-715.0766844479998</v>
+        <v>-732.0767991887999</v>
       </c>
       <c r="P62">
-        <v>-2056.538371551999</v>
+        <v>-2105.4301744112</v>
       </c>
       <c r="Q62">
-        <v>-1301.438371551999</v>
+        <v>-1350.3301744112</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.153186224865291</v>
+        <v>0.1559397178105549</v>
       </c>
       <c r="T62">
-        <v>2.480051382570231</v>
+        <v>2.543642443661776</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.0771288829511922</v>
+        <v>0.07586447503395954</v>
       </c>
       <c r="W62">
-        <v>0.1853125203034006</v>
+        <v>0.1855664134131809</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2989491587255512</v>
+        <v>0.2940483528448044</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6521,22 +6521,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1740120021281568</v>
+        <v>0.1755620021281568</v>
       </c>
       <c r="C63">
-        <v>-9609.377053158034</v>
+        <v>-10061.84214437917</v>
       </c>
       <c r="D63">
-        <v>10407.58994684196</v>
+        <v>10283.27185562083</v>
       </c>
       <c r="E63">
-        <v>10797.667</v>
+        <v>11125.814</v>
       </c>
       <c r="F63">
-        <v>20016.967</v>
+        <v>20345.114</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6557,37 +6557,37 @@
         <v>1181.9</v>
       </c>
       <c r="M63">
-        <v>4019.4069736</v>
+        <v>4085.2988912</v>
       </c>
       <c r="N63">
-        <v>-2837.5069736</v>
+        <v>-2903.3988912</v>
       </c>
       <c r="O63">
-        <v>-732.0767991887999</v>
+        <v>-749.0769139295999</v>
       </c>
       <c r="P63">
-        <v>-2105.4301744112</v>
+        <v>-2154.3219772704</v>
       </c>
       <c r="Q63">
-        <v>-1350.3301744112</v>
+        <v>-1399.2219772704</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1559397178105549</v>
+        <v>0.1588381314371484</v>
       </c>
       <c r="T63">
-        <v>2.543642443661776</v>
+        <v>2.610580402705507</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.07586447503395954</v>
+        <v>0.07464085446889568</v>
       </c>
       <c r="W63">
-        <v>0.1855664134131809</v>
+        <v>0.1858121164226458</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2940483528448044</v>
+        <v>0.2893056374763399</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6603,22 +6603,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1755620021281568</v>
+        <v>0.1771120021281568</v>
       </c>
       <c r="C64">
-        <v>-10061.84214437917</v>
+        <v>-10511.37234711685</v>
       </c>
       <c r="D64">
-        <v>10283.27185562083</v>
+        <v>10161.88865288315</v>
       </c>
       <c r="E64">
-        <v>11125.814</v>
+        <v>11453.961</v>
       </c>
       <c r="F64">
-        <v>20345.114</v>
+        <v>20673.261</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6639,37 +6639,37 @@
         <v>1181.9</v>
       </c>
       <c r="M64">
-        <v>4085.2988912</v>
+        <v>4151.1908088</v>
       </c>
       <c r="N64">
-        <v>-2903.3988912</v>
+        <v>-2969.2908088</v>
       </c>
       <c r="O64">
-        <v>-749.0769139295999</v>
+        <v>-766.0770286704</v>
       </c>
       <c r="P64">
-        <v>-2154.3219772704</v>
+        <v>-2203.2137801296</v>
       </c>
       <c r="Q64">
-        <v>-1399.2219772704</v>
+        <v>-1448.1137801296</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1588381314371484</v>
+        <v>0.1618932160705849</v>
       </c>
       <c r="T64">
-        <v>2.610580402705507</v>
+        <v>2.681136629805656</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.07464085446889568</v>
+        <v>0.07345607900113542</v>
       </c>
       <c r="W64">
-        <v>0.1858121164226458</v>
+        <v>0.186050019336572</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2893056374763399</v>
+        <v>0.2847134845005249</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6685,22 +6685,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1771120021281568</v>
+        <v>0.1786620021281568</v>
       </c>
       <c r="C65">
-        <v>-10511.37234711685</v>
+        <v>-10958.07037871109</v>
       </c>
       <c r="D65">
-        <v>10161.88865288315</v>
+        <v>10043.33762128891</v>
       </c>
       <c r="E65">
-        <v>11453.961</v>
+        <v>11782.108</v>
       </c>
       <c r="F65">
-        <v>20673.261</v>
+        <v>21001.408</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6721,37 +6721,37 @@
         <v>1181.9</v>
       </c>
       <c r="M65">
-        <v>4151.1908088</v>
+        <v>4217.0827264</v>
       </c>
       <c r="N65">
-        <v>-2969.2908088</v>
+        <v>-3035.1827264</v>
       </c>
       <c r="O65">
-        <v>-766.0770286704</v>
+        <v>-783.0771434112</v>
       </c>
       <c r="P65">
-        <v>-2203.2137801296</v>
+        <v>-2252.1055829888</v>
       </c>
       <c r="Q65">
-        <v>-1448.1137801296</v>
+        <v>-1497.0055829888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1618932160705849</v>
+        <v>0.1651180276281011</v>
       </c>
       <c r="T65">
-        <v>2.681136629805656</v>
+        <v>2.755612647300257</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.07345607900113542</v>
+        <v>0.07230832776674267</v>
       </c>
       <c r="W65">
-        <v>0.186050019336572</v>
+        <v>0.1862804877844381</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2847134845005249</v>
+        <v>0.2802648363052042</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6767,22 +6767,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1786620021281568</v>
+        <v>0.1802120021281568</v>
       </c>
       <c r="C66">
-        <v>-10958.07037871109</v>
+        <v>-11402.0342184763</v>
       </c>
       <c r="D66">
-        <v>10043.33762128891</v>
+        <v>9927.520781523703</v>
       </c>
       <c r="E66">
-        <v>11782.108</v>
+        <v>12110.255</v>
       </c>
       <c r="F66">
-        <v>21001.408</v>
+        <v>21329.555</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6803,37 +6803,37 @@
         <v>1181.9</v>
       </c>
       <c r="M66">
-        <v>4217.0827264</v>
+        <v>4282.974644</v>
       </c>
       <c r="N66">
-        <v>-3035.1827264</v>
+        <v>-3101.074644</v>
       </c>
       <c r="O66">
-        <v>-783.0771434112</v>
+        <v>-800.077258152</v>
       </c>
       <c r="P66">
-        <v>-2252.1055829888</v>
+        <v>-2300.997385848</v>
       </c>
       <c r="Q66">
-        <v>-1497.0055829888</v>
+        <v>-1545.897385848</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1651180276281011</v>
+        <v>0.1685271141317612</v>
       </c>
       <c r="T66">
-        <v>2.755612647300257</v>
+        <v>2.834344437223122</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.07230832776674267</v>
+        <v>0.07119589195494663</v>
       </c>
       <c r="W66">
-        <v>0.1862804877844381</v>
+        <v>0.1865038648954467</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2802648363052042</v>
+        <v>0.2759530695928164</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6849,22 +6849,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1802120021281568</v>
+        <v>0.1817620021281568</v>
       </c>
       <c r="C67">
-        <v>-11402.0342184763</v>
+        <v>-11843.35737777452</v>
       </c>
       <c r="D67">
-        <v>9927.520781523703</v>
+        <v>9814.344622225479</v>
       </c>
       <c r="E67">
-        <v>12110.255</v>
+        <v>12438.402</v>
       </c>
       <c r="F67">
-        <v>21329.555</v>
+        <v>21657.702</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6885,37 +6885,37 @@
         <v>1181.9</v>
       </c>
       <c r="M67">
-        <v>4282.974644</v>
+        <v>4348.8665616</v>
       </c>
       <c r="N67">
-        <v>-3101.074644</v>
+        <v>-3166.9665616</v>
       </c>
       <c r="O67">
-        <v>-800.077258152</v>
+        <v>-817.0773728928</v>
       </c>
       <c r="P67">
-        <v>-2300.997385848</v>
+        <v>-2349.8891887072</v>
       </c>
       <c r="Q67">
-        <v>-1545.897385848</v>
+        <v>-1594.7891887072</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1685271141317612</v>
+        <v>0.1721367351356365</v>
       </c>
       <c r="T67">
-        <v>2.834344437223122</v>
+        <v>2.917707508906155</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.07119589195494663</v>
+        <v>0.07011716631926562</v>
       </c>
       <c r="W67">
-        <v>0.1865038648954467</v>
+        <v>0.1867204730030915</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2759530695928164</v>
+        <v>0.2717719624777738</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6931,22 +6931,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1817620021281568</v>
+        <v>0.1833120021281568</v>
       </c>
       <c r="C68">
-        <v>-11843.35737777452</v>
+        <v>-12282.1291518235</v>
       </c>
       <c r="D68">
-        <v>9814.344622225479</v>
+        <v>9703.719848176501</v>
       </c>
       <c r="E68">
-        <v>12438.402</v>
+        <v>12766.549</v>
       </c>
       <c r="F68">
-        <v>21657.702</v>
+        <v>21985.849</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6967,37 +6967,37 @@
         <v>1181.9</v>
       </c>
       <c r="M68">
-        <v>4348.8665616</v>
+        <v>4414.7584792</v>
       </c>
       <c r="N68">
-        <v>-3166.9665616</v>
+        <v>-3232.8584792</v>
       </c>
       <c r="O68">
-        <v>-817.0773728928</v>
+        <v>-834.0774876336</v>
       </c>
       <c r="P68">
-        <v>-2349.8891887072</v>
+        <v>-2398.7809915664</v>
       </c>
       <c r="Q68">
-        <v>-1594.7891887072</v>
+        <v>-1643.6809915664</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1721367351356365</v>
+        <v>0.1759651210488377</v>
       </c>
       <c r="T68">
-        <v>2.917707508906155</v>
+        <v>3.006122887963918</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.07011716631926562</v>
+        <v>0.06907064144882882</v>
       </c>
       <c r="W68">
-        <v>0.1867204730030915</v>
+        <v>0.1869306151970752</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2717719624777738</v>
+        <v>0.2677156645303443</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7013,22 +7013,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1833120021281568</v>
+        <v>0.1848620021281568</v>
       </c>
       <c r="C69">
-        <v>-12282.1291518235</v>
+        <v>-12718.43485466464</v>
       </c>
       <c r="D69">
-        <v>9703.719848176501</v>
+        <v>9595.561145335363</v>
       </c>
       <c r="E69">
-        <v>12766.549</v>
+        <v>13094.696</v>
       </c>
       <c r="F69">
-        <v>21985.849</v>
+        <v>22313.996</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7049,37 +7049,37 @@
         <v>1181.9</v>
       </c>
       <c r="M69">
-        <v>4414.7584792</v>
+        <v>4480.6503968</v>
       </c>
       <c r="N69">
-        <v>-3232.8584792</v>
+        <v>-3298.7503968</v>
       </c>
       <c r="O69">
-        <v>-834.0774876336</v>
+        <v>-851.0776023743999</v>
       </c>
       <c r="P69">
-        <v>-2398.7809915664</v>
+        <v>-2447.6727944256</v>
       </c>
       <c r="Q69">
-        <v>-1643.6809915664</v>
+        <v>-1692.5727944256</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1759651210488377</v>
+        <v>0.1800327810816138</v>
       </c>
       <c r="T69">
-        <v>3.006122887963918</v>
+        <v>3.10006422821279</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06907064144882882</v>
+        <v>0.06805489672164017</v>
       </c>
       <c r="W69">
-        <v>0.1869306151970752</v>
+        <v>0.1871345767382947</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2677156645303443</v>
+        <v>0.2637786694637216</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7095,22 +7095,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1848620021281568</v>
+        <v>0.1864120021281568</v>
       </c>
       <c r="C70">
-        <v>-12718.43485466464</v>
+        <v>-13152.35603859037</v>
       </c>
       <c r="D70">
-        <v>9595.561145335363</v>
+        <v>9489.786961409625</v>
       </c>
       <c r="E70">
-        <v>13094.696</v>
+        <v>13422.843</v>
       </c>
       <c r="F70">
-        <v>22313.996</v>
+        <v>22642.143</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7131,37 +7131,37 @@
         <v>1181.9</v>
       </c>
       <c r="M70">
-        <v>4480.6503968</v>
+        <v>4546.542314400001</v>
       </c>
       <c r="N70">
-        <v>-3298.7503968</v>
+        <v>-3364.6423144</v>
       </c>
       <c r="O70">
-        <v>-851.0776023743999</v>
+        <v>-868.0777171152001</v>
       </c>
       <c r="P70">
-        <v>-2447.6727944256</v>
+        <v>-2496.564597284801</v>
       </c>
       <c r="Q70">
-        <v>-1692.5727944256</v>
+        <v>-1741.464597284801</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1800327810816138</v>
+        <v>0.1843628707939239</v>
       </c>
       <c r="T70">
-        <v>3.10006422821279</v>
+        <v>3.200066300090622</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.06805489672164017</v>
+        <v>0.06706859387060189</v>
       </c>
       <c r="W70">
-        <v>0.1871345767382947</v>
+        <v>0.1873326263507831</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2637786694637216</v>
+        <v>0.2599557901961314</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7177,22 +7177,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1864120021281568</v>
+        <v>0.1879620021281568</v>
       </c>
       <c r="C71">
-        <v>-13152.35603859037</v>
+        <v>-13583.97069921691</v>
       </c>
       <c r="D71">
-        <v>9489.786961409625</v>
+        <v>9386.319300783089</v>
       </c>
       <c r="E71">
-        <v>13422.843</v>
+        <v>13750.99</v>
       </c>
       <c r="F71">
-        <v>22642.143</v>
+        <v>22970.29</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7213,37 +7213,37 @@
         <v>1181.9</v>
       </c>
       <c r="M71">
-        <v>4546.542314400001</v>
+        <v>4612.434232000001</v>
       </c>
       <c r="N71">
-        <v>-3364.6423144</v>
+        <v>-3430.534232</v>
       </c>
       <c r="O71">
-        <v>-868.0777171152001</v>
+        <v>-885.0778318560001</v>
       </c>
       <c r="P71">
-        <v>-2496.564597284801</v>
+        <v>-2545.456400144</v>
       </c>
       <c r="Q71">
-        <v>-1741.464597284801</v>
+        <v>-1790.356400144</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1843628707939239</v>
+        <v>0.1889816331537214</v>
       </c>
       <c r="T71">
-        <v>3.200066300090622</v>
+        <v>3.30673517676031</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.06706859387060189</v>
+        <v>0.06611047110102188</v>
       </c>
       <c r="W71">
-        <v>0.1873326263507831</v>
+        <v>0.1875250174029148</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2599557901961314</v>
+        <v>0.2562421360504723</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7259,22 +7259,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1879620021281568</v>
+        <v>0.1895120021281568</v>
       </c>
       <c r="C72">
-        <v>-13583.97069921691</v>
+        <v>-14013.35346728616</v>
       </c>
       <c r="D72">
-        <v>9386.319300783089</v>
+        <v>9285.083532713839</v>
       </c>
       <c r="E72">
-        <v>13750.99</v>
+        <v>14079.137</v>
       </c>
       <c r="F72">
-        <v>22970.29</v>
+        <v>23298.437</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7295,37 +7295,37 @@
         <v>1181.9</v>
       </c>
       <c r="M72">
-        <v>4612.434232000001</v>
+        <v>4678.3261496</v>
       </c>
       <c r="N72">
-        <v>-3430.534232</v>
+        <v>-3496.4261496</v>
       </c>
       <c r="O72">
-        <v>-885.0778318560001</v>
+        <v>-902.0779465968001</v>
       </c>
       <c r="P72">
-        <v>-2545.456400144</v>
+        <v>-2594.3482030032</v>
       </c>
       <c r="Q72">
-        <v>-1790.356400144</v>
+        <v>-1839.2482030032</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1889816331537214</v>
+        <v>0.1939189308486773</v>
       </c>
       <c r="T72">
-        <v>3.30673517676031</v>
+        <v>3.420760527683079</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.06611047110102188</v>
+        <v>0.06517933770523283</v>
       </c>
       <c r="W72">
-        <v>0.1875250174029148</v>
+        <v>0.1877119889887892</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2562421360504723</v>
+        <v>0.2526330918807473</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7341,22 +7341,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1895120021281568</v>
+        <v>0.1910620021281568</v>
       </c>
       <c r="C73">
-        <v>-14013.35346728616</v>
+        <v>-14440.5757881881</v>
       </c>
       <c r="D73">
-        <v>9285.083532713839</v>
+        <v>9186.008211811892</v>
       </c>
       <c r="E73">
-        <v>14079.137</v>
+        <v>14407.284</v>
       </c>
       <c r="F73">
-        <v>23298.437</v>
+        <v>23626.584</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7377,37 +7377,37 @@
         <v>1181.9</v>
       </c>
       <c r="M73">
-        <v>4678.3261496</v>
+        <v>4744.218067199999</v>
       </c>
       <c r="N73">
-        <v>-3496.426149599999</v>
+        <v>-3562.318067199999</v>
       </c>
       <c r="O73">
-        <v>-902.0779465967998</v>
+        <v>-919.0780613375998</v>
       </c>
       <c r="P73">
-        <v>-2594.3482030032</v>
+        <v>-2643.2400058624</v>
       </c>
       <c r="Q73">
-        <v>-1839.2482030032</v>
+        <v>-1888.1400058624</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1939189308486773</v>
+        <v>0.1992088926647015</v>
       </c>
       <c r="T73">
-        <v>3.420760527683078</v>
+        <v>3.542930546528902</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.06517933770523285</v>
+        <v>0.0642740691259935</v>
       </c>
       <c r="W73">
-        <v>0.1877119889887892</v>
+        <v>0.1878937669195005</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2526330918807475</v>
+        <v>0.2491242989379593</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7423,22 +7423,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1910620021281568</v>
+        <v>0.1926120021281568</v>
       </c>
       <c r="C74">
-        <v>-14440.5757881881</v>
+        <v>-14865.70609011106</v>
       </c>
       <c r="D74">
-        <v>9186.008211811892</v>
+        <v>9089.024909888938</v>
       </c>
       <c r="E74">
-        <v>14407.284</v>
+        <v>14735.431</v>
       </c>
       <c r="F74">
-        <v>23626.584</v>
+        <v>23954.731</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7459,37 +7459,37 @@
         <v>1181.9</v>
       </c>
       <c r="M74">
-        <v>4744.218067199999</v>
+        <v>4810.109984799999</v>
       </c>
       <c r="N74">
-        <v>-3562.318067199999</v>
+        <v>-3628.209984799999</v>
       </c>
       <c r="O74">
-        <v>-919.0780613375998</v>
+        <v>-936.0781760783999</v>
       </c>
       <c r="P74">
-        <v>-2643.2400058624</v>
+        <v>-2692.1318087216</v>
       </c>
       <c r="Q74">
-        <v>-1888.1400058624</v>
+        <v>-1937.0318087216</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1992088926647015</v>
+        <v>0.2048907035041349</v>
       </c>
       <c r="T74">
-        <v>3.542930546528902</v>
+        <v>3.674150196400343</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.0642740691259935</v>
+        <v>0.06339360242563742</v>
       </c>
       <c r="W74">
-        <v>0.1878937669195005</v>
+        <v>0.188070564632932</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2491242989379593</v>
+        <v>0.2457116373086722</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7505,22 +7505,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1926120021281568</v>
+        <v>0.1941620021281568</v>
       </c>
       <c r="C75">
-        <v>-14865.70609011106</v>
+        <v>-15288.80994165151</v>
       </c>
       <c r="D75">
-        <v>9089.024909888938</v>
+        <v>8994.068058348485</v>
       </c>
       <c r="E75">
-        <v>14735.431</v>
+        <v>15063.578</v>
       </c>
       <c r="F75">
-        <v>23954.731</v>
+        <v>24282.878</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7541,37 +7541,37 @@
         <v>1181.9</v>
       </c>
       <c r="M75">
-        <v>4810.109984799999</v>
+        <v>4876.001902399999</v>
       </c>
       <c r="N75">
-        <v>-3628.209984799999</v>
+        <v>-3694.101902399999</v>
       </c>
       <c r="O75">
-        <v>-936.0781760783999</v>
+        <v>-953.0782908191999</v>
       </c>
       <c r="P75">
-        <v>-2692.1318087216</v>
+        <v>-2741.023611580799</v>
       </c>
       <c r="Q75">
-        <v>-1937.0318087216</v>
+        <v>-1985.923611580799</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2048907035041349</v>
+        <v>0.2110095767158323</v>
       </c>
       <c r="T75">
-        <v>3.674150196400343</v>
+        <v>3.815463665492664</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.06339360242563742</v>
+        <v>0.06253693212258828</v>
       </c>
       <c r="W75">
-        <v>0.188070564632932</v>
+        <v>0.1882425840297843</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2457116373086722</v>
+        <v>0.2423912097774739</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7587,22 +7587,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1941620021281568</v>
+        <v>0.1957120021281568</v>
       </c>
       <c r="C76">
-        <v>-15288.80994165151</v>
+        <v>-15709.95019964644</v>
       </c>
       <c r="D76">
-        <v>8994.068058348485</v>
+        <v>8901.074800353554</v>
       </c>
       <c r="E76">
-        <v>15063.578</v>
+        <v>15391.725</v>
       </c>
       <c r="F76">
-        <v>24282.878</v>
+        <v>24611.025</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7623,37 +7623,37 @@
         <v>1181.9</v>
       </c>
       <c r="M76">
-        <v>4876.001902399999</v>
+        <v>4941.893819999999</v>
       </c>
       <c r="N76">
-        <v>-3694.101902399999</v>
+        <v>-3759.993819999999</v>
       </c>
       <c r="O76">
-        <v>-953.0782908191999</v>
+        <v>-970.0784055599999</v>
       </c>
       <c r="P76">
-        <v>-2741.023611580799</v>
+        <v>-2789.915414439999</v>
       </c>
       <c r="Q76">
-        <v>-1985.923611580799</v>
+        <v>-2034.81541444</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2110095767158323</v>
+        <v>0.2176179597844657</v>
       </c>
       <c r="T76">
-        <v>3.815463665492664</v>
+        <v>3.968082212112371</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.06253693212258828</v>
+        <v>0.06170310636095376</v>
       </c>
       <c r="W76">
-        <v>0.1882425840297843</v>
+        <v>0.1884100162427205</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2423912097774739</v>
+        <v>0.239159326980441</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7669,22 +7669,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1957120021281568</v>
+        <v>0.1972620021281568</v>
       </c>
       <c r="C77">
-        <v>-15709.95019964644</v>
+        <v>-16129.18714792848</v>
       </c>
       <c r="D77">
-        <v>8901.074800353554</v>
+        <v>8809.984852071515</v>
       </c>
       <c r="E77">
-        <v>15391.725</v>
+        <v>15719.872</v>
       </c>
       <c r="F77">
-        <v>24611.025</v>
+        <v>24939.172</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7705,37 +7705,37 @@
         <v>1181.9</v>
       </c>
       <c r="M77">
-        <v>4941.893819999999</v>
+        <v>5007.7857376</v>
       </c>
       <c r="N77">
-        <v>-3759.993819999999</v>
+        <v>-3825.8857376</v>
       </c>
       <c r="O77">
-        <v>-970.0784055599999</v>
+        <v>-987.0785203008001</v>
       </c>
       <c r="P77">
-        <v>-2789.915414439999</v>
+        <v>-2838.8072172992</v>
       </c>
       <c r="Q77">
-        <v>-2034.81541444</v>
+        <v>-2083.7072172992</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2176179597844657</v>
+        <v>0.2247770414421517</v>
       </c>
       <c r="T77">
-        <v>3.968082212112371</v>
+        <v>4.133418970950387</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.06170310636095376</v>
+        <v>0.06089122338252015</v>
       </c>
       <c r="W77">
-        <v>0.1884100162427205</v>
+        <v>0.1885730423447899</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.239159326980441</v>
+        <v>0.2360124937306982</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7751,22 +7751,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1972620021281568</v>
+        <v>0.1988120021281568</v>
       </c>
       <c r="C78">
-        <v>-16129.18714792848</v>
+        <v>-16546.57862764762</v>
       </c>
       <c r="D78">
-        <v>8809.984852071515</v>
+        <v>8720.740372352375</v>
       </c>
       <c r="E78">
-        <v>15719.872</v>
+        <v>16048.019</v>
       </c>
       <c r="F78">
-        <v>24939.172</v>
+        <v>25267.319</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7787,37 +7787,37 @@
         <v>1181.9</v>
       </c>
       <c r="M78">
-        <v>5007.7857376</v>
+        <v>5073.6776552</v>
       </c>
       <c r="N78">
-        <v>-3825.8857376</v>
+        <v>-3891.7776552</v>
       </c>
       <c r="O78">
-        <v>-987.0785203008001</v>
+        <v>-1004.0786350416</v>
       </c>
       <c r="P78">
-        <v>-2838.8072172992</v>
+        <v>-2887.6990201584</v>
       </c>
       <c r="Q78">
-        <v>-2083.7072172992</v>
+        <v>-2132.5990201584</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2247770414421517</v>
+        <v>0.2325586519396366</v>
       </c>
       <c r="T78">
-        <v>4.133418970950387</v>
+        <v>4.313132839252577</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.06089122338252015</v>
+        <v>0.06010042827365625</v>
       </c>
       <c r="W78">
-        <v>0.1885730423447899</v>
+        <v>0.1887318340026498</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2360124937306982</v>
+        <v>0.2329473964095203</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7833,22 +7833,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1988120021281568</v>
+        <v>0.2003620021281568</v>
       </c>
       <c r="C79">
-        <v>-16546.57862764762</v>
+        <v>-16962.18015975143</v>
       </c>
       <c r="D79">
-        <v>8720.740372352375</v>
+        <v>8633.285840248565</v>
       </c>
       <c r="E79">
-        <v>16048.019</v>
+        <v>16376.166</v>
       </c>
       <c r="F79">
-        <v>25267.319</v>
+        <v>25595.466</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7869,37 +7869,37 @@
         <v>1181.9</v>
       </c>
       <c r="M79">
-        <v>5073.6776552</v>
+        <v>5139.5695728</v>
       </c>
       <c r="N79">
-        <v>-3891.7776552</v>
+        <v>-3957.6695728</v>
       </c>
       <c r="O79">
-        <v>-1004.0786350416</v>
+        <v>-1021.0787497824</v>
       </c>
       <c r="P79">
-        <v>-2887.6990201584</v>
+        <v>-2936.5908230176</v>
       </c>
       <c r="Q79">
-        <v>-2132.5990201584</v>
+        <v>-2181.4908230176</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2325586519396366</v>
+        <v>0.2410476815732565</v>
       </c>
       <c r="T79">
-        <v>4.313132839252577</v>
+        <v>4.509184331945876</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.06010042827365625</v>
+        <v>0.05932990996245553</v>
       </c>
       <c r="W79">
-        <v>0.1887318340026498</v>
+        <v>0.1888865540795389</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2329473964095203</v>
+        <v>0.229960891327347</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7915,22 +7915,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2003620021281568</v>
+        <v>0.2019120021281568</v>
       </c>
       <c r="C80">
-        <v>-16962.18015975143</v>
+        <v>-17376.04506016885</v>
       </c>
       <c r="D80">
-        <v>8633.285840248565</v>
+        <v>8547.567939831146</v>
       </c>
       <c r="E80">
-        <v>16376.166</v>
+        <v>16704.313</v>
       </c>
       <c r="F80">
-        <v>25595.466</v>
+        <v>25923.613</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7951,37 +7951,37 @@
         <v>1181.9</v>
       </c>
       <c r="M80">
-        <v>5139.5695728</v>
+        <v>5205.4614904</v>
       </c>
       <c r="N80">
-        <v>-3957.6695728</v>
+        <v>-4023.5614904</v>
       </c>
       <c r="O80">
-        <v>-1021.0787497824</v>
+        <v>-1038.0788645232</v>
       </c>
       <c r="P80">
-        <v>-2936.5908230176</v>
+        <v>-2985.4826258768</v>
       </c>
       <c r="Q80">
-        <v>-2181.4908230176</v>
+        <v>-2230.3826258768</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2410476815732565</v>
+        <v>0.250345190219602</v>
       </c>
       <c r="T80">
-        <v>4.509184331945876</v>
+        <v>4.723907395371871</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05932990996245553</v>
+        <v>0.05857889844394343</v>
       </c>
       <c r="W80">
-        <v>0.1888865540795389</v>
+        <v>0.1890373571924562</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.229960891327347</v>
+        <v>0.227049993968773</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7997,22 +7997,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2019120021281568</v>
+        <v>0.2034620021281568</v>
       </c>
       <c r="C81">
-        <v>-17376.04506016885</v>
+        <v>-17788.2245481996</v>
       </c>
       <c r="D81">
-        <v>8547.567939831146</v>
+        <v>8463.535451800399</v>
       </c>
       <c r="E81">
-        <v>16704.313</v>
+        <v>17032.46</v>
       </c>
       <c r="F81">
-        <v>25923.613</v>
+        <v>26251.76</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8033,37 +8033,37 @@
         <v>1181.9</v>
       </c>
       <c r="M81">
-        <v>5205.4614904</v>
+        <v>5271.353408</v>
       </c>
       <c r="N81">
-        <v>-4023.5614904</v>
+        <v>-4089.453408</v>
       </c>
       <c r="O81">
-        <v>-1038.0788645232</v>
+        <v>-1055.078979264</v>
       </c>
       <c r="P81">
-        <v>-2985.4826258768</v>
+        <v>-3034.374428736</v>
       </c>
       <c r="Q81">
-        <v>-2230.3826258768</v>
+        <v>-2279.274428736</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.250345190219602</v>
+        <v>0.2605724497305821</v>
       </c>
       <c r="T81">
-        <v>4.723907395371871</v>
+        <v>4.960102765140464</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05857889844394343</v>
+        <v>0.05784666221339414</v>
       </c>
       <c r="W81">
-        <v>0.1890373571924562</v>
+        <v>0.1891843902275505</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.227049993968773</v>
+        <v>0.2242118690441633</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8079,22 +8079,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2034620021281568</v>
+        <v>0.2050120021281568</v>
       </c>
       <c r="C82">
-        <v>-17788.2245481996</v>
+        <v>-18198.7678485723</v>
       </c>
       <c r="D82">
-        <v>8463.535451800399</v>
+        <v>8381.139151427695</v>
       </c>
       <c r="E82">
-        <v>17032.46</v>
+        <v>17360.607</v>
       </c>
       <c r="F82">
-        <v>26251.76</v>
+        <v>26579.907</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8115,37 +8115,37 @@
         <v>1181.9</v>
       </c>
       <c r="M82">
-        <v>5271.353408</v>
+        <v>5337.2453256</v>
       </c>
       <c r="N82">
-        <v>-4089.453408</v>
+        <v>-4155.345325599999</v>
       </c>
       <c r="O82">
-        <v>-1055.078979264</v>
+        <v>-1072.0790940048</v>
       </c>
       <c r="P82">
-        <v>-3034.374428736</v>
+        <v>-3083.266231595199</v>
       </c>
       <c r="Q82">
-        <v>-2279.274428736</v>
+        <v>-2328.166231595199</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2605724497305821</v>
+        <v>0.2718762628742969</v>
       </c>
       <c r="T82">
-        <v>4.960102765140464</v>
+        <v>5.221160805411015</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.05784666221339414</v>
+        <v>0.05713250588977199</v>
       </c>
       <c r="W82">
-        <v>0.1891843902275505</v>
+        <v>0.1893277928173338</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2242118690441633</v>
+        <v>0.2214438212781861</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8161,22 +8161,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2050120021281568</v>
+        <v>0.2065620021281568</v>
       </c>
       <c r="C83">
-        <v>-18198.7678485723</v>
+        <v>-18607.72228759858</v>
       </c>
       <c r="D83">
-        <v>8381.139151427695</v>
+        <v>8300.331712401423</v>
       </c>
       <c r="E83">
-        <v>17360.607</v>
+        <v>17688.754</v>
       </c>
       <c r="F83">
-        <v>26579.907</v>
+        <v>26908.054</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8197,37 +8197,37 @@
         <v>1181.9</v>
       </c>
       <c r="M83">
-        <v>5337.2453256</v>
+        <v>5403.1372432</v>
       </c>
       <c r="N83">
-        <v>-4155.345325599999</v>
+        <v>-4221.237243199999</v>
       </c>
       <c r="O83">
-        <v>-1072.0790940048</v>
+        <v>-1089.0792087456</v>
       </c>
       <c r="P83">
-        <v>-3083.266231595199</v>
+        <v>-3132.1580344544</v>
       </c>
       <c r="Q83">
-        <v>-2328.166231595199</v>
+        <v>-2377.0580344544</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2718762628742969</v>
+        <v>0.2844360552562023</v>
       </c>
       <c r="T83">
-        <v>5.221160805411015</v>
+        <v>5.511225294600516</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.05713250588977199</v>
+        <v>0.05643576801306745</v>
       </c>
       <c r="W83">
-        <v>0.1893277928173338</v>
+        <v>0.1894676977829761</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2214438212781861</v>
+        <v>0.2187432868723546</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8243,22 +8243,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2065620021281568</v>
+        <v>0.2081120021281568</v>
       </c>
       <c r="C84">
-        <v>-18607.72228759858</v>
+        <v>-19015.13338381781</v>
       </c>
       <c r="D84">
-        <v>8300.331712401423</v>
+        <v>8221.06761618219</v>
       </c>
       <c r="E84">
-        <v>17688.754</v>
+        <v>18016.901</v>
       </c>
       <c r="F84">
-        <v>26908.054</v>
+        <v>27236.201</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8279,37 +8279,37 @@
         <v>1181.9</v>
       </c>
       <c r="M84">
-        <v>5403.1372432</v>
+        <v>5469.029160800001</v>
       </c>
       <c r="N84">
-        <v>-4221.237243199999</v>
+        <v>-4287.129160800001</v>
       </c>
       <c r="O84">
-        <v>-1089.0792087456</v>
+        <v>-1106.0793234864</v>
       </c>
       <c r="P84">
-        <v>-3132.1580344544</v>
+        <v>-3181.049837313601</v>
       </c>
       <c r="Q84">
-        <v>-2377.0580344544</v>
+        <v>-2425.949837313601</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2844360552562023</v>
+        <v>0.2984734702712731</v>
       </c>
       <c r="T84">
-        <v>5.511225294600516</v>
+        <v>5.835415017812313</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.05643576801306745</v>
+        <v>0.05575581900086182</v>
       </c>
       <c r="W84">
-        <v>0.1894676977829761</v>
+        <v>0.189604231544627</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2187432868723546</v>
+        <v>0.2161078255847356</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8325,22 +8325,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2081120021281568</v>
+        <v>0.2096620021281568</v>
       </c>
       <c r="C85">
-        <v>-19015.13338381781</v>
+        <v>-19421.04493349734</v>
       </c>
       <c r="D85">
-        <v>8221.06761618219</v>
+        <v>8143.303066502659</v>
       </c>
       <c r="E85">
-        <v>18016.901</v>
+        <v>18345.048</v>
       </c>
       <c r="F85">
-        <v>27236.201</v>
+        <v>27564.348</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8361,37 +8361,37 @@
         <v>1181.9</v>
       </c>
       <c r="M85">
-        <v>5469.029160800001</v>
+        <v>5534.921078400001</v>
       </c>
       <c r="N85">
-        <v>-4287.129160800001</v>
+        <v>-4353.021078400001</v>
       </c>
       <c r="O85">
-        <v>-1106.0793234864</v>
+        <v>-1123.0794382272</v>
       </c>
       <c r="P85">
-        <v>-3181.049837313601</v>
+        <v>-3229.9416401728</v>
       </c>
       <c r="Q85">
-        <v>-2425.949837313601</v>
+        <v>-2474.8416401728</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2984734702712731</v>
+        <v>0.3142655621632278</v>
       </c>
       <c r="T85">
-        <v>5.835415017812313</v>
+        <v>6.200128456425583</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.05575581900086182</v>
+        <v>0.05509205925085156</v>
       </c>
       <c r="W85">
-        <v>0.189604231544627</v>
+        <v>0.189737514502429</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2161078255847356</v>
+        <v>0.2135351133753935</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8407,22 +8407,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2096620021281568</v>
+        <v>0.2112120021281568</v>
       </c>
       <c r="C86">
-        <v>-19421.04493349734</v>
+        <v>-19825.49909132558</v>
       </c>
       <c r="D86">
-        <v>8143.303066502659</v>
+        <v>8066.995908674416</v>
       </c>
       <c r="E86">
-        <v>18345.048</v>
+        <v>18673.195</v>
       </c>
       <c r="F86">
-        <v>27564.348</v>
+        <v>27892.495</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8443,37 +8443,37 @@
         <v>1181.9</v>
       </c>
       <c r="M86">
-        <v>5534.9210784</v>
+        <v>5600.812996</v>
       </c>
       <c r="N86">
-        <v>-4353.021078399999</v>
+        <v>-4418.912995999999</v>
       </c>
       <c r="O86">
-        <v>-1123.0794382272</v>
+        <v>-1140.079552968</v>
       </c>
       <c r="P86">
-        <v>-3229.941640172799</v>
+        <v>-3278.833443031999</v>
       </c>
       <c r="Q86">
-        <v>-2474.8416401728</v>
+        <v>-2523.733443031999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3142655621632275</v>
+        <v>0.3321632663074427</v>
       </c>
       <c r="T86">
-        <v>6.200128456425579</v>
+        <v>6.613470353520617</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.05509205925085157</v>
+        <v>0.05444391737731213</v>
       </c>
       <c r="W86">
-        <v>0.189737514502429</v>
+        <v>0.1898676613906357</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2135351133753938</v>
+        <v>0.2110229355709774</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8489,22 +8489,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2112120021281568</v>
+        <v>0.2127620021281568</v>
       </c>
       <c r="C87">
-        <v>-19825.49909132558</v>
+        <v>-20228.53644661042</v>
       </c>
       <c r="D87">
-        <v>8066.995908674416</v>
+        <v>7992.105553389575</v>
       </c>
       <c r="E87">
-        <v>18673.195</v>
+        <v>19001.342</v>
       </c>
       <c r="F87">
-        <v>27892.495</v>
+        <v>28220.642</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8525,37 +8525,37 @@
         <v>1181.9</v>
       </c>
       <c r="M87">
-        <v>5600.812996</v>
+        <v>5666.7049136</v>
       </c>
       <c r="N87">
-        <v>-4418.912995999999</v>
+        <v>-4484.804913599999</v>
       </c>
       <c r="O87">
-        <v>-1140.079552968</v>
+        <v>-1157.0796677088</v>
       </c>
       <c r="P87">
-        <v>-3278.833443031999</v>
+        <v>-3327.725245891199</v>
       </c>
       <c r="Q87">
-        <v>-2523.733443031999</v>
+        <v>-2572.625245891199</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3321632663074427</v>
+        <v>0.3526177853294029</v>
       </c>
       <c r="T87">
-        <v>6.613470353520617</v>
+        <v>7.085861093057804</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.05444391737731213</v>
+        <v>0.05381084857059921</v>
       </c>
       <c r="W87">
-        <v>0.1898676613906357</v>
+        <v>0.1899947816070237</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2110229355709774</v>
+        <v>0.2085691805061985</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8571,22 +8571,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2127620021281568</v>
+        <v>0.2143120021281568</v>
       </c>
       <c r="C88">
-        <v>-20228.53644661042</v>
+        <v>-20630.19609527228</v>
       </c>
       <c r="D88">
-        <v>7992.105553389575</v>
+        <v>7918.592904727721</v>
       </c>
       <c r="E88">
-        <v>19001.342</v>
+        <v>19329.489</v>
       </c>
       <c r="F88">
-        <v>28220.642</v>
+        <v>28548.789</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8607,37 +8607,37 @@
         <v>1181.9</v>
       </c>
       <c r="M88">
-        <v>5666.7049136</v>
+        <v>5732.5968312</v>
       </c>
       <c r="N88">
-        <v>-4484.804913599999</v>
+        <v>-4550.696831199999</v>
       </c>
       <c r="O88">
-        <v>-1157.0796677088</v>
+        <v>-1174.0797824496</v>
       </c>
       <c r="P88">
-        <v>-3327.725245891199</v>
+        <v>-3376.617048750399</v>
       </c>
       <c r="Q88">
-        <v>-2572.625245891199</v>
+        <v>-2621.517048750399</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3526177853294029</v>
+        <v>0.3762191534316647</v>
       </c>
       <c r="T88">
-        <v>7.085861093057804</v>
+        <v>7.630927330985328</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.05381084857059921</v>
+        <v>0.05319233306978773</v>
       </c>
       <c r="W88">
-        <v>0.1899947816070237</v>
+        <v>0.1901189795195866</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2085691805061985</v>
+        <v>0.2061718336038284</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8653,22 +8653,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2143120021281568</v>
+        <v>0.2158620021281568</v>
       </c>
       <c r="C89">
-        <v>-20630.19609527228</v>
+        <v>-21030.51570790022</v>
       </c>
       <c r="D89">
-        <v>7918.592904727721</v>
+        <v>7846.420292099774</v>
       </c>
       <c r="E89">
-        <v>19329.489</v>
+        <v>19657.636</v>
       </c>
       <c r="F89">
-        <v>28548.789</v>
+        <v>28876.936</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8689,37 +8689,37 @@
         <v>1181.9</v>
       </c>
       <c r="M89">
-        <v>5732.5968312</v>
+        <v>5798.488748799999</v>
       </c>
       <c r="N89">
-        <v>-4550.696831199999</v>
+        <v>-4616.588748799999</v>
       </c>
       <c r="O89">
-        <v>-1174.0797824496</v>
+        <v>-1191.0798971904</v>
       </c>
       <c r="P89">
-        <v>-3376.617048750399</v>
+        <v>-3425.508851609599</v>
       </c>
       <c r="Q89">
-        <v>-2621.517048750399</v>
+        <v>-2670.408851609599</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3762191534316647</v>
+        <v>0.4037540828843035</v>
       </c>
       <c r="T89">
-        <v>7.630927330985328</v>
+        <v>8.266837941900773</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.05319233306978773</v>
+        <v>0.05258787473944922</v>
       </c>
       <c r="W89">
-        <v>0.1901189795195866</v>
+        <v>0.1902403547523186</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2061718336038284</v>
+        <v>0.2038289718583304</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8735,22 +8735,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2158620021281568</v>
+        <v>0.2174120021281568</v>
       </c>
       <c r="C90">
-        <v>-21030.51570790022</v>
+        <v>-21429.53159411992</v>
       </c>
       <c r="D90">
-        <v>7846.420292099774</v>
+        <v>7775.551405880082</v>
       </c>
       <c r="E90">
-        <v>19657.636</v>
+        <v>19985.783</v>
       </c>
       <c r="F90">
-        <v>28876.936</v>
+        <v>29205.083</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8771,37 +8771,37 @@
         <v>1181.9</v>
       </c>
       <c r="M90">
-        <v>5798.488748799999</v>
+        <v>5864.3806664</v>
       </c>
       <c r="N90">
-        <v>-4616.588748799999</v>
+        <v>-4682.480666400001</v>
       </c>
       <c r="O90">
-        <v>-1191.0798971904</v>
+        <v>-1208.0800119312</v>
       </c>
       <c r="P90">
-        <v>-3425.508851609599</v>
+        <v>-3474.4006544688</v>
       </c>
       <c r="Q90">
-        <v>-2670.408851609599</v>
+        <v>-2719.300654468801</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4037540828843035</v>
+        <v>0.436295363146513</v>
       </c>
       <c r="T90">
-        <v>8.266837941900773</v>
+        <v>9.018368663891755</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.05258787473944922</v>
+        <v>0.05199699974237675</v>
       </c>
       <c r="W90">
-        <v>0.1902403547523186</v>
+        <v>0.1903590024517308</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2038289718583304</v>
+        <v>0.2015387586913827</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8817,22 +8817,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2174120021281568</v>
+        <v>0.2507713726970718</v>
       </c>
       <c r="C91">
-        <v>-21429.53159411992</v>
+        <v>-23023.16019437124</v>
       </c>
       <c r="D91">
-        <v>7775.551405880082</v>
+        <v>6510.069805628753</v>
       </c>
       <c r="E91">
-        <v>19985.783</v>
+        <v>20313.93</v>
       </c>
       <c r="F91">
-        <v>29205.083</v>
+        <v>29533.23</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8853,45 +8853,45 @@
         <v>1181.9</v>
       </c>
       <c r="M91">
-        <v>5864.3806664</v>
+        <v>6963.935634</v>
       </c>
       <c r="N91">
-        <v>-4682.480666400001</v>
+        <v>-5782.035634</v>
       </c>
       <c r="O91">
-        <v>-1208.0800119312</v>
+        <v>-1491.765193572</v>
       </c>
       <c r="P91">
-        <v>-3474.4006544688</v>
+        <v>-4290.270440427999</v>
       </c>
       <c r="Q91">
-        <v>-2719.300654468801</v>
+        <v>-3535.170440427999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.436295363146513</v>
+        <v>0.4784386051503148</v>
       </c>
       <c r="T91">
-        <v>9.018368663891755</v>
+        <v>9.991653698621588</v>
       </c>
       <c r="U91">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05199699974237675</v>
+        <v>0.04378705031551991</v>
       </c>
       <c r="W91">
-        <v>0.1903590024517308</v>
+        <v>0.2254750135356004</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.2015387586913827</v>
+        <v>0.1697172492849609</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8899,22 +8899,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2507713726970718</v>
+        <v>0.2526713726970718</v>
       </c>
       <c r="C92">
-        <v>-23023.16019437124</v>
+        <v>-23411.09861195326</v>
       </c>
       <c r="D92">
-        <v>6510.069805628753</v>
+        <v>6450.27838804674</v>
       </c>
       <c r="E92">
-        <v>20313.93</v>
+        <v>20642.077</v>
       </c>
       <c r="F92">
-        <v>29533.23</v>
+        <v>29861.377</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8935,37 +8935,37 @@
         <v>1181.9</v>
       </c>
       <c r="M92">
-        <v>6963.935634</v>
+        <v>7041.312696599999</v>
       </c>
       <c r="N92">
-        <v>-5782.035634</v>
+        <v>-5859.412696599999</v>
       </c>
       <c r="O92">
-        <v>-1491.765193572</v>
+        <v>-1511.7284757228</v>
       </c>
       <c r="P92">
-        <v>-4290.270440427999</v>
+        <v>-4347.684220877199</v>
       </c>
       <c r="Q92">
-        <v>-3535.170440427999</v>
+        <v>-3592.584220877199</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4784386051503148</v>
+        <v>0.5265095612781275</v>
       </c>
       <c r="T92">
-        <v>9.991653698621588</v>
+        <v>11.10183744291288</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04378705031551991</v>
+        <v>0.04330587393842629</v>
       </c>
       <c r="W92">
-        <v>0.2254750135356004</v>
+        <v>0.2255884749253191</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1697172492849609</v>
+        <v>0.1678522245675438</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8981,22 +8981,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2526713726970718</v>
+        <v>0.2545713726970719</v>
       </c>
       <c r="C93">
-        <v>-23411.09861195326</v>
+        <v>-23797.94872234125</v>
       </c>
       <c r="D93">
-        <v>6450.27838804674</v>
+        <v>6391.57527765875</v>
       </c>
       <c r="E93">
-        <v>20642.077</v>
+        <v>20970.224</v>
       </c>
       <c r="F93">
-        <v>29861.377</v>
+        <v>30189.524</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9017,37 +9017,37 @@
         <v>1181.9</v>
       </c>
       <c r="M93">
-        <v>7041.312696599999</v>
+        <v>7118.6897592</v>
       </c>
       <c r="N93">
-        <v>-5859.412696599999</v>
+        <v>-5936.789759199999</v>
       </c>
       <c r="O93">
-        <v>-1511.7284757228</v>
+        <v>-1531.6917578736</v>
       </c>
       <c r="P93">
-        <v>-4347.684220877199</v>
+        <v>-4405.0980013264</v>
       </c>
       <c r="Q93">
-        <v>-3592.584220877199</v>
+        <v>-3649.9980013264</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5265095612781275</v>
+        <v>0.5865982564378937</v>
       </c>
       <c r="T93">
-        <v>11.10183744291288</v>
+        <v>12.48956712327699</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04330587393842629</v>
+        <v>0.04283515791735643</v>
       </c>
       <c r="W93">
-        <v>0.2255884749253191</v>
+        <v>0.2256994697630874</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1678522245675438</v>
+        <v>0.1660277438657227</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9063,22 +9063,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2545713726970719</v>
+        <v>0.2564713726970719</v>
       </c>
       <c r="C94">
-        <v>-23797.94872234125</v>
+        <v>-24183.73997116386</v>
       </c>
       <c r="D94">
-        <v>6391.57527765875</v>
+        <v>6333.931028836132</v>
       </c>
       <c r="E94">
-        <v>20970.224</v>
+        <v>21298.371</v>
       </c>
       <c r="F94">
-        <v>30189.524</v>
+        <v>30517.671</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9099,37 +9099,37 @@
         <v>1181.9</v>
       </c>
       <c r="M94">
-        <v>7118.6897592</v>
+        <v>7196.0668218</v>
       </c>
       <c r="N94">
-        <v>-5936.789759199999</v>
+        <v>-6014.1668218</v>
       </c>
       <c r="O94">
-        <v>-1531.6917578736</v>
+        <v>-1551.6550400244</v>
       </c>
       <c r="P94">
-        <v>-4405.0980013264</v>
+        <v>-4462.5117817756</v>
       </c>
       <c r="Q94">
-        <v>-3649.9980013264</v>
+        <v>-3707.4117817756</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5865982564378937</v>
+        <v>0.6638551502147356</v>
       </c>
       <c r="T94">
-        <v>12.48956712327699</v>
+        <v>14.27379099803085</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04283515791735643</v>
+        <v>0.04237456482147087</v>
       </c>
       <c r="W94">
-        <v>0.2256994697630874</v>
+        <v>0.2258080776150972</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1660277438657227</v>
+        <v>0.1642424993080267</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9145,22 +9145,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2564713726970719</v>
+        <v>0.2583713726970718</v>
       </c>
       <c r="C95">
-        <v>-24183.73997116386</v>
+        <v>-24568.50075128909</v>
       </c>
       <c r="D95">
-        <v>6333.931028836132</v>
+        <v>6277.317248710911</v>
       </c>
       <c r="E95">
-        <v>21298.371</v>
+        <v>21626.518</v>
       </c>
       <c r="F95">
-        <v>30517.671</v>
+        <v>30845.818</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9181,37 +9181,37 @@
         <v>1181.9</v>
       </c>
       <c r="M95">
-        <v>7196.0668218</v>
+        <v>7273.443884400001</v>
       </c>
       <c r="N95">
-        <v>-6014.1668218</v>
+        <v>-6091.5438844</v>
       </c>
       <c r="O95">
-        <v>-1551.6550400244</v>
+        <v>-1571.6183221752</v>
       </c>
       <c r="P95">
-        <v>-4462.5117817756</v>
+        <v>-4519.9255622248</v>
       </c>
       <c r="Q95">
-        <v>-3707.4117817756</v>
+        <v>-3764.8255622248</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6638551502147356</v>
+        <v>0.7668643419171919</v>
       </c>
       <c r="T95">
-        <v>14.27379099803085</v>
+        <v>16.65275616436933</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04237456482147087</v>
+        <v>0.04192377157868928</v>
       </c>
       <c r="W95">
-        <v>0.2258080776150972</v>
+        <v>0.2259143746617451</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1642424993080267</v>
+        <v>0.1624952386770903</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9227,22 +9227,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2583713726970718</v>
+        <v>0.2602713726970719</v>
       </c>
       <c r="C96">
-        <v>-24568.50075128909</v>
+        <v>-24952.25844945624</v>
       </c>
       <c r="D96">
-        <v>6277.317248710911</v>
+        <v>6221.706550543762</v>
       </c>
       <c r="E96">
-        <v>21626.518</v>
+        <v>21954.665</v>
       </c>
       <c r="F96">
-        <v>30845.818</v>
+        <v>31173.965</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9263,37 +9263,37 @@
         <v>1181.9</v>
       </c>
       <c r="M96">
-        <v>7273.443884400001</v>
+        <v>7350.820947</v>
       </c>
       <c r="N96">
-        <v>-6091.5438844</v>
+        <v>-6168.920947000001</v>
       </c>
       <c r="O96">
-        <v>-1571.6183221752</v>
+        <v>-1591.581604326</v>
       </c>
       <c r="P96">
-        <v>-4519.9255622248</v>
+        <v>-4577.339342674</v>
       </c>
       <c r="Q96">
-        <v>-3764.8255622248</v>
+        <v>-3822.239342674</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7668643419171919</v>
+        <v>0.9110772103006307</v>
       </c>
       <c r="T96">
-        <v>16.65275616436933</v>
+        <v>19.98330739724321</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04192377157868928</v>
+        <v>0.04148246871996623</v>
       </c>
       <c r="W96">
-        <v>0.2259143746617451</v>
+        <v>0.226018433875832</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1624952386770903</v>
+        <v>0.1607847624804892</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9309,22 +9309,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2602713726970719</v>
+        <v>0.2621713726970719</v>
       </c>
       <c r="C97">
-        <v>-24952.25844945624</v>
+        <v>-25335.03949045104</v>
       </c>
       <c r="D97">
-        <v>6221.706550543762</v>
+        <v>6167.072509548963</v>
       </c>
       <c r="E97">
-        <v>21954.665</v>
+        <v>22282.812</v>
       </c>
       <c r="F97">
-        <v>31173.965</v>
+        <v>31502.112</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9345,37 +9345,37 @@
         <v>1181.9</v>
       </c>
       <c r="M97">
-        <v>7350.820947</v>
+        <v>7428.198009600001</v>
       </c>
       <c r="N97">
-        <v>-6168.920947000001</v>
+        <v>-6246.298009600001</v>
       </c>
       <c r="O97">
-        <v>-1591.581604326</v>
+        <v>-1611.5448864768</v>
       </c>
       <c r="P97">
-        <v>-4577.339342674</v>
+        <v>-4634.753123123201</v>
       </c>
       <c r="Q97">
-        <v>-3822.239342674</v>
+        <v>-3879.653123123201</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9110772103006307</v>
+        <v>1.127396512875789</v>
       </c>
       <c r="T97">
-        <v>19.98330739724321</v>
+        <v>24.97913424655401</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04148246871996623</v>
+        <v>0.04105035967079991</v>
       </c>
       <c r="W97">
-        <v>0.226018433875832</v>
+        <v>0.2261203251896254</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1607847624804892</v>
+        <v>0.1591099212046507</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9391,22 +9391,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2621713726970718</v>
+        <v>0.2640713726970718</v>
       </c>
       <c r="C98">
-        <v>-25335.03949045103</v>
+        <v>-25716.8693789735</v>
       </c>
       <c r="D98">
-        <v>6167.072509548967</v>
+        <v>6113.389621026497</v>
       </c>
       <c r="E98">
-        <v>22282.812</v>
+        <v>22610.959</v>
       </c>
       <c r="F98">
-        <v>31502.112</v>
+        <v>31830.25899999999</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9427,37 +9427,37 @@
         <v>1181.9</v>
       </c>
       <c r="M98">
-        <v>7428.1980096</v>
+        <v>7505.575072199999</v>
       </c>
       <c r="N98">
-        <v>-6246.298009599999</v>
+        <v>-6323.6750722</v>
       </c>
       <c r="O98">
-        <v>-1611.5448864768</v>
+        <v>-1631.5081686276</v>
       </c>
       <c r="P98">
-        <v>-4634.7531231232</v>
+        <v>-4692.1669035724</v>
       </c>
       <c r="Q98">
-        <v>-3879.6531231232</v>
+        <v>-3937.0669035724</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.127396512875786</v>
+        <v>1.487928683834381</v>
       </c>
       <c r="T98">
-        <v>24.97913424655394</v>
+        <v>33.3055123287386</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04105035967079992</v>
+        <v>0.04062716008656486</v>
       </c>
       <c r="W98">
-        <v>0.2261203251896254</v>
+        <v>0.226220115651588</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1591099212046508</v>
+        <v>0.1574696127386235</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9473,22 +9473,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2640713726970718</v>
+        <v>0.2659713726970718</v>
       </c>
       <c r="C99">
-        <v>-25716.8693789735</v>
+        <v>-26097.77273933799</v>
       </c>
       <c r="D99">
-        <v>6113.389621026497</v>
+        <v>6060.63326066201</v>
       </c>
       <c r="E99">
-        <v>22610.959</v>
+        <v>22939.106</v>
       </c>
       <c r="F99">
-        <v>31830.25899999999</v>
+        <v>32158.406</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9509,37 +9509,37 @@
         <v>1181.9</v>
       </c>
       <c r="M99">
-        <v>7505.575072199999</v>
+        <v>7582.952134799999</v>
       </c>
       <c r="N99">
-        <v>-6323.6750722</v>
+        <v>-6401.052134799998</v>
       </c>
       <c r="O99">
-        <v>-1631.5081686276</v>
+        <v>-1651.4714507784</v>
       </c>
       <c r="P99">
-        <v>-4692.1669035724</v>
+        <v>-4749.580684021599</v>
       </c>
       <c r="Q99">
-        <v>-3937.0669035724</v>
+        <v>-3994.480684021599</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.487928683834381</v>
+        <v>2.208993025751572</v>
       </c>
       <c r="T99">
-        <v>33.3055123287386</v>
+        <v>49.95826849310789</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04062716008656486</v>
+        <v>0.0402125972285387</v>
       </c>
       <c r="W99">
-        <v>0.226220115651588</v>
+        <v>0.2263178695735106</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1574696127386235</v>
+        <v>0.1558627799555764</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9555,22 +9555,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2659713726970718</v>
+        <v>0.2678713726970718</v>
       </c>
       <c r="C100">
-        <v>-26097.77273933799</v>
+        <v>-26477.77335313523</v>
       </c>
       <c r="D100">
-        <v>6060.63326066201</v>
+        <v>6008.779646864766</v>
       </c>
       <c r="E100">
-        <v>22939.106</v>
+        <v>23267.253</v>
       </c>
       <c r="F100">
-        <v>32158.406</v>
+        <v>32486.553</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9591,37 +9591,37 @@
         <v>1181.9</v>
       </c>
       <c r="M100">
-        <v>7582.952134799999</v>
+        <v>7660.329197399999</v>
       </c>
       <c r="N100">
-        <v>-6401.052134799998</v>
+        <v>-6478.429197399999</v>
       </c>
       <c r="O100">
-        <v>-1651.4714507784</v>
+        <v>-1671.4347329292</v>
       </c>
       <c r="P100">
-        <v>-4749.580684021599</v>
+        <v>-4806.994464470799</v>
       </c>
       <c r="Q100">
-        <v>-3994.480684021599</v>
+        <v>-4051.894464470799</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.208993025751572</v>
+        <v>4.372186051503142</v>
       </c>
       <c r="T100">
-        <v>49.95826849310789</v>
+        <v>99.91653698621577</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0402125972285387</v>
+        <v>0.03980640937774538</v>
       </c>
       <c r="W100">
-        <v>0.2263178695735106</v>
+        <v>0.2264136486687277</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9629,91 +9629,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1558627799555764</v>
+        <v>0.1542884084408735</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2678713726970718</v>
-      </c>
-      <c r="C101">
-        <v>-26477.77335313523</v>
-      </c>
-      <c r="D101">
-        <v>6008.779646864766</v>
-      </c>
-      <c r="E101">
-        <v>23267.253</v>
-      </c>
-      <c r="F101">
-        <v>32486.553</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>23595.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1937</v>
-      </c>
-      <c r="K101">
-        <v>755.0999999999999</v>
-      </c>
-      <c r="L101">
-        <v>1181.9</v>
-      </c>
-      <c r="M101">
-        <v>7660.329197399999</v>
-      </c>
-      <c r="N101">
-        <v>-6478.429197399999</v>
-      </c>
-      <c r="O101">
-        <v>-1671.4347329292</v>
-      </c>
-      <c r="P101">
-        <v>-4806.994464470799</v>
-      </c>
-      <c r="Q101">
-        <v>-4051.894464470799</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.372186051503142</v>
-      </c>
-      <c r="T101">
-        <v>99.91653698621577</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03980640937774538</v>
-      </c>
-      <c r="W101">
-        <v>0.2264136486687277</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1542884084408735</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
